--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ykraiem\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="8_{E38240D2-6D03-460C-AD1F-56A7CB9B1EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92565F34-EE0C-4D23-9F15-D94300D44B3F}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53012F43-4FC2-4F6E-9064-525D4764D57E}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="3795" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{78D94C61-402A-46A6-8F9B-6154C169E404}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Description" sheetId="3" r:id="rId1"/>
-    <sheet name="Indicateurs" sheetId="1" r:id="rId2"/>
-    <sheet name="Axes d'analyses" sheetId="2" r:id="rId3"/>
+    <sheet name="Description" sheetId="1" r:id="rId1"/>
+    <sheet name="Indicateurs" sheetId="2" r:id="rId2"/>
+    <sheet name="Axes d'analyses" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="258">
   <si>
     <t>Theme</t>
   </si>
@@ -95,6 +95,26 @@
     <t>SNE, INSEE</t>
   </si>
   <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>L'objectif est de présenter, pour chaque territoire, le volume de logements sociaux agréés dans l'année, leur répartition par type de financement (PLAI dont PLAI adapté, PLUS, PLS), par mode de production (construction neuve, acquisition-amélioration, acquisition sans travaux) et par nature du logement (ordinaire ou spécifique). Les typologies de logements (T1 à T5 et plus) sont également présentées.
+Les engagements dans le cadre du Programme National de Renouvellement Urbain (ANRU) font l'objet d'un traitement distinct et sont présentés séparément des opérations de droit commun. Seules les opérations de France métropolitaine et des régions d'Outre-Mer sont couvertes.</t>
+  </si>
+  <si>
+    <t>SIAP</t>
+  </si>
+  <si>
+    <t>Toutes les régions de France y compris les régions d'Outre-Mer</t>
+  </si>
+  <si>
+    <t>Financement</t>
+  </si>
+  <si>
+    <t>L'objectif est de présenter, pour chaque territoire, les coûts des opérations agréées dans l'année (coût global TTC et HT, coût par logement, coût au m²) ainsi que la décomposition du financement selon sa source : fonds propres de l'organisme, emprunts (prêts Caisse des Dépôts et assimilés) et subventions (État, collectivités territoriales, Action Logement et autres aides publiques). La part du foncier dans le coût global est également documentée.
+Les opérations ANRU sont exclues du périmètre. Seules les opérations de France métropolitaine et des régions d'Outre-Mer sont couvertes.</t>
+  </si>
+  <si>
     <t>Indicateur</t>
   </si>
   <si>
@@ -207,6 +227,9 @@
 Les régions d'outre-mer sont exclus du calcul puisque le DPE GES n'est pas renseigné</t>
   </si>
   <si>
+    <t>Part de locataires sociaux</t>
+  </si>
+  <si>
     <t>Calcul: Nombre de logements sociaux occupés / Nombre de résidences principales privées</t>
   </si>
   <si>
@@ -269,6 +292,9 @@
     <t>Moyenne de l'ancienneté de la demande au 31 décembre de l'année selectionnée. Il s'agit donc de l'écart entre le jour de la demande de logement social et le 31 décembre de l'année sélectionnée</t>
   </si>
   <si>
+    <t>,</t>
+  </si>
+  <si>
     <t>Pression de la demande</t>
   </si>
   <si>
@@ -333,6 +359,227 @@
   </si>
   <si>
     <t>Rapport entre le nombre de logements attribués sur l'année sélectionnée et le nombre de demande en stock à fin de l'année sélectionnée</t>
+  </si>
+  <si>
+    <t>Nombre d'agréments hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre total de logements sociaux ayant obtenu un agrément de financement au cours de l'année de référence, hors opérations du Programme National de Renouvellement Urbain (ANRU).
+Calcul : somme des agréments par opération.</t>
+  </si>
+  <si>
+    <t>Nombre de logements ordinaires hors ANRU</t>
+  </si>
+  <si>
+    <t>Parmi les logements agréés, nombre de logements à usage de résidence principale ordinaire, à l'exclusion des logements spécifiques (foyers de jeunes travailleurs, résidences sociales, pensions de famille, logements adaptés). Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de logements spécifiques hors ANRU</t>
+  </si>
+  <si>
+    <t>Parmi les logements agréés, nombre de logements à destination spécifique : résidences sociales, foyers de jeunes travailleurs, pensions de famille, logements adaptés aux personnes en situation de handicap ou âgées. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de PLAI hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés sous financement PLAI (Prêt Locatif Aidé d'Intégration), dont PLAI adapté. Le PLAI s'adresse aux ménages aux ressources très modestes et impose les niveaux de loyer les plus bas du parc social. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de PLAI adapté hors ANRU</t>
+  </si>
+  <si>
+    <t>Sous-ensemble du PLAI destiné aux personnes en très grande difficulté d'insertion sociale, dont le profil nécessite un accompagnement social renforcé. Ce volume est inclus dans le total PLAI. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de PLUS hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés sous financement PLUS (Prêt Locatif à Usage Social), financement de droit commun du logement social accessible à la majorité des ménages. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de PLS hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés sous financement PLS (Prêt Locatif Social). Le PLS s'adresse aux ménages dont les ressources dépassent les plafonds PLUS et dont les loyers sont intermédiaires entre le parc HLM classique et le marché privé. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de construction neuve hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés produits par construction sur terrain nu (ex nihilo). Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre d'acquisition-amélioration hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés produits par l'acquisition d'un bâtiment existant accompagnée de travaux de réhabilitation significatifs. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre d'acquisition sans travaux hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés produits par l'acquisition d'un bâtiment existant sans réalisation de travaux. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de T1 hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés de type T1 (une pièce principale). Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de T2 hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés de type T2 (deux pièces principales). Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de T3 hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés de type T3 (trois pièces principales). Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de T4 hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés de type T4 (quatre pièces principales). Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de T5 et plus hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés de type T5 et plus (cinq pièces principales et plus). Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre d'engagements ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements sociaux agréés dans le cadre d'opérations du Programme National de Renouvellement Urbain (ANRU). Présenté séparément des agréments de droit commun.</t>
+  </si>
+  <si>
+    <t>Nombre de PLAI ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements PLAI agréés dans le cadre d'opérations ANRU.</t>
+  </si>
+  <si>
+    <t>Nombre de PLUS ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements PLUS agréés dans le cadre d'opérations ANRU.</t>
+  </si>
+  <si>
+    <t>Total (Agréments + engagements)</t>
+  </si>
+  <si>
+    <t>Volume total de logements sociaux produits dans l'année : somme des agréments hors ANRU et des engagements ANRU.
+Calcul : Nombre d'agréments hors ANRU + Nombre d'engagements ANRU.</t>
+  </si>
+  <si>
+    <t>Coût global de l'opération hors ANRU TTC</t>
+  </si>
+  <si>
+    <t>Montant total toutes taxes comprises de l'ensemble des opérations de production agréées dans l'année, hors ANRU.</t>
+  </si>
+  <si>
+    <t>Coût global de l'opération hors ANRU HT</t>
+  </si>
+  <si>
+    <t>Montant total hors taxes de l'ensemble des opérations de production agréées dans l'année, hors ANRU.</t>
+  </si>
+  <si>
+    <t>Coût de construction moyen hors ANRU TTC par logement</t>
+  </si>
+  <si>
+    <t>Coût moyen de l'opération TTC par logement agréé, calculé en rapportant le coût global TTC au nombre total d'agréments.
+Calcul : Coût global TTC / Nombre d'agréments hors ANRU.</t>
+  </si>
+  <si>
+    <t>Coût de construction médian hors ANRU TTC par logement</t>
+  </si>
+  <si>
+    <t>Médiane des coûts TTC par logement, calculée opération par opération. Moins sensible aux opérations atypiques que la moyenne, la médiane est l'indicateur de référence pour comparer les coûts de production entre territoires. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Coût de construction moyen hors ANRU TTC par m²</t>
+  </si>
+  <si>
+    <t>Coût moyen de construction TTC par m² de surface utile, calculé sur les opérations dont la surface est renseignée. Hors ANRU.
+Calcul : somme des coûts TTC des opérations à surface renseignée / surface utile totale de ces opérations.</t>
+  </si>
+  <si>
+    <t>Coût du foncier hors ANRU HT</t>
+  </si>
+  <si>
+    <t>Montant total hors taxes consacré à l'acquisition du foncier pour l'ensemble des opérations agréées dans l'année. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Part du foncier hors ANRU</t>
+  </si>
+  <si>
+    <t>Part du coût foncier dans le coût global HT des opérations agréées. Indicateur permettant d'apprécier la pression foncière par territoire.
+Calcul : Coût du foncier HT / Coût global HT.</t>
+  </si>
+  <si>
+    <t>Coût du bâtiment hors ANRU HT</t>
+  </si>
+  <si>
+    <t>Montant total hors taxes des travaux de construction ou de réhabilitation du bâtiment pour l'ensemble des opérations agréées dans l'année. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Coût des prestations intellectuelles hors ANRU HT</t>
+  </si>
+  <si>
+    <t>Montant total hors taxes des honoraires (maîtrise d'œuvre, études techniques, contrôle technique, assurances...) pour l'ensemble des opérations agréées. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Montant Fonds propres hors ANRU TTC</t>
+  </si>
+  <si>
+    <t>Montant total TTC financé par les fonds propres de l'organisme bailleur pour les opérations agréées dans l'année. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Montant Prêts hors ANRU TTC</t>
+  </si>
+  <si>
+    <t>Montant total TTC des emprunts contractés (prêts de la Caisse des Dépôts, prêts bancaires, prêts Action Logement...) pour les opérations agréées. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Coût de construction moyen emprunts hors ANRU TTC</t>
+  </si>
+  <si>
+    <t>Part des emprunts dans le financement, ramenée au logement. Calcul : Montant total des prêts TTC / Nombre d'agréments hors ANRU.</t>
+  </si>
+  <si>
+    <t>Montant Subventions hors ANRU TTC</t>
+  </si>
+  <si>
+    <t>Montant total TTC des subventions reçues — État (aides à la pierre), collectivités territoriales, Action Logement, autres financeurs publics — pour les opérations agréées dans l'année. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Coût source de financement hors ANRU TTC</t>
+  </si>
+  <si>
+    <t>Montant TTC apporté par la source de financement sélectionnée (fonds propres, prêts ou subventions) pour les opérations agréées, hors ANRU. Utilisé en combinaison avec le filtre par source de financement pour décomposer la structure de financement.</t>
+  </si>
+  <si>
+    <t>Nombre d'agréments hors ANRU (financement)</t>
+  </si>
+  <si>
+    <t>Nombre de logements agréés calculé depuis la table de financement, en agrégeant les données par opération et par source de financement. Donne le même résultat que le total Production mais depuis la table de financement. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Coût global de l'opération hors ANRU TTC (financement)</t>
+  </si>
+  <si>
+    <t>Montant total TTC ventilé par source de financement pour les opérations agréées dans l'année. Permet l'analyse du coût par source de financement. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Surface utile totale en m² hors ANRU</t>
+  </si>
+  <si>
+    <t>Somme des surfaces utiles en m² des logements agréés dans l'année. Hors ANRU.</t>
   </si>
   <si>
     <t>Axe</t>
@@ -603,22 +850,28 @@
 Radiation pour cause de non renouvellement</t>
   </si>
   <si>
-    <t>Part de locataires sociaux</t>
-  </si>
-  <si>
     <t>DALO</t>
   </si>
   <si>
+    <t>Demandeurs et attributaires reconnus prioritaires au titre DALO</t>
+  </si>
+  <si>
+    <t>Il s'agit d'une demande ou d'une attribution DALO ssi :
+- le statut dalo est différent de NON
+- le statut dalo n'est pas null
+- la date de décision dalo &lt;= 31/12/N</t>
+  </si>
+  <si>
     <t>Premier quartile</t>
   </si>
   <si>
+    <t>Demandeurs et attributaires dont les ressources se situent sous le premier quartile de ressources sur les territoires concernés par la réforme des attributions</t>
+  </si>
+  <si>
+    <t>Il s'agit d'une demande ou d'une attribution Premier quartile ssi (montant du revenu mensuel du foyer / unité de consommation) x 12 mois &lt;= montant du seuil de ressources</t>
+  </si>
+  <si>
     <t>Logement d'abord</t>
-  </si>
-  <si>
-    <t>Demandeurs et attributaires reconnus prioritaires au titre DALO</t>
-  </si>
-  <si>
-    <t>Demandeurs et attributaires dont les ressources se situent sous le premier quartile de ressources sur les territoires concernés par la réforme des attributions</t>
   </si>
   <si>
     <t>Demandeurs et attributaires bénéficiant du plan Logement d'abord</t>
@@ -636,20 +889,83 @@
 - Coordination thérapeutique</t>
   </si>
   <si>
-    <t>Il s'agit d'une demande ou d'une attribution Premier quartile ssi (montant du revenu mensuel du foyer / unité de consommation) x 12 mois &lt;= montant du seuil de ressources</t>
-  </si>
-  <si>
-    <t>Il s'agit d'une demande ou d'une attribution DALO ssi :
-- le statut dalo est différent de NON
-- le statut dalo n'est pas null
-- la date de décision dalo &lt;= 31/12/N</t>
+    <t>Mode de production</t>
+  </si>
+  <si>
+    <t>Mode de réalisation technique de l'opération de production de logements sociaux.</t>
+  </si>
+  <si>
+    <t>Construction neuve : logements construits sur terrain nu
+Acquisition-amélioration : acquisition d'un bâtiment existant avec travaux
+Acquisition sans travaux : achat d'un bâtiment existant sans réhabilitation
+Autre</t>
+  </si>
+  <si>
+    <t>Mode d'acquisition</t>
+  </si>
+  <si>
+    <t>Modalité juridique d'acquisition du foncier ou du bâti pour la réalisation de l'opération.</t>
+  </si>
+  <si>
+    <t>Construction sur terrain acquis · VEFA (Vente en État Futur d'Achèvement) · Bail emphytéotique · Bail à construction · Acquisition directe · Autre</t>
+  </si>
+  <si>
+    <t>Nature du logement</t>
+  </si>
+  <si>
+    <t>Catégorie du logement produit selon sa destination et sa réglementation.</t>
+  </si>
+  <si>
+    <t>Logement ordinaire : logement locatif social à usage de résidence principale
+Logement spécifique : résidence sociale, foyer de jeunes travailleurs, pension de famille, résidence étudiante
+Logement adapté : adapté aux personnes en situation de handicap ou âgées</t>
+  </si>
+  <si>
+    <t>Type de financement public accordé à l'opération. Détermine le niveau de loyer maximal et les plafonds de ressources des locataires.</t>
+  </si>
+  <si>
+    <t>PLAI : Prêt Locatif Aidé d'Intégration (ménages très modestes)
+PLUS : Prêt Locatif à Usage Social (financement de droit commun)
+PLS : Prêt Locatif Social (ménages aux revenus intermédiaires)
+Autres financements aidés</t>
+  </si>
+  <si>
+    <t>Type de bénéficiaire</t>
+  </si>
+  <si>
+    <t>Catégorie de l'organisme maître d'ouvrage bénéficiaire de l'agrément de production.</t>
+  </si>
+  <si>
+    <t>ESH (Entreprise Sociale pour l'Habitat / SA HLM) · OPH (Office Public de l'Habitat) · Coopérative HLM · SEM (Société d'Économie Mixte) · Organisme agréé · Autre</t>
+  </si>
+  <si>
+    <t>ANRU / Hors ANRU</t>
+  </si>
+  <si>
+    <t>Segmentation permettant de distinguer les opérations relevant du Programme National de Renouvellement Urbain (ANRU) de celles de droit commun.</t>
+  </si>
+  <si>
+    <t>ANRU : opérations engagées dans le cadre du renouvellement urbain
+Hors ANRU : opérations de droit commun
+Total : ANRU + Hors ANRU</t>
+  </si>
+  <si>
+    <t>Source de financement</t>
+  </si>
+  <si>
+    <t>Organisme ou dispositif ayant apporté un financement à l'opération de production. Trois grandes catégories sont distinguées selon la nature du financement.</t>
+  </si>
+  <si>
+    <t>Fonds propres : apport direct de l'organisme bailleur social
+Emprunts : prêts de la Caisse des Dépôts, prêts bancaires, prêts Action Logement
+Subventions : aides à la pierre de l'État, subventions des collectivités territoriales, aides Action Logement, autres aides publiques</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -725,9 +1041,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -743,6 +1059,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1077,15 +1394,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF32A818-55DC-4C7D-829B-81D7B53E1994}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.3984375" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="109" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1426,7 @@
       </c>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" ht="128.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="128.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1130,7 +1447,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="85.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1151,431 +1468,872 @@
         <v>12</v>
       </c>
     </row>
+    <row r="4" spans="1:8" ht="85.5">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="71.25">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{EAB25B75-F1A1-4ADD-A90A-A502A052CA55}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{4C3DA737-6F2E-421C-84D3-2B4B25E9F2D7}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C998C4-4C13-4862-92D5-F4E9358593F6}">
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.59765625" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="65.5703125" customWidth="1"/>
+    <col min="3" max="3" width="73.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="42.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="42.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="42.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="57" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="71.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="57" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="71.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="28.5" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="57" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="57" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="42.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="85.5" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="57" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="57" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="57" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="42.75" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="28.5" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="71.25" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="57" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="42.75" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="28.5" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="28.5" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="57">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="42.75">
+      <c r="A39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="42.75">
+      <c r="A40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="42.75">
+      <c r="A41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="42.75">
+      <c r="A42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="42.75">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="42.75">
+      <c r="A44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="28.5">
+      <c r="A46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="28.5">
+      <c r="A47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="28.5">
+      <c r="A53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="42.75">
+      <c r="A56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="28.5">
+      <c r="A57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="28.5">
+      <c r="A58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="42.75">
+      <c r="A59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="42.75">
+      <c r="A60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="57">
+      <c r="A61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="28.5">
+      <c r="A62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="42.75">
+      <c r="A63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="28.5">
+      <c r="A64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="57" x14ac:dyDescent="0.45">
-      <c r="A25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>88</v>
+      <c r="C64" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="28.5">
+      <c r="A65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="28.5">
+      <c r="A66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="28.5">
+      <c r="A67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="28.5">
+      <c r="A68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="42.75">
+      <c r="A69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="42.75">
+      <c r="A70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="42.75">
+      <c r="A71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="28.5">
+      <c r="A72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1584,387 +2342,526 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D63C1C-82A7-4D8E-A65D-B74419366C15}">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
-    <col min="2" max="2" width="33.59765625" customWidth="1"/>
-    <col min="3" max="3" width="34.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.265625" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="85.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>174</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="42.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="114" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="114" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="128.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="99.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="99.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="171" x14ac:dyDescent="0.45">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="171" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="187.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="187.5" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>197</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="85.5" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>122</v>
+        <v>202</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="270.75" x14ac:dyDescent="0.45">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="270.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>124</v>
+        <v>204</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="171" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="285" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="285" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="85.5" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="242.25" x14ac:dyDescent="0.45">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="242.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>137</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="71.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="99.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="85.5" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>146</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="71.25" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="57" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>151</v>
+        <v>232</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="171" x14ac:dyDescent="0.45">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="171" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>152</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C27" s="5"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C29" s="5"/>
-    </row>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="85.5">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="42.75">
+      <c r="A26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="85.5">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="57">
+      <c r="A28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="42.75">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="57">
+      <c r="A30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="85.5">
+      <c r="A31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="85.5">
+      <c r="A32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="42.75">
+      <c r="A33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="85.5">
+      <c r="A34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="57">
+      <c r="A35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="42.75">
+      <c r="A36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052237A89E8CA214B92381756AEA23611" ma:contentTypeVersion="20" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="510f2d890aca16c7e52118f19c292bce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44042f46-c638-40f0-b803-0a3c16db3a5d" xmlns:ns3="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5bb1233f2449b16a4f87373320f89a9" ns2:_="" ns3:_="">
     <xsd:import namespace="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
@@ -2264,7 +3161,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2273,40 +3170,29 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB5A1737-75AC-4C46-9CF2-0725CB708A15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8E4D90C-A9A5-4A73-BF8C-EEF74536E875}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C7AC71B-59C7-4E14-BBB6-8E6DAC860991}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F53CA91-B762-4110-8F3F-3FE1EDA322A6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}"/>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ykraiem\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53012F43-4FC2-4F6E-9064-525D4764D57E}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05819AB5-ECE2-4619-8CA4-6E7CA24BB8D7}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>Fréquence de rafraichissement</t>
   </si>
   <si>
-    <t>Dernière date de rafraichissement</t>
-  </si>
-  <si>
     <t>Sources</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
   </si>
   <si>
     <t xml:space="preserve">Toutes les régions de France y compris les  régions d’Outre-Mer </t>
-  </si>
-  <si>
-    <t>Demande et attribution</t>
   </si>
   <si>
     <t>Le rapport sur les demandes et les attributions de logements sociaux est réalisé à partir des données du Système National d’Enregistrement (SNE). Il met en parallèle le profil des demandeurs avec celui des attributaires de logements sociaux et montre l’adéquation entre les attributions et la demande au travers de différents indicateurs. 
@@ -960,12 +954,18 @@
 Emprunts : prêts de la Caisse des Dépôts, prêts bancaires, prêts Action Logement
 Subventions : aides à la pierre de l'État, subventions des collectivités territoriales, aides Action Logement, autres aides publiques</t>
   </si>
+  <si>
+    <t>Demandes et attributions</t>
+  </si>
+  <si>
+    <t>Ordre</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1396,13 +1396,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.86328125" customWidth="1"/>
     <col min="2" max="2" width="109" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1416,98 +1416,106 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="128.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" ht="128.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="85.5" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="85.5">
-      <c r="A4" s="1" t="s">
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="9" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="71.25">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1522,818 +1530,818 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G73"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="65.5703125" customWidth="1"/>
-    <col min="3" max="3" width="73.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="2" max="2" width="65.59765625" customWidth="1"/>
+    <col min="3" max="3" width="73.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="42.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="42.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="42.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="57" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="6" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="71.25" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="7" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="8" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="71.25" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="9" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="28.5" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="10" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="57" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="11" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="57" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="42.75" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    <row r="13" spans="1:3" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="85.5" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1" t="s">
+    <row r="14" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="57" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1" t="s">
+    <row r="15" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="57" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1" t="s">
+    <row r="16" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="57" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="1" t="s">
+    <row r="19" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="42.75" customHeight="1">
-      <c r="A19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="1" t="s">
+    <row r="20" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="1" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="1" t="s">
+    <row r="22" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="71.25" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="1" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="1" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="1" t="s">
+    <row r="25" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="57" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="1" t="s">
+    <row r="26" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="42.75" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="6" t="s">
+      <c r="G26" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G26" t="s">
+      <c r="C27" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="6" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="1" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="1" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="1" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="1" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="1" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="1" t="s">
+    <row r="34" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="28.5" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="1" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="1" t="s">
+    <row r="37" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="28.5" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="1" t="s">
+    <row r="38" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="57">
-      <c r="A38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="1" t="s">
+    <row r="39" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="42.75">
-      <c r="A39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" s="1" t="s">
+    <row r="40" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="42.75">
-      <c r="A40" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="42.75">
-      <c r="A41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" s="1" t="s">
+    <row r="42" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="42.75">
-      <c r="A42" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="1" t="s">
+    <row r="43" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="42.75">
-      <c r="A43" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" s="1" t="s">
+    <row r="44" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="42.75">
-      <c r="A44" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B44" s="1" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" s="1" t="s">
+    <row r="46" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="28.5">
-      <c r="A46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="28.5">
-      <c r="A47" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" s="1" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" s="1" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49" s="1" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" s="1" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" s="1" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" s="1" t="s">
+    <row r="53" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="28.5">
-      <c r="A53" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B54" s="1" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="42.75">
-      <c r="A56" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="28.5">
-      <c r="A57" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B57" s="1" t="s">
+    <row r="58" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="28.5">
-      <c r="A58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B58" s="1" t="s">
+    <row r="59" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="42.75">
-      <c r="A59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="1" t="s">
+    <row r="60" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="42.75">
-      <c r="A60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B60" s="1" t="s">
+    <row r="61" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+      <c r="A61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="57">
-      <c r="A61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="28.5">
-      <c r="A62" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B62" s="1" t="s">
+    <row r="63" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="42.75">
-      <c r="A63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B63" s="1" t="s">
+    <row r="64" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="28.5">
-      <c r="A64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B64" s="1" t="s">
+    <row r="65" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="28.5">
-      <c r="A65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B65" s="1" t="s">
+    <row r="66" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="28.5">
-      <c r="A66" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B66" s="1" t="s">
+    <row r="67" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="28.5">
-      <c r="A67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="28.5">
-      <c r="A68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B68" s="1" t="s">
+    <row r="69" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="42.75">
-      <c r="A69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B69" s="1" t="s">
+    <row r="70" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="42.75">
-      <c r="A70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B70" s="1" t="s">
+    <row r="71" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="42.75">
-      <c r="A71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B71" s="1" t="s">
+    <row r="72" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="28.5">
-      <c r="A72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B72" s="1" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2343,525 +2351,533 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.73046875" customWidth="1"/>
+    <col min="2" max="2" width="33.59765625" customWidth="1"/>
+    <col min="3" max="3" width="34.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="85.5" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" ht="42.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="114" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="114" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="128.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="128.25" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="57" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="99.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="99.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="171" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="187.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="187.5" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="85.5" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="270.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="270.75" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="57" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="171" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="285" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="285" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="85.5" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="242.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="242.25" customHeight="1">
-      <c r="A18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="71.25" customHeight="1">
-      <c r="A19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="99.75" customHeight="1">
-      <c r="A20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="85.5" customHeight="1">
-      <c r="A21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C21" s="2" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="71.25" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="23" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="C23" s="8" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="57" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C23" s="8" t="s">
+    </row>
+    <row r="24" spans="1:4" ht="171" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="171" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C24" s="2" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="85.5">
-      <c r="A25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C25" s="2" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="42.75">
-      <c r="A26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="85.5">
-      <c r="A27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="D27" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="28" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="57">
-      <c r="A28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28" s="2" t="s">
+    <row r="29" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="42.75">
-      <c r="A29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="57">
-      <c r="A30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="85.5">
-      <c r="A31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="85.5">
+    </row>
+    <row r="32" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C32" s="2" t="s">
+    </row>
+    <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="42.75">
-      <c r="A33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="2" t="s">
+    </row>
+    <row r="34" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="85.5">
-      <c r="A34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C34" s="2" t="s">
+    </row>
+    <row r="35" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="57">
-      <c r="A35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C35" s="2" t="s">
+    <row r="36" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="42.75">
-      <c r="A36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="D36" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052237A89E8CA214B92381756AEA23611" ma:contentTypeVersion="20" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="510f2d890aca16c7e52118f19c292bce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44042f46-c638-40f0-b803-0a3c16db3a5d" xmlns:ns3="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5bb1233f2449b16a4f87373320f89a9" ns2:_="" ns3:_="">
     <xsd:import namespace="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
@@ -3161,15 +3177,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3186,13 +3193,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8E4D90C-A9A5-4A73-BF8C-EEF74536E875}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8E4D90C-A9A5-4A73-BF8C-EEF74536E875}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05819AB5-ECE2-4619-8CA4-6E7CA24BB8D7}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53FDE3FC-9C32-4A9C-91F1-3ECA30E64516}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -82,10 +82,6 @@
     <t xml:space="preserve">Toutes les régions de France y compris les  régions d’Outre-Mer </t>
   </si>
   <si>
-    <t>Le rapport sur les demandes et les attributions de logements sociaux est réalisé à partir des données du Système National d’Enregistrement (SNE). Il met en parallèle le profil des demandeurs avec celui des attributaires de logements sociaux et montre l’adéquation entre les attributions et la demande au travers de différents indicateurs. 
-Sont considérés comme « demandeurs » les demandeurs en attente d’un logement social à fin décembre &lt;annee&gt; et sont comptés comme « attributaires » les ménages ayant emménagé dans un logement social durant l’année &lt;annee&gt;. Les chiffres et indicateurs présentés sur le tableau de bord ne prennent pas en compte la demande des associations, mais uniquement celle des demandeurs physiques</t>
-  </si>
-  <si>
     <t>SNE, INSEE</t>
   </si>
   <si>
@@ -94,9 +90,6 @@
   <si>
     <t>L'objectif est de présenter, pour chaque territoire, le volume de logements sociaux agréés dans l'année, leur répartition par type de financement (PLAI dont PLAI adapté, PLUS, PLS), par mode de production (construction neuve, acquisition-amélioration, acquisition sans travaux) et par nature du logement (ordinaire ou spécifique). Les typologies de logements (T1 à T5 et plus) sont également présentées.
 Les engagements dans le cadre du Programme National de Renouvellement Urbain (ANRU) font l'objet d'un traitement distinct et sont présentés séparément des opérations de droit commun. Seules les opérations de France métropolitaine et des régions d'Outre-Mer sont couvertes.</t>
-  </si>
-  <si>
-    <t>SIAP</t>
   </si>
   <si>
     <t>Toutes les régions de France y compris les régions d'Outre-Mer</t>
@@ -959,6 +952,13 @@
   </si>
   <si>
     <t>Ordre</t>
+  </si>
+  <si>
+    <t>Le rapport sur les demandes et les attributions de logements sociaux est réalisé à partir des données du Système National d’Enregistrement (SNE). Il met en parallèle le profil des demandeurs avec celui des attributaires de logements sociaux et montre l’adéquation entre les attributions et la demande au travers de différents indicateurs. 
+Sont considérés comme « demandeurs » les demandeurs en attente d’un logement social à fin décembre de l'année selectionnée et sont comptés comme « attributaires » les ménages ayant emménagé dans un logement social durant l’année sélectionnée. Les chiffres et indicateurs présentés sur le tableau de bord ne prennent pas en compte la demande des associations, mais uniquement celle des demandeurs physiques</t>
+  </si>
+  <si>
+    <t>SIAP, INSEE</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1416,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>4</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="3" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>8</v>
@@ -1466,7 +1466,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>11</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="4" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>8</v>
@@ -1489,18 +1489,18 @@
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>8</v>
@@ -1512,10 +1512,10 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1554,10 +1554,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1565,10 +1565,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1576,10 +1576,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -1587,10 +1587,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -1598,10 +1598,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -1609,10 +1609,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -1620,10 +1620,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -1631,10 +1631,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -1642,10 +1642,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -1653,10 +1653,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1664,10 +1664,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -1675,10 +1675,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -1686,10 +1686,10 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -1697,10 +1697,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -1708,10 +1708,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -1719,629 +1719,629 @@
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" t="s">
         <v>70</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2365,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2379,13 +2379,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2393,10 +2393,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -2405,13 +2405,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="114" customHeight="1" x14ac:dyDescent="0.45">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="128.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2433,13 +2433,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -2447,13 +2447,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -2461,13 +2461,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -2475,13 +2475,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
@@ -2489,378 +2489,378 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="187.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="270.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="285" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="242.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="171" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -2869,12 +2869,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3178,24 +3184,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3220,12 +3223,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53FDE3FC-9C32-4A9C-91F1-3ECA30E64516}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1D909FE-12AE-473A-9C2A-A5C4731ACEF4}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38295" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="374">
   <si>
     <t>Theme</t>
   </si>
@@ -698,10 +698,6 @@
 Famille monoparentale: Ménage où une seule personne est titulaire du bail ayant une ou plusieurs personne(s) à charge dont le lien avec le demandeur et la différence d'âge s'apparente à un lien de parenté.
 Couple sans enfant: Ménage formé de deux personnes co-titulaires du bail dont le lien est d'être conjoints, pacsés ou concubins, sans personne à charge
 Autre: Ménages n'entrant pas dans les catégories sus-citées.</t>
-  </si>
-  <si>
-    <t>verifier pour le co titulaire couple
-verifier famille mono</t>
   </si>
   <si>
     <t>Tranche de ressources par UC</t>
@@ -959,6 +955,357 @@
   </si>
   <si>
     <t>SIAP, INSEE</t>
+  </si>
+  <si>
+    <t>Relogement</t>
+  </si>
+  <si>
+    <t>Nombre d'opérations</t>
+  </si>
+  <si>
+    <t>Nombre de ménages pris en charge</t>
+  </si>
+  <si>
+    <t>Nombre de départs spontanés ou autres</t>
+  </si>
+  <si>
+    <t>Moyenne de propositions par ménage relogé</t>
+  </si>
+  <si>
+    <t>Nombre de logements concernés</t>
+  </si>
+  <si>
+    <t>Nombre de logements vacants</t>
+  </si>
+  <si>
+    <t>Nombre de ménages relogés</t>
+  </si>
+  <si>
+    <t>Nombre de ménages à reloger</t>
+  </si>
+  <si>
+    <t>Pourcentage de relogement</t>
+  </si>
+  <si>
+    <t>Nombre de décohabitants</t>
+  </si>
+  <si>
+    <t>Nombre de dossiers</t>
+  </si>
+  <si>
+    <t>Nombre d'opérations de relogement distinctes comprises dans le périmètre d'analyse sélectionné.</t>
+  </si>
+  <si>
+    <t>Nombre total de ménages suivis au titre du relogement, dossiers principaux et supplémentaires (hébergés, décohabitants) confondus, tous statuts.</t>
+  </si>
+  <si>
+    <t>Ménages sortis du dispositif sans relogement par le bailleur : départ spontané (décès, départ volontaire), expulsion, prise en charge associative, etc.</t>
+  </si>
+  <si>
+    <t>Nombre moyen de propositions écrites de logement adressées aux ménages effectivement relogés.</t>
+  </si>
+  <si>
+    <t>Nombre total de logements de l'opération concernés par le relogement (occupés + vacants).</t>
+  </si>
+  <si>
+    <t>Parmi les logements concernés, ceux qui étaient vacants.</t>
+  </si>
+  <si>
+    <t>Ménages ayant fait l'objet d'un relogement effectif (statut de relogement = « Oui »).</t>
+  </si>
+  <si>
+    <t>Ménages pris en charge restant à reloger.</t>
+  </si>
+  <si>
+    <t>Part des ménages relogés sur l'ensemble des ménages pris en charge ; mesure l'état d'avancement global.</t>
+  </si>
+  <si>
+    <t>Ménages dont le statut d'occupation antérieur est une décohabitation (départ d'un membre du foyer vers un logement autonome).</t>
+  </si>
+  <si>
+    <t>Nombre de dossiers de relogement du périmètre (utilisé notamment dans le suivi par année).</t>
+  </si>
+  <si>
+    <t>Vue d'ensemble</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Pourcentage des 65 ans et plus</t>
+  </si>
+  <si>
+    <t>Nombre de ménages avec ancienneté de plus de 10 ans</t>
+  </si>
+  <si>
+    <t>Pourcentage de personnes isolées</t>
+  </si>
+  <si>
+    <t>Pourcentage du total</t>
+  </si>
+  <si>
+    <t>Profil des ménages — démographie</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le représentant est âgé de 65 ans ou plus.</t>
+  </si>
+  <si>
+    <t>Ménages occupant leur logement d'origine depuis plus de 10 ans (tranches 10-15 ans et plus de 15 ans).</t>
+  </si>
+  <si>
+    <t>Part des ménages composés d'une personne seule.</t>
+  </si>
+  <si>
+    <t>Part (en %) d'une catégorie dans le total affiché à l'écran ; mesure de répartition générique des tableaux « Nombre + % total ».</t>
+  </si>
+  <si>
+    <t>Moyenne des ressources mensuelles</t>
+  </si>
+  <si>
+    <t>Moyenne du revenu fiscal de référence</t>
+  </si>
+  <si>
+    <t>Pourcentage de bénéficiaires des APL</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages en emploi</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages retraités</t>
+  </si>
+  <si>
+    <t>Profil des ménages — finances</t>
+  </si>
+  <si>
+    <t>Ressources mensuelles moyennes du ménage, prestations sociales comprises.</t>
+  </si>
+  <si>
+    <t>Revenu fiscal de référence moyen des ménages.</t>
+  </si>
+  <si>
+    <t>Part des ménages percevant une aide personnalisée au logement (APL réelle).</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le représentant occupe un emploi, stable ou précaire.</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le représentant est retraité.</t>
+  </si>
+  <si>
+    <t>Évolution de la surroccupation (points)</t>
+  </si>
+  <si>
+    <t>Moyenne de l'évolution du nombre de pièces</t>
+  </si>
+  <si>
+    <t>Moyenne de l'évolution de la surface (m²)</t>
+  </si>
+  <si>
+    <t>Moyenne de la surface habitable avant</t>
+  </si>
+  <si>
+    <t>Moyenne de la surface habitable après</t>
+  </si>
+  <si>
+    <t>Moyenne de l'évolution de la surface (%)</t>
+  </si>
+  <si>
+    <t>Variation, en points, de la part de ménages en situation de sur-occupation entre avant et après le relogement.</t>
+  </si>
+  <si>
+    <t>Variation moyenne du nombre de pièces du logement entre avant et après le relogement.</t>
+  </si>
+  <si>
+    <t>Variation moyenne de la surface habitable (m²) entre avant et après le relogement.</t>
+  </si>
+  <si>
+    <t>Surface habitable moyenne du logement d'origine.</t>
+  </si>
+  <si>
+    <t>Surface habitable moyenne du logement de relogement.</t>
+  </si>
+  <si>
+    <t>Variation moyenne de la surface habitable, exprimée en pourcentage de la surface du logement d'origine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Évolution des conditions de logement</t>
+  </si>
+  <si>
+    <t>Moyenne du reste à charge après</t>
+  </si>
+  <si>
+    <t>Moyenne du reste à charge avant</t>
+  </si>
+  <si>
+    <t>Moyenne du taux d'effort avant</t>
+  </si>
+  <si>
+    <t>Moyenne du taux d'effort après</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages au taux d'effort critique (plus de 30 %)</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages avec hausse du taux d'effort</t>
+  </si>
+  <si>
+    <t>Moyenne du loyer avant</t>
+  </si>
+  <si>
+    <t>Moyenne du loyer après</t>
+  </si>
+  <si>
+    <t>Moyenne des charges avant</t>
+  </si>
+  <si>
+    <t>Moyenne des charges après</t>
+  </si>
+  <si>
+    <t>Moyenne de l'APL avant</t>
+  </si>
+  <si>
+    <t>Moyenne de l'APL après</t>
+  </si>
+  <si>
+    <t>Moyenne de la quittance avant</t>
+  </si>
+  <si>
+    <t>Moyenne de la quittance après</t>
+  </si>
+  <si>
+    <t>Nombre de ménages par tranche de taux d'effort</t>
+  </si>
+  <si>
+    <t>Nombre de ménages (matrice de transition du taux d'effort)</t>
+  </si>
+  <si>
+    <t>Nombre de ménages (matrice d'équilibre surface / reste à charge)</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages (matrices des déterminants du taux d'effort)</t>
+  </si>
+  <si>
+    <t>Position taux d'effort (diagonale)</t>
+  </si>
+  <si>
+    <t>Reste à charge mensuel moyen après relogement : dépense de logement réellement supportée (loyer + charges − APL).</t>
+  </si>
+  <si>
+    <t>Reste à charge mensuel moyen avant relogement : loyer + charges − APL du logement d'origine. Champ matérialisé dans le fait (CCD resteAChargeActuel).</t>
+  </si>
+  <si>
+    <t>Taux d'effort moyen avant relogement : part des ressources consacrée à la dépense de logement.</t>
+  </si>
+  <si>
+    <t>Taux d'effort moyen après relogement.</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le taux d'effort après relogement est supérieur ou égal à 30 %.</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le taux d'effort augmente de plus de 2,5 points après relogement (tranches « +2,5 à +15 pts » et « &gt; +15 pts »).</t>
+  </si>
+  <si>
+    <t>Loyer de base mensuel moyen avant relogement.</t>
+  </si>
+  <si>
+    <t>Loyer mensuel moyen inscrit au bail après relogement.</t>
+  </si>
+  <si>
+    <t>Charges mensuelles moyennes avant relogement (provisions individuelles + collectives).</t>
+  </si>
+  <si>
+    <t>Charges mensuelles moyennes après relogement (provisions individuelles + collectives).</t>
+  </si>
+  <si>
+    <t>APL mensuelle moyenne avant relogement (APL réelle).</t>
+  </si>
+  <si>
+    <t>APL mensuelle moyenne après relogement (APL simulée).</t>
+  </si>
+  <si>
+    <t>Quittance mensuelle moyenne avant relogement (loyer + charges).</t>
+  </si>
+  <si>
+    <t>Quittance mensuelle moyenne après relogement.</t>
+  </si>
+  <si>
+    <t>Répartition des ménages par tranche de taux d'effort, avant et après relogement.</t>
+  </si>
+  <si>
+    <t>Nombre de ménages pour chaque combinaison tranche de taux d'effort avant × après ; met en évidence améliorations et dégradations.</t>
+  </si>
+  <si>
+    <t>Nombre de ménages pour chaque combinaison évolution de la surface (%) × évolution du reste à charge (%).</t>
+  </si>
+  <si>
+    <t>Répartition (%) des ménages par modalité d'un facteur (typologie, financement, âge du bâti, nature de logement, QPV, localisation) croisée avec l'évolution du taux d'effort.</t>
+  </si>
+  <si>
+    <t>Qualifie, pour un couple de tranches de taux d'effort avant / après, le sens de l'évolution : dégradation, stabilité ou amélioration. Sert à colorer la matrice de transition.</t>
+  </si>
+  <si>
+    <t>Impact financier</t>
+  </si>
+  <si>
+    <t>Nombre de ménages relogés chez le même bailleur</t>
+  </si>
+  <si>
+    <t>Nombre de ménages relogés chez un autre bailleur</t>
+  </si>
+  <si>
+    <t>Nouveau logement</t>
+  </si>
+  <si>
+    <t>Ménages relogés par leur bailleur d'origine.</t>
+  </si>
+  <si>
+    <t>Ménages relogés par un bailleur différent de leur bailleur d'origine.</t>
+  </si>
+  <si>
+    <t>Sous-theme</t>
+  </si>
+  <si>
+    <t>Dossier supplémentaire</t>
+  </si>
+  <si>
+    <t>Taux d'effort</t>
+  </si>
+  <si>
+    <t>Reste à charge</t>
+  </si>
+  <si>
+    <t>ANRU / NPNRU</t>
+  </si>
+  <si>
+    <t>Décohabitation</t>
+  </si>
+  <si>
+    <t>QPV</t>
+  </si>
+  <si>
+    <t>Regroupement</t>
+  </si>
+  <si>
+    <t>Dossier rattaché à un dossier principal, créé pour les personnes hébergées ou les décohabitants du ménage.</t>
+  </si>
+  <si>
+    <t>Part des ressources du ménage consacrée à la dépense de logement (quittance nette d'APL rapportée aux ressources).</t>
+  </si>
+  <si>
+    <t>Dépense de logement réellement supportée par le ménage après déduction de l'APL.</t>
+  </si>
+  <si>
+    <t>Opération relevant du Nouveau Programme National de Renouvellement Urbain.</t>
+  </si>
+  <si>
+    <t>Départ d'un membre du foyer vers un logement autonome.</t>
+  </si>
+  <si>
+    <t>Quartier prioritaire de la politique de la ville.</t>
+  </si>
+  <si>
+    <t>Ensemble d'opérations regroupées définissant un périmètre d'accès et d'analyse — base de la sécurité au niveau ligne (RLS).</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1390,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1060,6 +1407,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1395,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="31.86328125" customWidth="1"/>
@@ -1416,7 +1766,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>4</v>
@@ -1451,10 +1801,10 @@
     </row>
     <row r="3" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>8</v>
@@ -1489,7 +1839,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>15</v>
@@ -1512,11 +1862,14 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1529,16 +1882,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="31.1328125" customWidth="1"/>
     <col min="2" max="2" width="65.59765625" customWidth="1"/>
     <col min="3" max="3" width="73.59765625" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1548,8 +1901,11 @@
       <c r="C1" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D1" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1559,8 +1915,9 @@
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1570,8 +1927,9 @@
       <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1581,8 +1939,9 @@
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1592,8 +1951,9 @@
       <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -1603,8 +1963,9 @@
       <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1614,8 +1975,9 @@
       <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1625,8 +1987,9 @@
       <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -1636,8 +1999,9 @@
       <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1647,8 +2011,9 @@
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1658,8 +2023,9 @@
       <c r="C11" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -1669,8 +2035,9 @@
       <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -1680,8 +2047,9 @@
       <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -1691,8 +2059,9 @@
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -1702,8 +2071,9 @@
       <c r="C15" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -1713,8 +2083,9 @@
       <c r="C16" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -1724,10 +2095,11 @@
       <c r="C17" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>52</v>
@@ -1735,10 +2107,11 @@
       <c r="C18" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>54</v>
@@ -1746,10 +2119,11 @@
       <c r="C19" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>56</v>
@@ -1757,10 +2131,11 @@
       <c r="C20" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>58</v>
@@ -1768,10 +2143,11 @@
       <c r="C21" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>60</v>
@@ -1779,10 +2155,11 @@
       <c r="C22" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>62</v>
@@ -1790,10 +2167,11 @@
       <c r="C23" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>64</v>
@@ -1801,10 +2179,11 @@
       <c r="C24" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>66</v>
@@ -1812,10 +2191,11 @@
       <c r="C25" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>68</v>
@@ -1823,13 +2203,14 @@
       <c r="C26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G26" t="s">
+      <c r="D26" s="1"/>
+      <c r="F26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>71</v>
@@ -1837,10 +2218,11 @@
       <c r="C27" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>73</v>
@@ -1848,10 +2230,11 @@
       <c r="C28" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>75</v>
@@ -1859,10 +2242,11 @@
       <c r="C29" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>77</v>
@@ -1870,10 +2254,11 @@
       <c r="C30" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>79</v>
@@ -1881,10 +2266,11 @@
       <c r="C31" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>81</v>
@@ -1892,10 +2278,11 @@
       <c r="C32" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>83</v>
@@ -1903,10 +2290,11 @@
       <c r="C33" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>85</v>
@@ -1914,10 +2302,11 @@
       <c r="C34" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>87</v>
@@ -1925,10 +2314,11 @@
       <c r="C35" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>89</v>
@@ -1936,10 +2326,11 @@
       <c r="C36" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>91</v>
@@ -1947,8 +2338,9 @@
       <c r="C37" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>13</v>
       </c>
@@ -1958,8 +2350,9 @@
       <c r="C38" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>13</v>
       </c>
@@ -1969,8 +2362,9 @@
       <c r="C39" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
@@ -1980,8 +2374,9 @@
       <c r="C40" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>13</v>
       </c>
@@ -1991,8 +2386,9 @@
       <c r="C41" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
@@ -2002,8 +2398,9 @@
       <c r="C42" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>13</v>
       </c>
@@ -2013,8 +2410,9 @@
       <c r="C43" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>13</v>
       </c>
@@ -2024,8 +2422,9 @@
       <c r="C44" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>13</v>
       </c>
@@ -2035,8 +2434,9 @@
       <c r="C45" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>13</v>
       </c>
@@ -2046,8 +2446,9 @@
       <c r="C46" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>13</v>
       </c>
@@ -2057,8 +2458,9 @@
       <c r="C47" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>13</v>
       </c>
@@ -2068,8 +2470,9 @@
       <c r="C48" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>13</v>
       </c>
@@ -2079,8 +2482,9 @@
       <c r="C49" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>13</v>
       </c>
@@ -2090,8 +2494,9 @@
       <c r="C50" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>13</v>
       </c>
@@ -2101,8 +2506,9 @@
       <c r="C51" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>13</v>
       </c>
@@ -2112,8 +2518,9 @@
       <c r="C52" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>13</v>
       </c>
@@ -2123,8 +2530,9 @@
       <c r="C53" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>13</v>
       </c>
@@ -2134,8 +2542,9 @@
       <c r="C54" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>13</v>
       </c>
@@ -2145,8 +2554,9 @@
       <c r="C55" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D55" s="1"/>
+    </row>
+    <row r="56" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
         <v>13</v>
       </c>
@@ -2156,8 +2566,9 @@
       <c r="C56" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D56" s="1"/>
+    </row>
+    <row r="57" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
         <v>16</v>
       </c>
@@ -2167,8 +2578,9 @@
       <c r="C57" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D57" s="1"/>
+    </row>
+    <row r="58" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>16</v>
       </c>
@@ -2178,8 +2590,9 @@
       <c r="C58" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
         <v>16</v>
       </c>
@@ -2189,8 +2602,9 @@
       <c r="C59" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
         <v>16</v>
       </c>
@@ -2200,8 +2614,9 @@
       <c r="C60" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
         <v>16</v>
       </c>
@@ -2211,8 +2626,9 @@
       <c r="C61" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
         <v>16</v>
       </c>
@@ -2222,8 +2638,9 @@
       <c r="C62" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
         <v>16</v>
       </c>
@@ -2233,8 +2650,9 @@
       <c r="C63" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D63" s="1"/>
+    </row>
+    <row r="64" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
         <v>16</v>
       </c>
@@ -2244,8 +2662,9 @@
       <c r="C64" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D64" s="1"/>
+    </row>
+    <row r="65" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>16</v>
       </c>
@@ -2255,8 +2674,9 @@
       <c r="C65" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D65" s="1"/>
+    </row>
+    <row r="66" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2266,8 +2686,9 @@
       <c r="C66" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D66" s="1"/>
+    </row>
+    <row r="67" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
         <v>16</v>
       </c>
@@ -2277,8 +2698,9 @@
       <c r="C67" s="2" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D67" s="1"/>
+    </row>
+    <row r="68" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
         <v>16</v>
       </c>
@@ -2288,8 +2710,9 @@
       <c r="C68" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D68" s="1"/>
+    </row>
+    <row r="69" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>16</v>
       </c>
@@ -2299,8 +2722,9 @@
       <c r="C69" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D69" s="1"/>
+    </row>
+    <row r="70" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
         <v>16</v>
       </c>
@@ -2310,8 +2734,9 @@
       <c r="C70" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="D70" s="1"/>
+    </row>
+    <row r="71" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
         <v>16</v>
       </c>
@@ -2321,8 +2746,9 @@
       <c r="C71" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
         <v>16</v>
       </c>
@@ -2332,8 +2758,9 @@
       <c r="C72" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D72" s="1"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
         <v>16</v>
       </c>
@@ -2342,6 +2769,665 @@
       </c>
       <c r="C73" s="2" t="s">
         <v>164</v>
+      </c>
+      <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A85" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A86" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A87" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A88" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A90" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A91" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A96" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A97" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A98" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A99" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A100" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A101" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A102" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A107" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A108" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A109" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A110" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A111" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A112" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A113" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A114" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A115" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A116" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A117" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A118" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A119" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A120" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -2351,12 +3437,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23.73046875" customWidth="1"/>
     <col min="2" max="2" width="33.59765625" customWidth="1"/>
-    <col min="3" max="3" width="34.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="53.265625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2500,7 +3586,7 @@
     </row>
     <row r="11" spans="1:5" ht="187.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>193</v>
@@ -2512,187 +3598,187 @@
         <v>195</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>196</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="270.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="285" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="242.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="171" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
@@ -2700,13 +3786,13 @@
         <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
@@ -2714,13 +3800,13 @@
         <v>13</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
@@ -2728,13 +3814,13 @@
         <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="57" x14ac:dyDescent="0.45">
@@ -2745,10 +3831,10 @@
         <v>175</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
@@ -2756,13 +3842,13 @@
         <v>13</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="57" x14ac:dyDescent="0.45">
@@ -2770,13 +3856,13 @@
         <v>13</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
@@ -2784,13 +3870,13 @@
         <v>16</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
@@ -2798,13 +3884,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
@@ -2812,13 +3898,13 @@
         <v>16</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
@@ -2826,13 +3912,13 @@
         <v>16</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="57" x14ac:dyDescent="0.45">
@@ -2843,10 +3929,10 @@
         <v>175</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
@@ -2854,14 +3940,110 @@
         <v>16</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>247</v>
-      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="12"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2869,18 +4051,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3184,21 +4360,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3223,9 +4402,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1D909FE-12AE-473A-9C2A-A5C4731ACEF4}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11748F16-358C-47F5-A8EE-8BAE976A6AA1}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="468">
   <si>
     <t>Theme</t>
   </si>
@@ -59,15 +59,6 @@
   </si>
   <si>
     <t>Parc social</t>
-  </si>
-  <si>
-    <t>Portrait du parc social à partir des données du Répertoire du Parc Locatif des bailleurs Sociaux (RPLS) au 1er janvier
-L’objectif est de présenter, pour chaque territoire, une synthèse de l’évolution récente du parc, sa
-répartition selon des catégories habituellement utilisées (type de financement, origine, nombre de
-pièces, localisation en QPV...) ainsi qu’un comparatif des indicateurs clés (rotation, vacance,
-surface et loyer…) par catégorie.
-Seuls les logements locatifs ordinaires sont recensés, les logements foyers ne sont
-donc pas compris dans les résultats. Par ailleurs, les informations présentées portent sur le parc locatif social, au sens strict, et n’intègrent donc pas les logements nonconventionnés des SEM de France métropolitaine</t>
   </si>
   <si>
     <t>support.data@union-habitat.org</t>
@@ -1306,6 +1297,305 @@
   </si>
   <si>
     <t>Ensemble d'opérations regroupées définissant un périmètre d'accès et d'analyse — base de la sécurité au niveau ligne (RLS).</t>
+  </si>
+  <si>
+    <t>Occupation</t>
+  </si>
+  <si>
+    <t>Portrait du parc social à partir des données du Répertoire du Parc Locatif des bailleurs Sociaux (RPLS) au 1er janvier
+L’objectif est de présenter, pour chaque territoire, une synthèse de l’évolution récente du parc, sa
+répartition selon des catégories habituellement utilisées (type de financement, origine, nombre de
+pièces, localisation en QPV...) ainsi qu’un comparatif des indicateurs clés (rotation, vacance,
+surface et loyer…) par catégorie.
+Seuls les logements locatifs ordinaires sont recensés, les logements foyers ne sont
+donc pas compris dans les résultats. Par ailleurs, les informations présentées portent sur le parc locatif social, au sens strict, et n’intègrent donc pas les logements non conventionnés des SEM de France métropolitaine</t>
+  </si>
+  <si>
+    <t>Le rapport sur l’occupation des logements sociaux est élaboré à partir des données issues de l’enquête OPS (Occupation du Parc Social). Réalisée tous les deux ans, cette enquête est menée auprès des organismes d’habitations à loyer modéré (HLM), des sociétés d’économie mixte (SEM) agréées pour le logement social, des administrations publiques, des organismes agréés pour le logement des personnes défavorisées, ainsi que des autres personnes morales propriétaires de logements locatifs sociaux.
+Ce rapport a pour objectif de dresser une synthèse de l’occupation du parc locatif social et de contribuer à une meilleure connaissance des caractéristiques socio-économiques des ménages locataires de logements sociaux.</t>
+  </si>
+  <si>
+    <t>Biennale</t>
+  </si>
+  <si>
+    <t>OPS, INSEE</t>
+  </si>
+  <si>
+    <t>Taux de réponse à l'enquête OPS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages répondants</t>
+  </si>
+  <si>
+    <t>Nombre de ménages non répondants</t>
+  </si>
+  <si>
+    <t>Nombre de logements occupés</t>
+  </si>
+  <si>
+    <t>Part des occupants &gt; 65 ans</t>
+  </si>
+  <si>
+    <t>Part de familles nombreuses</t>
+  </si>
+  <si>
+    <t>Taille moyenne des ménages</t>
+  </si>
+  <si>
+    <t>Part de familles monoparentales</t>
+  </si>
+  <si>
+    <t>Part de personnes seules</t>
+  </si>
+  <si>
+    <t>Part d'occupants majeurs au chômage</t>
+  </si>
+  <si>
+    <t>Part de ménages dont les revenus sont &lt; PLAI</t>
+  </si>
+  <si>
+    <t>Nombre de familles monoparentales</t>
+  </si>
+  <si>
+    <t>Nombre de familles monoparentales avec 1 ou 2 enfants</t>
+  </si>
+  <si>
+    <t>Nombre de familles monoparentales avec 3 enfants ou plus</t>
+  </si>
+  <si>
+    <t>Nombre de couples sans enfant</t>
+  </si>
+  <si>
+    <t>Nombre de couples avec enfant(s)</t>
+  </si>
+  <si>
+    <t>Nombre de couples avec 1 ou 2 enfants</t>
+  </si>
+  <si>
+    <t>Nombre de couples avec 3 enfants ou plus</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants &lt; 18 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants 18-24 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants 25-49 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants 50-64 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants 65-74 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants &gt;75 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants total</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail &lt; 29 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail 30-49 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail 50-64 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail &gt; 65 ans</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont &lt; 40% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont 40-60% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont 60-100% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont 100-130% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont 130-160% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont &gt;160% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de répondants sur les ressources</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs en CDI</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs en CDD</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs au chômage</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs sans emploi</t>
+  </si>
+  <si>
+    <t>Nombre de logements occupés, donnés en gestion ou en location</t>
+  </si>
+  <si>
+    <t>Part des ménages dont les plafonds de ressources sont strictement inférieur à 60% du plafond PLUS parmi les ménages ayant répondu sur les ressources</t>
+  </si>
+  <si>
+    <t>Nombre de ménages composés d'une personne isolée avec au moins un enfant</t>
+  </si>
+  <si>
+    <t>Nombre de ménages composés d'une personne isolée avec 1 ou 2 enfant(s)</t>
+  </si>
+  <si>
+    <t>Nombre de ménages composés d'une personne isolée avec 3 enfant(s) ou plus</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de moins de 18 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 18 à 24 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 25 à 49 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 50 à 64 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 65 à 74 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 75 ans ou plus</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail âgés de moins de 29 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail âgés de 30 à 49 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail âgés de 50 à 64 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail âgés de 65 ans ou plus</t>
+  </si>
+  <si>
+    <t>Nombre de ménages ayant répondu sur les ressources</t>
+  </si>
+  <si>
+    <t>Taux de réponse à l'enquête OPS
+Calcul: Nombre de ménages répondants / Nombre de logements occupés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de ménages ayant répondu à l'enquête  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de ménages n'ayant pas répondu à l'enquête  </t>
+  </si>
+  <si>
+    <t>Nombre d'occupants répondants</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants parmi les ménages ayant répondu à l'enquête</t>
+  </si>
+  <si>
+    <t>Part d'occupants de 65 ans et plus parmi les occupants ayant répondu à l'enquête
+Calcul: Nombre d'occupants de 65 ans et plus / Nombre d'occupants répondants</t>
+  </si>
+  <si>
+    <t>Part de familles nombreuses (3 enfants ou plus) parmi les ménages ayant répondu sur la composition familiale
+Calcul: (Nombre de familles monoparentales avec 3 enfants ou plus + Nombre de couples avec 3 enfants ou plus) / Nombre de ménages répondants sur la composition familiale</t>
+  </si>
+  <si>
+    <t>Taille moyenne des ménages
+Calcul: Nombre d'occupants répondants / Nombre de ménages répondants</t>
+  </si>
+  <si>
+    <t>Part de familles monoparentales parmi les ménages ayant répondu sur la composition familiale
+Calcul: Nombre de familles monoparentales / Nombre de ménages répondants sur la compositon familiale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part de personnes seules parmi les ménages ayant répondu sur la composition familiale
+Calcul: Nombre de personnes seules /   Nombre de ménages répondants sur la compositon familiale
+</t>
+  </si>
+  <si>
+    <t>Part d'occupants majeurs au chômage parmi les occupants majeurs ayant répondu sur la situation professionnelle</t>
+  </si>
+  <si>
+    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) sans enfant</t>
+  </si>
+  <si>
+    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec enfant(s)</t>
+  </si>
+  <si>
+    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec 1 ou 2 enfant(s)</t>
+  </si>
+  <si>
+    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec 3 enfant(s) ou plus</t>
+  </si>
+  <si>
+    <t>Nombre de nouveaux locataires du parc social qui ont emménagé depuis moins de 2 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs au chômage (personne en recherche d’emploi)</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs sans emploi: foyer, retraités, pré-retraités, en invalidité, au foyer, étudiants, etc.</t>
+  </si>
+  <si>
+    <t>Emménagés récents</t>
+  </si>
+  <si>
+    <t>Ensemble des ménages</t>
+  </si>
+  <si>
+    <t>Les données représentent l’ensemble des ménages du parc social ayant répondu à l’enquête</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de ménages composés d'une personne isolée majeure sans enfant </t>
+  </si>
+  <si>
+    <t>QPV/Hors QPV</t>
+  </si>
+  <si>
+    <t>Année</t>
+  </si>
+  <si>
+    <t>Echelle géographique</t>
+  </si>
+  <si>
+    <t>Filtre obligatoire: REGION, DEPARTEMENT ou COMMUNE</t>
+  </si>
+  <si>
+    <t>Région/Département/Commune</t>
+  </si>
+  <si>
+    <t>Sélection du ou des territoires à afficher</t>
+  </si>
+  <si>
+    <t>Filtre obligatoire: TOUS, QPV, HQPV</t>
+  </si>
+  <si>
+    <t>Echelle géographique affiché. Met à jour le champ Région/Département/Commune en fonction de la sélection</t>
+  </si>
+  <si>
+    <t>Nombre de ménages ayant répondu à l'enquête</t>
+  </si>
+  <si>
+    <t>Nombre de ménages ayant emmenagés récemment</t>
+  </si>
+  <si>
+    <t>Année de l'enquête.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Les enquêtes OPS ont lieu tous les 2 ans. </t>
   </si>
 </sst>
 </file>
@@ -1407,9 +1697,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1766,7 +2060,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>4</v>
@@ -1781,95 +2075,115 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E4" s="1">
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="10"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="E6" s="11">
+        <v>5</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1882,7 +2196,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="31.1328125" customWidth="1"/>
@@ -1896,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1910,10 +2224,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -1922,10 +2236,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -1934,10 +2248,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -1946,10 +2260,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D5" s="1"/>
     </row>
@@ -1958,10 +2272,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -1970,10 +2284,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -1982,10 +2296,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D8" s="1"/>
     </row>
@@ -1994,10 +2308,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -2006,10 +2320,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D10" s="1"/>
     </row>
@@ -2018,10 +2332,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -2030,10 +2344,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D12" s="1"/>
     </row>
@@ -2042,10 +2356,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -2054,10 +2368,10 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D14" s="1"/>
     </row>
@@ -2066,10 +2380,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -2078,10 +2392,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D16" s="1"/>
     </row>
@@ -2090,1345 +2404,1861 @@
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="D24" s="1"/>
     </row>
     <row r="25" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D26" s="1"/>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D28" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="D31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="D32" s="1"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D33" s="1"/>
     </row>
     <row r="34" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D36" s="1"/>
     </row>
     <row r="37" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="D37" s="1"/>
     </row>
     <row r="38" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="D38" s="1"/>
     </row>
     <row r="39" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D39" s="1"/>
     </row>
     <row r="40" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="D42" s="1"/>
     </row>
     <row r="43" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="D43" s="1"/>
     </row>
     <row r="44" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D44" s="1"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D45" s="1"/>
     </row>
     <row r="46" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="D46" s="1"/>
     </row>
     <row r="47" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="D47" s="1"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="D48" s="1"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="D49" s="1"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="D50" s="1"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="D52" s="1"/>
     </row>
     <row r="53" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="D53" s="1"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="D54" s="1"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="D55" s="1"/>
     </row>
     <row r="56" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="D56" s="1"/>
     </row>
     <row r="57" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="D57" s="1"/>
     </row>
     <row r="58" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="D58" s="1"/>
     </row>
     <row r="59" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="D59" s="1"/>
     </row>
     <row r="60" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="D60" s="1"/>
     </row>
     <row r="61" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D61" s="1"/>
     </row>
     <row r="62" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="D62" s="1"/>
     </row>
     <row r="63" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D63" s="1"/>
     </row>
     <row r="64" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="D64" s="1"/>
     </row>
     <row r="65" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="D65" s="1"/>
     </row>
     <row r="66" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="D66" s="1"/>
     </row>
     <row r="67" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D67" s="1"/>
     </row>
     <row r="68" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="D68" s="1"/>
     </row>
     <row r="69" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="D69" s="1"/>
     </row>
     <row r="70" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="D70" s="1"/>
     </row>
     <row r="71" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D71" s="1"/>
     </row>
     <row r="72" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="D72" s="1"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="D73" s="1"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="D75" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A76" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B76" s="1" t="s">
+      <c r="D76" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A77" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B77" s="1" t="s">
+      <c r="D77" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A78" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B78" s="1" t="s">
+      <c r="D78" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A79" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B79" s="1" t="s">
+      <c r="D79" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A80" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B80" s="1" t="s">
+      <c r="D80" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A81" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B81" s="1" t="s">
+      <c r="D81" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A82" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B82" s="1" t="s">
+      <c r="D82" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A83" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B83" s="1" t="s">
+      <c r="D83" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A84" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>280</v>
-      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A85" s="11" t="s">
-        <v>257</v>
+      <c r="A85" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A86" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A86" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B86" s="1" t="s">
+      <c r="D86" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A87" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A87" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B87" s="1" t="s">
+      <c r="D87" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A88" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A88" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B88" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C88" s="1" t="s">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A89" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A90" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A90" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B90" s="1" t="s">
+      <c r="D90" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A91" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A91" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B91" s="1" t="s">
+      <c r="D91" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A92" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B92" s="1" t="s">
+      <c r="D92" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A93" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B93" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C93" s="1" t="s">
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A94" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D95" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A96" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A97" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A98" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A99" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A100" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A95" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A96" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A97" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A98" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A99" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A100" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A101" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D101" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A102" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A107" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A108" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A109" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A110" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A111" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A112" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A113" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A114" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A116" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A117" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A118" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A119" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A101" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A102" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A103" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A104" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A105" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A106" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A107" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A108" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A109" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A110" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A111" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A112" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A113" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A114" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A115" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A116" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A117" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A118" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A119" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A120" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A120" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>356</v>
-      </c>
+    </row>
+    <row r="121" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A121" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D121" s="1"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A122" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D122" s="1"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A123" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D123" s="1"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A124" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="D124" s="1"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A125" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D125" s="1"/>
+    </row>
+    <row r="126" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A126" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D126" s="1"/>
+    </row>
+    <row r="127" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A127" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D127" s="1"/>
+    </row>
+    <row r="128" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A128" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="D128" s="1"/>
+    </row>
+    <row r="129" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A129" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D129" s="1"/>
+    </row>
+    <row r="130" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A130" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D130" s="1"/>
+    </row>
+    <row r="131" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A131" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D131" s="1"/>
+    </row>
+    <row r="132" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A132" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D132" s="1"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A133" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D133" s="1"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A134" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D134" s="1"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A135" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D135" s="1"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A136" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D136" s="1"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A137" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D137" s="1"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A138" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D138" s="1"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A139" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D139" s="1"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A140" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D140" s="1"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A141" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D141" s="1"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A142" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D142" s="1"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A143" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D143" s="1"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A144" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D144" s="1"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A145" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D145" s="1"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A146" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D146" s="1"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A147" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D147" s="1"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A148" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D148" s="1"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A149" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D149" s="1"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A150" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D150" s="1"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A151" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D151" s="1"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A152" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D152" s="1"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A153" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D153" s="1"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A154" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D154" s="1"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A155" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D155" s="1"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A156" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D156" s="1"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A157" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D157" s="1"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A158" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D158" s="1"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A159" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D159" s="1"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A160" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D160" s="1"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A161" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D161" s="1"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A162" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D162" s="1"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A163" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D163" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3437,7 +4267,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23.73046875" customWidth="1"/>
@@ -3451,13 +4281,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3465,13 +4295,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3479,10 +4309,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -3491,13 +4321,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="114" customHeight="1" x14ac:dyDescent="0.45">
@@ -3505,13 +4335,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="128.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3519,13 +4349,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
@@ -3533,13 +4363,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -3547,13 +4377,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -3561,13 +4391,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
@@ -3575,475 +4405,545 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="187.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="270.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="285" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="242.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="171" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D37" s="1"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D38" s="1"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D39" s="1"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D42" s="1"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A44" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="D43" s="1"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
+      <c r="B44" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+      <c r="A45" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>467</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4051,12 +4951,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4360,24 +5266,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4402,12 +5305,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11748F16-358C-47F5-A8EE-8BAE976A6AA1}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81495B1D-5412-48DC-9B86-D14AFAC97FF6}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="499">
   <si>
     <t>Theme</t>
   </si>
@@ -1596,6 +1596,99 @@
   </si>
   <si>
     <t xml:space="preserve"> Les enquêtes OPS ont lieu tous les 2 ans. </t>
+  </si>
+  <si>
+    <t>Réhabilitations et démolitions</t>
+  </si>
+  <si>
+    <t>Le rapport sur les réhabilitations et les démolitions est élaboré à partir des données issues de l'Observatoire de la Production Locative (OPL), et concerne les ordres de service lancés. Il a pour objectif de présenter l'évolution du nombre de logements ayant fait l'objet de travaux d'amélioration énergétique, en mettant en valeur ceux ayant connu un changement d'étiquette énergétique, ainsi que les passoires thermiques. Il permet également de suivre l'évolution des démolitions, qu'elles soient ANRU ou hors ANRU.</t>
+  </si>
+  <si>
+    <t>OPL, INSEE</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique (lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de démolitions total</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont changement d'etiquette </t>
+  </si>
+  <si>
+    <t>dont changement d'etiquette (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>dont traitement des passoires thermiques F et G (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>dont traitement des passoires thermiques E (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>dont traitement des passoires thermiques F (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>dont traitement des passoires thermiques G (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de démolitions ANRU (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de démolitions Hors ANRU (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de démolitions total (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Changement de vecteur energetique</t>
+  </si>
+  <si>
+    <t>Rénovation énergétique lourde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont traitement des passoires thermiques F et G </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont traitement des passoires thermiques E </t>
+  </si>
+  <si>
+    <t>dont traitement des passoires thermiques F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont traitement des passoires thermiques G </t>
+  </si>
+  <si>
+    <t>Démolitions ANRU</t>
+  </si>
+  <si>
+    <t>Démolitions hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de logements avec rénovation energétique lourde (ordres de service lancés). La rénovation énergétique est dîte "lourde" si le coût des travaux est supérieur à 50k€ par logement</t>
+  </si>
+  <si>
+    <t>Nombre de logements avec changement de vecteur energetique (ordres de service lancés).Il s'agit du nombre de logements ayant fait l'objet d'une modification du mode de chauffage et de production d'eau chaude sanitaire par l'installation de dispositifs fonctionnant majoritairement à l'aide d'énergies renouvelables.</t>
+  </si>
+  <si>
+    <t>Régions actuelles</t>
+  </si>
+  <si>
+    <t>Régions anciennes</t>
+  </si>
+  <si>
+    <t>Découpage des régions tel que défini depuis 1er janvier 2026</t>
+  </si>
+  <si>
+    <t>Découpage des régions avant le 1er janvier 2016</t>
+  </si>
+  <si>
+    <t>Depuis le 1er janvier 2016, on observe un total de 18 régions, dont 13 en France Métropolitaine</t>
+  </si>
+  <si>
+    <t>Avant le 1er janvier 2016, la France comptait 27 régions, dont 22 en France Métropolitaine</t>
   </si>
 </sst>
 </file>
@@ -1697,11 +1790,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2039,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="31.86328125" customWidth="1"/>
@@ -2166,22 +2259,45 @@
       <c r="A6" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="2" t="s">
         <v>375</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="1">
         <v>5</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="1" t="s">
         <v>377</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+      <c r="A7" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2196,7 +2312,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="31.1328125" customWidth="1"/>
@@ -3745,7 +3861,7 @@
       </c>
     </row>
     <row r="121" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A121" s="11" t="s">
+      <c r="A121" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B121" s="6" t="s">
@@ -3757,7 +3873,7 @@
       <c r="D121" s="1"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A122" s="11" t="s">
+      <c r="A122" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B122" s="6" t="s">
@@ -3769,7 +3885,7 @@
       <c r="D122" s="1"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A123" s="11" t="s">
+      <c r="A123" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B123" s="6" t="s">
@@ -3781,7 +3897,7 @@
       <c r="D123" s="1"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A124" s="11" t="s">
+      <c r="A124" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B124" s="6" t="s">
@@ -3793,7 +3909,7 @@
       <c r="D124" s="1"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A125" s="11" t="s">
+      <c r="A125" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -3805,7 +3921,7 @@
       <c r="D125" s="1"/>
     </row>
     <row r="126" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A126" s="11" t="s">
+      <c r="A126" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -3817,7 +3933,7 @@
       <c r="D126" s="1"/>
     </row>
     <row r="127" spans="1:4" ht="57" x14ac:dyDescent="0.45">
-      <c r="A127" s="11" t="s">
+      <c r="A127" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -3829,19 +3945,19 @@
       <c r="D127" s="1"/>
     </row>
     <row r="128" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A128" s="11" t="s">
+      <c r="A128" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="C128" s="12" t="s">
+      <c r="C128" s="10" t="s">
         <v>441</v>
       </c>
       <c r="D128" s="1"/>
     </row>
     <row r="129" spans="1:4" ht="57" x14ac:dyDescent="0.45">
-      <c r="A129" s="11" t="s">
+      <c r="A129" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -3853,7 +3969,7 @@
       <c r="D129" s="1"/>
     </row>
     <row r="130" spans="1:4" ht="57" x14ac:dyDescent="0.45">
-      <c r="A130" s="11" t="s">
+      <c r="A130" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -3865,7 +3981,7 @@
       <c r="D130" s="1"/>
     </row>
     <row r="131" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A131" s="11" t="s">
+      <c r="A131" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -3877,7 +3993,7 @@
       <c r="D131" s="1"/>
     </row>
     <row r="132" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A132" s="11" t="s">
+      <c r="A132" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -3889,7 +4005,7 @@
       <c r="D132" s="1"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A133" s="11" t="s">
+      <c r="A133" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -3901,7 +4017,7 @@
       <c r="D133" s="1"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A134" s="11" t="s">
+      <c r="A134" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -3913,7 +4029,7 @@
       <c r="D134" s="1"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A135" s="11" t="s">
+      <c r="A135" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -3925,7 +4041,7 @@
       <c r="D135" s="1"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A136" s="11" t="s">
+      <c r="A136" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B136" s="1" t="s">
@@ -3937,7 +4053,7 @@
       <c r="D136" s="1"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A137" s="11" t="s">
+      <c r="A137" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -3949,7 +4065,7 @@
       <c r="D137" s="1"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A138" s="11" t="s">
+      <c r="A138" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -3961,7 +4077,7 @@
       <c r="D138" s="1"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A139" s="11" t="s">
+      <c r="A139" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B139" s="1" t="s">
@@ -3973,7 +4089,7 @@
       <c r="D139" s="1"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A140" s="11" t="s">
+      <c r="A140" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -3985,7 +4101,7 @@
       <c r="D140" s="1"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A141" s="11" t="s">
+      <c r="A141" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B141" s="1" t="s">
@@ -3997,7 +4113,7 @@
       <c r="D141" s="1"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A142" s="11" t="s">
+      <c r="A142" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B142" s="1" t="s">
@@ -4009,7 +4125,7 @@
       <c r="D142" s="1"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A143" s="11" t="s">
+      <c r="A143" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B143" s="1" t="s">
@@ -4021,7 +4137,7 @@
       <c r="D143" s="1"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A144" s="11" t="s">
+      <c r="A144" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B144" s="1" t="s">
@@ -4033,7 +4149,7 @@
       <c r="D144" s="1"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A145" s="11" t="s">
+      <c r="A145" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B145" s="1" t="s">
@@ -4045,7 +4161,7 @@
       <c r="D145" s="1"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A146" s="11" t="s">
+      <c r="A146" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B146" s="1" t="s">
@@ -4057,7 +4173,7 @@
       <c r="D146" s="1"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A147" s="11" t="s">
+      <c r="A147" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B147" s="1" t="s">
@@ -4069,7 +4185,7 @@
       <c r="D147" s="1"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A148" s="11" t="s">
+      <c r="A148" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B148" s="1" t="s">
@@ -4081,7 +4197,7 @@
       <c r="D148" s="1"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A149" s="11" t="s">
+      <c r="A149" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B149" s="1" t="s">
@@ -4093,7 +4209,7 @@
       <c r="D149" s="1"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A150" s="11" t="s">
+      <c r="A150" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B150" s="1" t="s">
@@ -4105,7 +4221,7 @@
       <c r="D150" s="1"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A151" s="11" t="s">
+      <c r="A151" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B151" s="1" t="s">
@@ -4117,7 +4233,7 @@
       <c r="D151" s="1"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A152" s="11" t="s">
+      <c r="A152" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B152" s="1" t="s">
@@ -4129,7 +4245,7 @@
       <c r="D152" s="1"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A153" s="11" t="s">
+      <c r="A153" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B153" s="1" t="s">
@@ -4141,7 +4257,7 @@
       <c r="D153" s="1"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A154" s="11" t="s">
+      <c r="A154" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B154" s="1" t="s">
@@ -4153,7 +4269,7 @@
       <c r="D154" s="1"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A155" s="11" t="s">
+      <c r="A155" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B155" s="1" t="s">
@@ -4165,7 +4281,7 @@
       <c r="D155" s="1"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A156" s="11" t="s">
+      <c r="A156" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B156" s="1" t="s">
@@ -4177,7 +4293,7 @@
       <c r="D156" s="1"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A157" s="11" t="s">
+      <c r="A157" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B157" s="1" t="s">
@@ -4189,7 +4305,7 @@
       <c r="D157" s="1"/>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A158" s="11" t="s">
+      <c r="A158" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -4201,7 +4317,7 @@
       <c r="D158" s="1"/>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -4213,52 +4329,184 @@
       <c r="D159" s="1"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A160" s="11" t="s">
+      <c r="A160" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C160" s="2" t="s">
         <v>415</v>
       </c>
       <c r="D160" s="1"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="C161" s="2" t="s">
         <v>450</v>
       </c>
       <c r="D161" s="1"/>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A162" s="11" t="s">
+    <row r="162" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A162" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="C162" s="2" t="s">
         <v>451</v>
       </c>
       <c r="D162" s="1"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A163" s="11" t="s">
+      <c r="A163" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C163" s="2" t="s">
         <v>449</v>
       </c>
       <c r="D163" s="1"/>
+    </row>
+    <row r="164" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A164" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D164" s="1"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A165" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D165" s="1"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A166" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D166" s="1"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A167" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D167" s="1"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A168" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D168" s="1"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A169" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D169" s="1"/>
+    </row>
+    <row r="170" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A170" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D170" s="1"/>
+    </row>
+    <row r="171" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A171" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D171" s="1"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A172" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D172" s="1"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A173" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D173" s="1"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A174" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D174" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4267,7 +4515,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23.73046875" customWidth="1"/>
@@ -4864,7 +5112,7 @@
       <c r="D43" s="1"/>
     </row>
     <row r="44" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -4878,7 +5126,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -4892,7 +5140,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -4906,7 +5154,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -4920,7 +5168,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -4932,7 +5180,7 @@
       <c r="D48" s="1"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -4941,8 +5189,36 @@
       <c r="C49" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="2" t="s">
         <v>467</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A50" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A51" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -4951,18 +5227,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5266,21 +5536,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5305,9 +5578,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81495B1D-5412-48DC-9B86-D14AFAC97FF6}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1986A7E2-1A00-4994-9DE8-7388336EEE79}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="3795" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -1616,24 +1616,6 @@
     <t>Nombre de logements bénéficiants de travaux d'amélioration energetique (ordres de service lancés)</t>
   </si>
   <si>
-    <t xml:space="preserve">dont changement d'etiquette </t>
-  </si>
-  <si>
-    <t>dont changement d'etiquette (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>dont traitement des passoires thermiques F et G (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>dont traitement des passoires thermiques E (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>dont traitement des passoires thermiques F (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>dont traitement des passoires thermiques G (ordres de service lancés)</t>
-  </si>
-  <si>
     <t>Nombre de démolitions ANRU (ordres de service lancés)</t>
   </si>
   <si>
@@ -1649,18 +1631,6 @@
     <t>Rénovation énergétique lourde</t>
   </si>
   <si>
-    <t xml:space="preserve">dont traitement des passoires thermiques F et G </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dont traitement des passoires thermiques E </t>
-  </si>
-  <si>
-    <t>dont traitement des passoires thermiques F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dont traitement des passoires thermiques G </t>
-  </si>
-  <si>
     <t>Démolitions ANRU</t>
   </si>
   <si>
@@ -1689,6 +1659,36 @@
   </si>
   <si>
     <t>Avant le 1er janvier 2016, la France comptait 27 régions, dont 22 en France Métropolitaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements dont changement d'etiquette </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques F et G </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques E </t>
+  </si>
+  <si>
+    <t>Nombre de logements dont traitement des passoires thermiques F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques G </t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques F et G (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont changement d'etiquette (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques E (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques F (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques G (ordres de service lancés)</t>
   </si>
 </sst>
 </file>
@@ -1773,7 +1773,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1791,10 +1791,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2279,10 +2275,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="57" x14ac:dyDescent="0.45">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="2" t="s">
         <v>469</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -4377,7 +4373,7 @@
       <c r="D163" s="1"/>
     </row>
     <row r="164" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="1" t="s">
         <v>468</v>
       </c>
       <c r="B164" s="1" t="s">
@@ -4388,123 +4384,123 @@
       </c>
       <c r="D164" s="1"/>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A165" s="11" t="s">
+    <row r="165" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A165" s="1" t="s">
         <v>468</v>
       </c>
       <c r="B165" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D165" s="1"/>
+    </row>
+    <row r="166" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A166" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D166" s="1"/>
+    </row>
+    <row r="167" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A167" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D167" s="1"/>
+    </row>
+    <row r="168" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A168" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D168" s="1"/>
+    </row>
+    <row r="169" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A169" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D169" s="1"/>
+    </row>
+    <row r="170" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A170" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D170" s="1"/>
+    </row>
+    <row r="171" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A171" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D171" s="1"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A172" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="D172" s="1"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A173" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D165" s="1"/>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A166" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D166" s="1"/>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A167" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D167" s="1"/>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A168" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D168" s="1"/>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A169" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D169" s="1"/>
-    </row>
-    <row r="170" spans="1:4" ht="57" x14ac:dyDescent="0.45">
-      <c r="A170" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D170" s="1"/>
-    </row>
-    <row r="171" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A171" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="D171" s="1"/>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A172" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D172" s="1"/>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A173" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="D173" s="1"/>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A174" s="11" t="s">
+      <c r="A174" s="1" t="s">
         <v>468</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>472</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D174" s="1"/>
     </row>
@@ -5194,31 +5190,31 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>493</v>
+      <c r="B50" s="1" t="s">
+        <v>483</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>494</v>
+      <c r="B51" s="1" t="s">
+        <v>484</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -5227,12 +5223,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5536,24 +5538,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5578,12 +5577,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1986A7E2-1A00-4994-9DE8-7388336EEE79}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5810A7F-6033-4BB7-A499-52EE466B5F05}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="3795" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="500">
   <si>
     <t>Theme</t>
   </si>
@@ -1689,6 +1689,9 @@
   </si>
   <si>
     <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques G (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Ordre affichage</t>
   </si>
 </sst>
 </file>
@@ -1773,7 +1776,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1793,6 +1796,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2315,9 +2319,10 @@
     <col min="2" max="2" width="65.59765625" customWidth="1"/>
     <col min="3" max="3" width="73.59765625" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2327,11 +2332,14 @@
       <c r="C1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E1" s="11" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2342,8 +2350,9 @@
         <v>20</v>
       </c>
       <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2354,8 +2363,9 @@
         <v>22</v>
       </c>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2366,8 +2376,9 @@
         <v>24</v>
       </c>
       <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2378,8 +2389,9 @@
         <v>26</v>
       </c>
       <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -2390,8 +2402,9 @@
         <v>28</v>
       </c>
       <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -2402,8 +2415,9 @@
         <v>30</v>
       </c>
       <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2414,8 +2428,9 @@
         <v>32</v>
       </c>
       <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2426,8 +2441,9 @@
         <v>34</v>
       </c>
       <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2438,8 +2454,9 @@
         <v>36</v>
       </c>
       <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -2450,8 +2467,9 @@
         <v>38</v>
       </c>
       <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -2462,8 +2480,9 @@
         <v>40</v>
       </c>
       <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -2474,8 +2493,9 @@
         <v>42</v>
       </c>
       <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -2486,8 +2506,9 @@
         <v>44</v>
       </c>
       <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -2498,8 +2519,9 @@
         <v>46</v>
       </c>
       <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -2510,6 +2532,7 @@
         <v>48</v>
       </c>
       <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
@@ -2522,6 +2545,7 @@
         <v>50</v>
       </c>
       <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
@@ -2534,6 +2558,7 @@
         <v>52</v>
       </c>
       <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
@@ -2546,6 +2571,7 @@
         <v>54</v>
       </c>
       <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
@@ -2558,6 +2584,7 @@
         <v>56</v>
       </c>
       <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
@@ -2570,6 +2597,7 @@
         <v>58</v>
       </c>
       <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
     </row>
     <row r="22" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
@@ -2582,6 +2610,7 @@
         <v>60</v>
       </c>
       <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
@@ -2594,6 +2623,7 @@
         <v>62</v>
       </c>
       <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
@@ -2606,6 +2636,7 @@
         <v>64</v>
       </c>
       <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
@@ -2618,6 +2649,7 @@
         <v>66</v>
       </c>
       <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
     </row>
     <row r="26" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
@@ -2630,6 +2662,7 @@
         <v>68</v>
       </c>
       <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
       <c r="F26" t="s">
         <v>69</v>
       </c>
@@ -2645,6 +2678,7 @@
         <v>71</v>
       </c>
       <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
@@ -2657,6 +2691,7 @@
         <v>73</v>
       </c>
       <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
@@ -2669,6 +2704,7 @@
         <v>75</v>
       </c>
       <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
@@ -2681,6 +2717,7 @@
         <v>77</v>
       </c>
       <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
@@ -2693,6 +2730,7 @@
         <v>79</v>
       </c>
       <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
@@ -2705,8 +2743,9 @@
         <v>81</v>
       </c>
       <c r="D32" s="1"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>252</v>
       </c>
@@ -2717,8 +2756,9 @@
         <v>83</v>
       </c>
       <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>252</v>
       </c>
@@ -2729,8 +2769,9 @@
         <v>85</v>
       </c>
       <c r="D34" s="1"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>252</v>
       </c>
@@ -2741,8 +2782,9 @@
         <v>87</v>
       </c>
       <c r="D35" s="1"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>252</v>
       </c>
@@ -2753,8 +2795,9 @@
         <v>89</v>
       </c>
       <c r="D36" s="1"/>
-    </row>
-    <row r="37" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>252</v>
       </c>
@@ -2765,8 +2808,9 @@
         <v>91</v>
       </c>
       <c r="D37" s="1"/>
-    </row>
-    <row r="38" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>12</v>
       </c>
@@ -2777,8 +2821,9 @@
         <v>93</v>
       </c>
       <c r="D38" s="1"/>
-    </row>
-    <row r="39" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
@@ -2789,8 +2834,9 @@
         <v>95</v>
       </c>
       <c r="D39" s="1"/>
-    </row>
-    <row r="40" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>12</v>
       </c>
@@ -2801,8 +2847,9 @@
         <v>97</v>
       </c>
       <c r="D40" s="1"/>
-    </row>
-    <row r="41" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>12</v>
       </c>
@@ -2813,8 +2860,9 @@
         <v>99</v>
       </c>
       <c r="D41" s="1"/>
-    </row>
-    <row r="42" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>12</v>
       </c>
@@ -2825,8 +2873,9 @@
         <v>101</v>
       </c>
       <c r="D42" s="1"/>
-    </row>
-    <row r="43" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
@@ -2837,8 +2886,9 @@
         <v>103</v>
       </c>
       <c r="D43" s="1"/>
-    </row>
-    <row r="44" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>12</v>
       </c>
@@ -2849,8 +2899,9 @@
         <v>105</v>
       </c>
       <c r="D44" s="1"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>12</v>
       </c>
@@ -2861,8 +2912,9 @@
         <v>107</v>
       </c>
       <c r="D45" s="1"/>
-    </row>
-    <row r="46" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>12</v>
       </c>
@@ -2873,8 +2925,9 @@
         <v>109</v>
       </c>
       <c r="D46" s="1"/>
-    </row>
-    <row r="47" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>12</v>
       </c>
@@ -2885,8 +2938,9 @@
         <v>111</v>
       </c>
       <c r="D47" s="1"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>12</v>
       </c>
@@ -2897,8 +2951,9 @@
         <v>113</v>
       </c>
       <c r="D48" s="1"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E48" s="1"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>12</v>
       </c>
@@ -2909,8 +2964,9 @@
         <v>115</v>
       </c>
       <c r="D49" s="1"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E49" s="1"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>12</v>
       </c>
@@ -2921,8 +2977,9 @@
         <v>117</v>
       </c>
       <c r="D50" s="1"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E50" s="1"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>12</v>
       </c>
@@ -2933,8 +2990,9 @@
         <v>119</v>
       </c>
       <c r="D51" s="1"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E51" s="1"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>12</v>
       </c>
@@ -2945,8 +3003,9 @@
         <v>121</v>
       </c>
       <c r="D52" s="1"/>
-    </row>
-    <row r="53" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E52" s="1"/>
+    </row>
+    <row r="53" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>12</v>
       </c>
@@ -2957,8 +3016,9 @@
         <v>123</v>
       </c>
       <c r="D53" s="1"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E53" s="1"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>12</v>
       </c>
@@ -2969,8 +3029,9 @@
         <v>125</v>
       </c>
       <c r="D54" s="1"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E54" s="1"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>12</v>
       </c>
@@ -2981,8 +3042,9 @@
         <v>127</v>
       </c>
       <c r="D55" s="1"/>
-    </row>
-    <row r="56" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
         <v>12</v>
       </c>
@@ -2993,8 +3055,9 @@
         <v>129</v>
       </c>
       <c r="D56" s="1"/>
-    </row>
-    <row r="57" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
         <v>15</v>
       </c>
@@ -3005,8 +3068,9 @@
         <v>131</v>
       </c>
       <c r="D57" s="1"/>
-    </row>
-    <row r="58" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E57" s="1"/>
+    </row>
+    <row r="58" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>15</v>
       </c>
@@ -3017,8 +3081,9 @@
         <v>133</v>
       </c>
       <c r="D58" s="1"/>
-    </row>
-    <row r="59" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E58" s="1"/>
+    </row>
+    <row r="59" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
         <v>15</v>
       </c>
@@ -3029,8 +3094,9 @@
         <v>135</v>
       </c>
       <c r="D59" s="1"/>
-    </row>
-    <row r="60" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E59" s="1"/>
+    </row>
+    <row r="60" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
         <v>15</v>
       </c>
@@ -3041,8 +3107,9 @@
         <v>137</v>
       </c>
       <c r="D60" s="1"/>
-    </row>
-    <row r="61" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="E60" s="1"/>
+    </row>
+    <row r="61" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
         <v>15</v>
       </c>
@@ -3053,8 +3120,9 @@
         <v>139</v>
       </c>
       <c r="D61" s="1"/>
-    </row>
-    <row r="62" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E61" s="1"/>
+    </row>
+    <row r="62" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
         <v>15</v>
       </c>
@@ -3065,8 +3133,9 @@
         <v>141</v>
       </c>
       <c r="D62" s="1"/>
-    </row>
-    <row r="63" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E62" s="1"/>
+    </row>
+    <row r="63" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
         <v>15</v>
       </c>
@@ -3077,8 +3146,9 @@
         <v>143</v>
       </c>
       <c r="D63" s="1"/>
-    </row>
-    <row r="64" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E63" s="1"/>
+    </row>
+    <row r="64" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
         <v>15</v>
       </c>
@@ -3089,8 +3159,9 @@
         <v>145</v>
       </c>
       <c r="D64" s="1"/>
-    </row>
-    <row r="65" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E64" s="1"/>
+    </row>
+    <row r="65" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>15</v>
       </c>
@@ -3101,8 +3172,9 @@
         <v>147</v>
       </c>
       <c r="D65" s="1"/>
-    </row>
-    <row r="66" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E65" s="1"/>
+    </row>
+    <row r="66" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
         <v>15</v>
       </c>
@@ -3113,8 +3185,9 @@
         <v>149</v>
       </c>
       <c r="D66" s="1"/>
-    </row>
-    <row r="67" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E66" s="1"/>
+    </row>
+    <row r="67" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
         <v>15</v>
       </c>
@@ -3125,8 +3198,9 @@
         <v>151</v>
       </c>
       <c r="D67" s="1"/>
-    </row>
-    <row r="68" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E67" s="1"/>
+    </row>
+    <row r="68" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
         <v>15</v>
       </c>
@@ -3137,8 +3211,9 @@
         <v>153</v>
       </c>
       <c r="D68" s="1"/>
-    </row>
-    <row r="69" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E68" s="1"/>
+    </row>
+    <row r="69" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>15</v>
       </c>
@@ -3149,8 +3224,9 @@
         <v>155</v>
       </c>
       <c r="D69" s="1"/>
-    </row>
-    <row r="70" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E69" s="1"/>
+    </row>
+    <row r="70" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
         <v>15</v>
       </c>
@@ -3161,8 +3237,9 @@
         <v>157</v>
       </c>
       <c r="D70" s="1"/>
-    </row>
-    <row r="71" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E70" s="1"/>
+    </row>
+    <row r="71" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
         <v>15</v>
       </c>
@@ -3173,8 +3250,9 @@
         <v>159</v>
       </c>
       <c r="D71" s="1"/>
-    </row>
-    <row r="72" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E71" s="1"/>
+    </row>
+    <row r="72" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
         <v>15</v>
       </c>
@@ -3185,8 +3263,9 @@
         <v>161</v>
       </c>
       <c r="D72" s="1"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E72" s="1"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
         <v>15</v>
       </c>
@@ -3197,8 +3276,9 @@
         <v>163</v>
       </c>
       <c r="D73" s="1"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E73" s="1"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
         <v>256</v>
       </c>
@@ -3211,8 +3291,11 @@
       <c r="D74" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
         <v>256</v>
       </c>
@@ -3225,8 +3308,11 @@
       <c r="D75" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
         <v>256</v>
       </c>
@@ -3239,8 +3325,11 @@
       <c r="D76" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
         <v>256</v>
       </c>
@@ -3253,8 +3342,11 @@
       <c r="D77" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
         <v>256</v>
       </c>
@@ -3267,8 +3359,11 @@
       <c r="D78" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
         <v>256</v>
       </c>
@@ -3281,8 +3376,11 @@
       <c r="D79" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
         <v>256</v>
       </c>
@@ -3295,8 +3393,11 @@
       <c r="D80" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
         <v>256</v>
       </c>
@@ -3309,8 +3410,11 @@
       <c r="D81" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
         <v>256</v>
       </c>
@@ -3323,8 +3427,11 @@
       <c r="D82" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
         <v>256</v>
       </c>
@@ -3337,8 +3444,11 @@
       <c r="D83" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
         <v>256</v>
       </c>
@@ -3351,8 +3461,11 @@
       <c r="D84" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
         <v>256</v>
       </c>
@@ -3365,8 +3478,11 @@
       <c r="D85" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
         <v>256</v>
       </c>
@@ -3379,8 +3495,11 @@
       <c r="D86" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E86" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
         <v>256</v>
       </c>
@@ -3393,8 +3512,11 @@
       <c r="D87" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
         <v>256</v>
       </c>
@@ -3407,8 +3529,11 @@
       <c r="D88" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E88" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
         <v>256</v>
       </c>
@@ -3421,8 +3546,11 @@
       <c r="D89" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E89" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
         <v>256</v>
       </c>
@@ -3435,8 +3563,11 @@
       <c r="D90" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E90" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
         <v>256</v>
       </c>
@@ -3449,8 +3580,11 @@
       <c r="D91" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E91" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>256</v>
       </c>
@@ -3463,8 +3597,11 @@
       <c r="D92" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E92" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
         <v>256</v>
       </c>
@@ -3477,8 +3614,11 @@
       <c r="D93" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E93" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
         <v>256</v>
       </c>
@@ -3491,8 +3631,11 @@
       <c r="D94" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E94" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
         <v>256</v>
       </c>
@@ -3505,8 +3648,11 @@
       <c r="D95" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E95" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
         <v>256</v>
       </c>
@@ -3519,8 +3665,11 @@
       <c r="D96" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E96" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
         <v>256</v>
       </c>
@@ -3533,8 +3682,11 @@
       <c r="D97" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E97" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
         <v>256</v>
       </c>
@@ -3547,8 +3699,11 @@
       <c r="D98" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E98" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
         <v>256</v>
       </c>
@@ -3561,8 +3716,11 @@
       <c r="D99" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E99" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
         <v>256</v>
       </c>
@@ -3575,8 +3733,11 @@
       <c r="D100" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E100" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
         <v>256</v>
       </c>
@@ -3589,8 +3750,11 @@
       <c r="D101" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E101" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
         <v>256</v>
       </c>
@@ -3603,8 +3767,11 @@
       <c r="D102" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E102" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
         <v>256</v>
       </c>
@@ -3617,8 +3784,11 @@
       <c r="D103" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E103" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
         <v>256</v>
       </c>
@@ -3631,8 +3801,11 @@
       <c r="D104" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E104" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
         <v>256</v>
       </c>
@@ -3645,8 +3818,11 @@
       <c r="D105" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E105" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
         <v>256</v>
       </c>
@@ -3659,8 +3835,11 @@
       <c r="D106" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E106" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
         <v>256</v>
       </c>
@@ -3673,8 +3852,11 @@
       <c r="D107" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E107" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
         <v>256</v>
       </c>
@@ -3687,8 +3869,11 @@
       <c r="D108" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E108" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
         <v>256</v>
       </c>
@@ -3701,8 +3886,11 @@
       <c r="D109" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E109" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
         <v>256</v>
       </c>
@@ -3715,8 +3903,11 @@
       <c r="D110" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E110" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
         <v>256</v>
       </c>
@@ -3729,8 +3920,11 @@
       <c r="D111" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E111" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
         <v>256</v>
       </c>
@@ -3743,8 +3937,11 @@
       <c r="D112" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E112" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
         <v>256</v>
       </c>
@@ -3757,8 +3954,11 @@
       <c r="D113" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E113" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
         <v>256</v>
       </c>
@@ -3771,8 +3971,11 @@
       <c r="D114" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E114" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
         <v>256</v>
       </c>
@@ -3785,8 +3988,11 @@
       <c r="D115" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E115" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
         <v>256</v>
       </c>
@@ -3799,8 +4005,11 @@
       <c r="D116" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E116" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
         <v>256</v>
       </c>
@@ -3813,8 +4022,11 @@
       <c r="D117" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E117" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
         <v>256</v>
       </c>
@@ -3827,8 +4039,11 @@
       <c r="D118" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E118" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
         <v>256</v>
       </c>
@@ -3841,8 +4056,11 @@
       <c r="D119" s="1" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E119" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
         <v>256</v>
       </c>
@@ -3855,8 +4073,11 @@
       <c r="D120" s="1" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E120" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
         <v>373</v>
       </c>
@@ -3867,8 +4088,9 @@
         <v>434</v>
       </c>
       <c r="D121" s="1"/>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E121" s="1"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
         <v>373</v>
       </c>
@@ -3879,8 +4101,9 @@
         <v>438</v>
       </c>
       <c r="D122" s="1"/>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E122" s="1"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
         <v>373</v>
       </c>
@@ -3891,8 +4114,9 @@
         <v>435</v>
       </c>
       <c r="D123" s="1"/>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E123" s="1"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
         <v>373</v>
       </c>
@@ -3903,8 +4127,9 @@
         <v>436</v>
       </c>
       <c r="D124" s="1"/>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E124" s="1"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
         <v>373</v>
       </c>
@@ -3915,8 +4140,9 @@
         <v>418</v>
       </c>
       <c r="D125" s="1"/>
-    </row>
-    <row r="126" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E125" s="1"/>
+    </row>
+    <row r="126" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
         <v>373</v>
       </c>
@@ -3927,8 +4153,9 @@
         <v>439</v>
       </c>
       <c r="D126" s="1"/>
-    </row>
-    <row r="127" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="E126" s="1"/>
+    </row>
+    <row r="127" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
         <v>373</v>
       </c>
@@ -3939,8 +4166,9 @@
         <v>440</v>
       </c>
       <c r="D127" s="1"/>
-    </row>
-    <row r="128" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E127" s="1"/>
+    </row>
+    <row r="128" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
         <v>373</v>
       </c>
@@ -3951,8 +4179,9 @@
         <v>441</v>
       </c>
       <c r="D128" s="1"/>
-    </row>
-    <row r="129" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="E128" s="1"/>
+    </row>
+    <row r="129" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
         <v>373</v>
       </c>
@@ -3963,8 +4192,9 @@
         <v>442</v>
       </c>
       <c r="D129" s="1"/>
-    </row>
-    <row r="130" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="E129" s="1"/>
+    </row>
+    <row r="130" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
         <v>373</v>
       </c>
@@ -3975,8 +4205,9 @@
         <v>443</v>
       </c>
       <c r="D130" s="1"/>
-    </row>
-    <row r="131" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E130" s="1"/>
+    </row>
+    <row r="131" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
         <v>373</v>
       </c>
@@ -3987,8 +4218,9 @@
         <v>444</v>
       </c>
       <c r="D131" s="1"/>
-    </row>
-    <row r="132" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E131" s="1"/>
+    </row>
+    <row r="132" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
         <v>373</v>
       </c>
@@ -3999,8 +4231,9 @@
         <v>419</v>
       </c>
       <c r="D132" s="1"/>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E132" s="1"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
         <v>373</v>
       </c>
@@ -4011,8 +4244,9 @@
         <v>455</v>
       </c>
       <c r="D133" s="1"/>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E133" s="1"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
         <v>373</v>
       </c>
@@ -4023,8 +4257,9 @@
         <v>420</v>
       </c>
       <c r="D134" s="1"/>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E134" s="1"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
         <v>373</v>
       </c>
@@ -4035,8 +4270,9 @@
         <v>421</v>
       </c>
       <c r="D135" s="1"/>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E135" s="1"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
         <v>373</v>
       </c>
@@ -4047,8 +4283,9 @@
         <v>422</v>
       </c>
       <c r="D136" s="1"/>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E136" s="1"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
         <v>373</v>
       </c>
@@ -4059,8 +4296,9 @@
         <v>445</v>
       </c>
       <c r="D137" s="1"/>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E137" s="1"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
         <v>373</v>
       </c>
@@ -4071,8 +4309,9 @@
         <v>446</v>
       </c>
       <c r="D138" s="1"/>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E138" s="1"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
         <v>373</v>
       </c>
@@ -4083,8 +4322,9 @@
         <v>447</v>
       </c>
       <c r="D139" s="1"/>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E139" s="1"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
         <v>373</v>
       </c>
@@ -4095,8 +4335,9 @@
         <v>448</v>
       </c>
       <c r="D140" s="1"/>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E140" s="1"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
         <v>373</v>
       </c>
@@ -4107,8 +4348,9 @@
         <v>423</v>
       </c>
       <c r="D141" s="1"/>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E141" s="1"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
         <v>373</v>
       </c>
@@ -4119,8 +4361,9 @@
         <v>424</v>
       </c>
       <c r="D142" s="1"/>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E142" s="1"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
         <v>373</v>
       </c>
@@ -4131,8 +4374,9 @@
         <v>425</v>
       </c>
       <c r="D143" s="1"/>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E143" s="1"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
         <v>373</v>
       </c>
@@ -4143,8 +4387,9 @@
         <v>426</v>
       </c>
       <c r="D144" s="1"/>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E144" s="1"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
         <v>373</v>
       </c>
@@ -4155,8 +4400,9 @@
         <v>427</v>
       </c>
       <c r="D145" s="1"/>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E145" s="1"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
         <v>373</v>
       </c>
@@ -4167,8 +4413,9 @@
         <v>428</v>
       </c>
       <c r="D146" s="1"/>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E146" s="1"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
         <v>373</v>
       </c>
@@ -4179,8 +4426,9 @@
         <v>402</v>
       </c>
       <c r="D147" s="1"/>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E147" s="1"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
         <v>373</v>
       </c>
@@ -4191,8 +4439,9 @@
         <v>429</v>
       </c>
       <c r="D148" s="1"/>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E148" s="1"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
         <v>373</v>
       </c>
@@ -4203,8 +4452,9 @@
         <v>430</v>
       </c>
       <c r="D149" s="1"/>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E149" s="1"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
         <v>373</v>
       </c>
@@ -4215,8 +4465,9 @@
         <v>431</v>
       </c>
       <c r="D150" s="1"/>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E150" s="1"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
         <v>373</v>
       </c>
@@ -4227,8 +4478,9 @@
         <v>432</v>
       </c>
       <c r="D151" s="1"/>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E151" s="1"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
         <v>373</v>
       </c>
@@ -4239,8 +4491,9 @@
         <v>407</v>
       </c>
       <c r="D152" s="1"/>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E152" s="1"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
         <v>373</v>
       </c>
@@ -4251,8 +4504,9 @@
         <v>408</v>
       </c>
       <c r="D153" s="1"/>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E153" s="1"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
         <v>373</v>
       </c>
@@ -4263,8 +4517,9 @@
         <v>409</v>
       </c>
       <c r="D154" s="1"/>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E154" s="1"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
         <v>373</v>
       </c>
@@ -4275,8 +4530,9 @@
         <v>410</v>
       </c>
       <c r="D155" s="1"/>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E155" s="1"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
         <v>373</v>
       </c>
@@ -4287,8 +4543,9 @@
         <v>411</v>
       </c>
       <c r="D156" s="1"/>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E156" s="1"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
         <v>373</v>
       </c>
@@ -4299,8 +4556,9 @@
         <v>412</v>
       </c>
       <c r="D157" s="1"/>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E157" s="1"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
         <v>373</v>
       </c>
@@ -4311,8 +4569,9 @@
         <v>433</v>
       </c>
       <c r="D158" s="1"/>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E158" s="1"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
         <v>373</v>
       </c>
@@ -4323,8 +4582,9 @@
         <v>414</v>
       </c>
       <c r="D159" s="1"/>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E159" s="1"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
         <v>373</v>
       </c>
@@ -4335,8 +4595,9 @@
         <v>415</v>
       </c>
       <c r="D160" s="1"/>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E160" s="1"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
         <v>373</v>
       </c>
@@ -4347,8 +4608,9 @@
         <v>450</v>
       </c>
       <c r="D161" s="1"/>
-    </row>
-    <row r="162" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E161" s="1"/>
+    </row>
+    <row r="162" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
         <v>373</v>
       </c>
@@ -4359,8 +4621,9 @@
         <v>451</v>
       </c>
       <c r="D162" s="1"/>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E162" s="1"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
         <v>373</v>
       </c>
@@ -4371,8 +4634,9 @@
         <v>449</v>
       </c>
       <c r="D163" s="1"/>
-    </row>
-    <row r="164" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E163" s="1"/>
+    </row>
+    <row r="164" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
         <v>468</v>
       </c>
@@ -4383,8 +4647,9 @@
         <v>473</v>
       </c>
       <c r="D164" s="1"/>
-    </row>
-    <row r="165" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E164" s="1"/>
+    </row>
+    <row r="165" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
         <v>468</v>
       </c>
@@ -4395,8 +4660,9 @@
         <v>495</v>
       </c>
       <c r="D165" s="1"/>
-    </row>
-    <row r="166" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E165" s="1"/>
+    </row>
+    <row r="166" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
         <v>468</v>
       </c>
@@ -4407,8 +4673,9 @@
         <v>494</v>
       </c>
       <c r="D166" s="1"/>
-    </row>
-    <row r="167" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E166" s="1"/>
+    </row>
+    <row r="167" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
         <v>468</v>
       </c>
@@ -4419,8 +4686,9 @@
         <v>496</v>
       </c>
       <c r="D167" s="1"/>
-    </row>
-    <row r="168" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E167" s="1"/>
+    </row>
+    <row r="168" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
         <v>468</v>
       </c>
@@ -4431,8 +4699,9 @@
         <v>497</v>
       </c>
       <c r="D168" s="1"/>
-    </row>
-    <row r="169" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E168" s="1"/>
+    </row>
+    <row r="169" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
         <v>468</v>
       </c>
@@ -4443,8 +4712,9 @@
         <v>498</v>
       </c>
       <c r="D169" s="1"/>
-    </row>
-    <row r="170" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="E169" s="1"/>
+    </row>
+    <row r="170" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
         <v>468</v>
       </c>
@@ -4455,8 +4725,9 @@
         <v>482</v>
       </c>
       <c r="D170" s="1"/>
-    </row>
-    <row r="171" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="E170" s="1"/>
+    </row>
+    <row r="171" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
         <v>468</v>
       </c>
@@ -4467,8 +4738,9 @@
         <v>481</v>
       </c>
       <c r="D171" s="1"/>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E171" s="1"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
         <v>468</v>
       </c>
@@ -4479,8 +4751,9 @@
         <v>474</v>
       </c>
       <c r="D172" s="1"/>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E172" s="1"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
         <v>468</v>
       </c>
@@ -4491,8 +4764,9 @@
         <v>475</v>
       </c>
       <c r="D173" s="1"/>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E173" s="1"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
         <v>468</v>
       </c>
@@ -4503,6 +4777,7 @@
         <v>476</v>
       </c>
       <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5223,18 +5498,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5538,21 +5807,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5577,9 +5849,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5810A7F-6033-4BB7-A499-52EE466B5F05}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71C99907-4E04-42C5-A04D-144B63FCBE57}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="504">
   <si>
     <t>Theme</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Fréquence de rafraichissement</t>
   </si>
   <si>
+    <t>Ordre</t>
+  </si>
+  <si>
     <t>Sources</t>
   </si>
   <si>
@@ -61,6 +64,15 @@
     <t>Parc social</t>
   </si>
   <si>
+    <t>Portrait du parc social à partir des données du Répertoire du Parc Locatif des bailleurs Sociaux (RPLS) au 1er janvier
+L’objectif est de présenter, pour chaque territoire, une synthèse de l’évolution récente du parc, sa
+répartition selon des catégories habituellement utilisées (type de financement, origine, nombre de
+pièces, localisation en QPV...) ainsi qu’un comparatif des indicateurs clés (rotation, vacance,
+surface et loyer…) par catégorie.
+Seuls les logements locatifs ordinaires sont recensés, les logements foyers ne sont
+donc pas compris dans les résultats. Par ailleurs, les informations présentées portent sur le parc locatif social, au sens strict, et n’intègrent donc pas les logements non conventionnés des SEM de France métropolitaine</t>
+  </si>
+  <si>
     <t>support.data@union-habitat.org</t>
   </si>
   <si>
@@ -71,6 +83,13 @@
   </si>
   <si>
     <t xml:space="preserve">Toutes les régions de France y compris les  régions d’Outre-Mer </t>
+  </si>
+  <si>
+    <t>Demandes et attributions</t>
+  </si>
+  <si>
+    <t>Le rapport sur les demandes et les attributions de logements sociaux est réalisé à partir des données du Système National d’Enregistrement (SNE). Il met en parallèle le profil des demandeurs avec celui des attributaires de logements sociaux et montre l’adéquation entre les attributions et la demande au travers de différents indicateurs. 
+Sont considérés comme « demandeurs » les demandeurs en attente d’un logement social à fin décembre de l'année selectionnée et sont comptés comme « attributaires » les ménages ayant emménagé dans un logement social durant l’année sélectionnée. Les chiffres et indicateurs présentés sur le tableau de bord ne prennent pas en compte la demande des associations, mais uniquement celle des demandeurs physiques</t>
   </si>
   <si>
     <t>SNE, INSEE</t>
@@ -83,6 +102,9 @@
 Les engagements dans le cadre du Programme National de Renouvellement Urbain (ANRU) font l'objet d'un traitement distinct et sont présentés séparément des opérations de droit commun. Seules les opérations de France métropolitaine et des régions d'Outre-Mer sont couvertes.</t>
   </si>
   <si>
+    <t>SIAP, INSEE</t>
+  </si>
+  <si>
     <t>Toutes les régions de France y compris les régions d'Outre-Mer</t>
   </si>
   <si>
@@ -93,10 +115,38 @@
 Les opérations ANRU sont exclues du périmètre. Seules les opérations de France métropolitaine et des régions d'Outre-Mer sont couvertes.</t>
   </si>
   <si>
+    <t>Occupation</t>
+  </si>
+  <si>
+    <t>Le rapport sur l’occupation des logements sociaux est élaboré à partir des données issues de l’enquête OPS (Occupation du Parc Social). Réalisée tous les deux ans, cette enquête est menée auprès des organismes d’habitations à loyer modéré (HLM), des sociétés d’économie mixte (SEM) agréées pour le logement social, des administrations publiques, des organismes agréés pour le logement des personnes défavorisées, ainsi que des autres personnes morales propriétaires de logements locatifs sociaux.
+Ce rapport a pour objectif de dresser une synthèse de l’occupation du parc locatif social et de contribuer à une meilleure connaissance des caractéristiques socio-économiques des ménages locataires de logements sociaux.</t>
+  </si>
+  <si>
+    <t>Biennale</t>
+  </si>
+  <si>
+    <t>OPS, INSEE</t>
+  </si>
+  <si>
+    <t>Rénovation et démolition</t>
+  </si>
+  <si>
+    <t>Le rapport sur les réhabilitations et les démolitions est élaboré à partir des données issues de l'Observatoire de la Production Locative (OPL), et concerne les ordres de service lancés. Il a pour objectif de présenter l'évolution du nombre de logements ayant fait l'objet de travaux d'amélioration énergétique, en mettant en valeur ceux ayant connu un changement d'étiquette énergétique, ainsi que les passoires thermiques. Il permet également de suivre l'évolution des démolitions, qu'elles soient ANRU ou hors ANRU.</t>
+  </si>
+  <si>
+    <t>OPL, INSEE</t>
+  </si>
+  <si>
     <t>Indicateur</t>
   </si>
   <si>
     <t>Définition</t>
+  </si>
+  <si>
+    <t>Sous-theme</t>
+  </si>
+  <si>
+    <t>Ordre affichage</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre de logements sociaux du parc  </t>
@@ -330,7 +380,8 @@
     <t>Délai d'attribution</t>
   </si>
   <si>
-    <t>Moyenne du délai d'attribution (en mois)</t>
+    <t>Moyenne du délai d'attribution (en mois)
+Calcul: Nombre de jours écoulés entre la date d'attribution et la date de création de la demande / (365 / 12)</t>
   </si>
   <si>
     <t>Taux de succès</t>
@@ -558,6 +609,616 @@
   </si>
   <si>
     <t>Somme des surfaces utiles en m² des logements agréés dans l'année. Hors ANRU.</t>
+  </si>
+  <si>
+    <t>Relogement</t>
+  </si>
+  <si>
+    <t>Nombre d'opérations</t>
+  </si>
+  <si>
+    <t>Nombre d'opérations de relogement distinctes comprises dans le périmètre d'analyse sélectionné.</t>
+  </si>
+  <si>
+    <t>Vue d'ensemble</t>
+  </si>
+  <si>
+    <t>Nombre de ménages pris en charge</t>
+  </si>
+  <si>
+    <t>Nombre total de ménages suivis au titre du relogement, dossiers principaux et supplémentaires (décohabitants)confondus. Les ménages relogés (Statut d'occupation antérieur = "H") sont exclus de l'ensemble des analyses du rapport</t>
+  </si>
+  <si>
+    <t>Nombre de départs spontanés ou autres</t>
+  </si>
+  <si>
+    <t>Ménages sortis du dispositif sans relogement par le bailleur : départ spontané (décès, départ volontaire), expulsion, prise en charge associative, etc.</t>
+  </si>
+  <si>
+    <t>Moyenne de propositions par ménage relogé</t>
+  </si>
+  <si>
+    <t>Nombre moyen de propositions écrites de logement adressées aux ménages effectivement relogés.</t>
+  </si>
+  <si>
+    <t>Nombre de logements concernés</t>
+  </si>
+  <si>
+    <t>Nombre total de logements de l'opération concernés par le relogement (occupés + vacants).</t>
+  </si>
+  <si>
+    <t>Nombre de logements vacants</t>
+  </si>
+  <si>
+    <t>Parmi les logements concernés, ceux qui étaient vacants.</t>
+  </si>
+  <si>
+    <t>Nombre de ménages relogés</t>
+  </si>
+  <si>
+    <t>Ménages ayant fait l'objet d'un relogement effectif (statut de relogement = « Oui »).</t>
+  </si>
+  <si>
+    <t>Nombre de ménages à reloger</t>
+  </si>
+  <si>
+    <t>Ménages pris en charge restant à reloger (type de relogement = à logement tiroir ou temporaire).</t>
+  </si>
+  <si>
+    <t>Pourcentage de relogement</t>
+  </si>
+  <si>
+    <t>Part des ménages relogés sur l'ensemble des ménages pris en charge ; mesure l'état d'avancement global.</t>
+  </si>
+  <si>
+    <t>Nombre de décohabitants</t>
+  </si>
+  <si>
+    <t>Ménages dont le statut d'occupation antérieur est une décohabitation (départ d'un membre du foyer vers un logement autonome).</t>
+  </si>
+  <si>
+    <t>Nombre de dossiers</t>
+  </si>
+  <si>
+    <t>Nombre de dossiers et sous-dossiers de relogement du périmètre (utilisé notamment dans le suivi par année).</t>
+  </si>
+  <si>
+    <t>Pourcentage des 65 ans et plus</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le représentant est âgé de 65 ans ou plus.</t>
+  </si>
+  <si>
+    <t>Profil des ménages — démographie</t>
+  </si>
+  <si>
+    <t>Nombre de ménages avec ancienneté de plus de 10 ans</t>
+  </si>
+  <si>
+    <t>Ménages occupant leur logement d'origine depuis plus de 10 ans (tranches 10-15 ans et plus de 15 ans).</t>
+  </si>
+  <si>
+    <t>Pourcentage de personnes isolées</t>
+  </si>
+  <si>
+    <t>Part des ménages composés d'une personne seule.</t>
+  </si>
+  <si>
+    <t>NR</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les informations non renseignées pour un indicateur</t>
+  </si>
+  <si>
+    <t>Pourcentage du total</t>
+  </si>
+  <si>
+    <t>Part (en %) d'une catégorie dans le total affiché à l'écran ; mesure de répartition générique des tableaux « Nombre + % total ».</t>
+  </si>
+  <si>
+    <t>Moyenne des ressources mensuelles</t>
+  </si>
+  <si>
+    <t>Ressources mensuelles moyennes du ménage, prestations sociales comprises.</t>
+  </si>
+  <si>
+    <t>Profil des ménages — finances</t>
+  </si>
+  <si>
+    <t>Moyenne du revenu fiscal de référence</t>
+  </si>
+  <si>
+    <t>Revenu fiscal de référence moyen des ménages.</t>
+  </si>
+  <si>
+    <t>Pourcentage de bénéficiaires des APL</t>
+  </si>
+  <si>
+    <t>Part des ménages percevant une aide personnalisée au logement (APL réelle).</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages en emploi</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le représentant occupe un emploi, stable ou précaire.</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages retraités</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le représentant est retraité.</t>
+  </si>
+  <si>
+    <t>Évolution de la surroccupation (Nombre de ménages)</t>
+  </si>
+  <si>
+    <t>Différence entre le nombre de ménages en situation de sur-occupation avant le relogement et le nombre de ménages en situation de sur-occupation après le relogement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Évolution des conditions de logement</t>
+  </si>
+  <si>
+    <t>Moyenne de l'évolution du nombre de pièces</t>
+  </si>
+  <si>
+    <t>Evolution moyenne du nombre de pièces du logement entre avant et après le relogement.</t>
+  </si>
+  <si>
+    <t>Moyenne de l'évolution de la surface (m²)</t>
+  </si>
+  <si>
+    <t>Evolution moyenne de la surface habitable (m²) entre avant et après le relogement.</t>
+  </si>
+  <si>
+    <t>Moyenne de la surface habitable avant</t>
+  </si>
+  <si>
+    <t>Surface habitable moyenne du logement initial.</t>
+  </si>
+  <si>
+    <t>Moyenne de la surface habitable après</t>
+  </si>
+  <si>
+    <t>Surface habitable moyenne du logement de relogement.</t>
+  </si>
+  <si>
+    <t>Moyenne de l'évolution de la surface (%)</t>
+  </si>
+  <si>
+    <t>Variation moyenne de la surface habitable, exprimée en pourcentage de la surface du logement d'origine.</t>
+  </si>
+  <si>
+    <t>Moyenne du reste à charge après</t>
+  </si>
+  <si>
+    <t>Reste à charge mensuel moyen après relogement : dépense de logement réellement supportée (loyer + charges − APL).</t>
+  </si>
+  <si>
+    <t>Impact financier</t>
+  </si>
+  <si>
+    <t>Moyenne du reste à charge avant</t>
+  </si>
+  <si>
+    <t>Reste à charge mensuel moyen avant relogement : loyer + charges − APL du logement d'origine.</t>
+  </si>
+  <si>
+    <t>Moyenne du taux d'effort avant</t>
+  </si>
+  <si>
+    <t>Part moyenne des ressources consacrée à la dépense de logement avant relogement</t>
+  </si>
+  <si>
+    <t>Moyenne du taux d'effort après</t>
+  </si>
+  <si>
+    <t>Part moyenne des ressources consacrée à la dépense de logement après relogement</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages au taux d'effort critique (plus de 30 %)</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le taux d'effort après relogement est supérieur ou égal à 30 %.</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages avec hausse du taux d'effort</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le taux d'effort  est en augmentation par rapport à la situation précédente.</t>
+  </si>
+  <si>
+    <t>Moyenne du loyer avant</t>
+  </si>
+  <si>
+    <t>Loyer de base mensuel moyen avant relogement.</t>
+  </si>
+  <si>
+    <t>Moyenne du loyer après</t>
+  </si>
+  <si>
+    <t>Loyer mensuel moyen inscrit au bail après relogement.</t>
+  </si>
+  <si>
+    <t>Moyenne des charges avant</t>
+  </si>
+  <si>
+    <t>Charges mensuelles moyennes avant relogement (provisions individuelles + collectives).</t>
+  </si>
+  <si>
+    <t>Moyenne des charges après</t>
+  </si>
+  <si>
+    <t>Charges mensuelles moyennes après relogement (provisions individuelles + collectives).</t>
+  </si>
+  <si>
+    <t>Moyenne de l'APL avant</t>
+  </si>
+  <si>
+    <t>APL mensuelle moyenne avant relogement (APL réelle).</t>
+  </si>
+  <si>
+    <t>Moyenne de l'APL après</t>
+  </si>
+  <si>
+    <t>APL mensuelle moyenne après relogement (APL simulée).</t>
+  </si>
+  <si>
+    <t>Moyenne de la quittance avant</t>
+  </si>
+  <si>
+    <t>Quittance mensuelle moyenne avant relogement (loyer + charges).</t>
+  </si>
+  <si>
+    <t>Moyenne de la quittance après</t>
+  </si>
+  <si>
+    <t>Quittance mensuelle moyenne après relogement (loyer + charges).</t>
+  </si>
+  <si>
+    <t>Nombre de ménages par tranche de taux d'effort</t>
+  </si>
+  <si>
+    <t>Répartition des ménages par tranche de taux d'effort, avant et après relogement.</t>
+  </si>
+  <si>
+    <t>Nombre de ménages (matrice de transition du taux d'effort)</t>
+  </si>
+  <si>
+    <t>Nombre de ménages pour chaque combinaison tranche de taux d'effort avant × après ; met en évidence améliorations et dégradations.</t>
+  </si>
+  <si>
+    <t>Nombre de ménages (matrice d'équilibre surface / reste à charge)</t>
+  </si>
+  <si>
+    <t>Nombre de ménages pour chaque combinaison évolution de la surface (%) × évolution du reste à charge (%).</t>
+  </si>
+  <si>
+    <t>Pourcentage de ménages (matrices des déterminants du taux d'effort)</t>
+  </si>
+  <si>
+    <t>Répartition (%) des ménages par modalité d'un facteur (typologie, financement, âge du bâti, nature de logement, QPV, localisation) croisée avec l'évolution du taux d'effort.</t>
+  </si>
+  <si>
+    <t>Position taux d'effort (diagonale)</t>
+  </si>
+  <si>
+    <t>Qualifie, pour un couple de tranches de taux d'effort avant / après, le sens de l'évolution : dégradation, stabilité ou amélioration. Sert à colorer la matrice de transition.</t>
+  </si>
+  <si>
+    <t>Nombre de ménages relogés chez le même bailleur</t>
+  </si>
+  <si>
+    <t>Ménages relogés par leur bailleur d'origine.</t>
+  </si>
+  <si>
+    <t>Nouveau logement</t>
+  </si>
+  <si>
+    <t>Nombre de ménages relogés chez un autre bailleur</t>
+  </si>
+  <si>
+    <t>Ménages relogés par un bailleur différent de leur bailleur d'origine.</t>
+  </si>
+  <si>
+    <t>Taux de réponse à l'enquête OPS</t>
+  </si>
+  <si>
+    <t>Taux de réponse à l'enquête OPS
+Calcul: Nombre de ménages répondants / Nombre de logements occupés</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants répondants</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants parmi les ménages ayant répondu à l'enquête</t>
+  </si>
+  <si>
+    <t>Nombre de ménages répondants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de ménages ayant répondu à l'enquête  </t>
+  </si>
+  <si>
+    <t>Nombre de ménages non répondants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de ménages n'ayant pas répondu à l'enquête  </t>
+  </si>
+  <si>
+    <t>Nombre de logements occupés</t>
+  </si>
+  <si>
+    <t>Nombre de logements occupés, donnés en gestion ou en location</t>
+  </si>
+  <si>
+    <t>Part des occupants &gt; 65 ans</t>
+  </si>
+  <si>
+    <t>Part d'occupants de 65 ans et plus parmi les occupants ayant répondu à l'enquête
+Calcul: Nombre d'occupants de 65 ans et plus / Nombre d'occupants répondants</t>
+  </si>
+  <si>
+    <t>Part de familles nombreuses</t>
+  </si>
+  <si>
+    <t>Part de familles nombreuses (3 enfants ou plus) parmi les ménages ayant répondu sur la composition familiale
+Calcul: (Nombre de familles monoparentales avec 3 enfants ou plus + Nombre de couples avec 3 enfants ou plus) / Nombre de ménages répondants sur la composition familiale</t>
+  </si>
+  <si>
+    <t>Taille moyenne des ménages</t>
+  </si>
+  <si>
+    <t>Taille moyenne des ménages
+Calcul: Nombre d'occupants répondants / Nombre de ménages répondants</t>
+  </si>
+  <si>
+    <t>Part de familles monoparentales</t>
+  </si>
+  <si>
+    <t>Part de familles monoparentales parmi les ménages ayant répondu sur la composition familiale
+Calcul: Nombre de familles monoparentales / Nombre de ménages répondants sur la compositon familiale</t>
+  </si>
+  <si>
+    <t>Part de personnes seules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part de personnes seules parmi les ménages ayant répondu sur la composition familiale
+Calcul: Nombre de personnes seules /   Nombre de ménages répondants sur la compositon familiale
+</t>
+  </si>
+  <si>
+    <t>Part d'occupants majeurs au chômage</t>
+  </si>
+  <si>
+    <t>Part d'occupants majeurs au chômage parmi les occupants majeurs ayant répondu sur la situation professionnelle</t>
+  </si>
+  <si>
+    <t>Part de ménages dont les revenus sont &lt; PLAI</t>
+  </si>
+  <si>
+    <t>Part des ménages dont les plafonds de ressources sont strictement inférieur à 60% du plafond PLUS parmi les ménages ayant répondu sur les ressources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de ménages composés d'une personne isolée majeure sans enfant </t>
+  </si>
+  <si>
+    <t>Nombre de familles monoparentales</t>
+  </si>
+  <si>
+    <t>Nombre de ménages composés d'une personne isolée avec au moins un enfant</t>
+  </si>
+  <si>
+    <t>Nombre de familles monoparentales avec 1 ou 2 enfants</t>
+  </si>
+  <si>
+    <t>Nombre de ménages composés d'une personne isolée avec 1 ou 2 enfant(s)</t>
+  </si>
+  <si>
+    <t>Nombre de familles monoparentales avec 3 enfants ou plus</t>
+  </si>
+  <si>
+    <t>Nombre de ménages composés d'une personne isolée avec 3 enfant(s) ou plus</t>
+  </si>
+  <si>
+    <t>Nombre de couples sans enfant</t>
+  </si>
+  <si>
+    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) sans enfant</t>
+  </si>
+  <si>
+    <t>Nombre de couples avec enfant(s)</t>
+  </si>
+  <si>
+    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec enfant(s)</t>
+  </si>
+  <si>
+    <t>Nombre de couples avec 1 ou 2 enfants</t>
+  </si>
+  <si>
+    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec 1 ou 2 enfant(s)</t>
+  </si>
+  <si>
+    <t>Nombre de couples avec 3 enfants ou plus</t>
+  </si>
+  <si>
+    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec 3 enfant(s) ou plus</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants &lt; 18 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de moins de 18 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants 18-24 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 18 à 24 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants 25-49 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 25 à 49 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants 50-64 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 50 à 64 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants 65-74 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 65 à 74 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants &gt;75 ans</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants âgés de 75 ans ou plus</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants total</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail &lt; 29 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail âgés de moins de 29 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail 30-49 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail âgés de 30 à 49 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail 50-64 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail âgés de 50 à 64 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail &gt; 65 ans</t>
+  </si>
+  <si>
+    <t>Nombre de titulaires du bail âgés de 65 ans ou plus</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont &lt; 40% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont 40-60% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont 60-100% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont 100-130% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont 130-160% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont les revenus sont &gt;160% PLUS</t>
+  </si>
+  <si>
+    <t>Nombre de répondants sur les ressources</t>
+  </si>
+  <si>
+    <t>Nombre de ménages ayant répondu sur les ressources</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs en CDI</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs en CDD</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs au chômage</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs au chômage (personne en recherche d’emploi)</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs sans emploi</t>
+  </si>
+  <si>
+    <t>Nombre d'occupants majeurs sans emploi: foyer, retraités, pré-retraités, en invalidité, au foyer, étudiants, etc.</t>
+  </si>
+  <si>
+    <t>Emménagés récents</t>
+  </si>
+  <si>
+    <t>Nombre de nouveaux locataires du parc social qui ont emménagé depuis moins de 2 ans</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique (lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements dont changement d'etiquette </t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont changement d'etiquette (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques F et G </t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques F et G (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques E </t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques E (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de logements dont traitement des passoires thermiques F</t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques F (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques G </t>
+  </si>
+  <si>
+    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques G (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Changement de vecteur energetique</t>
+  </si>
+  <si>
+    <t>Nombre de logements avec changement de vecteur energetique (ordres de service lancés).Il s'agit du nombre de logements ayant fait l'objet d'une modification du mode de chauffage et de production d'eau chaude sanitaire par l'installation de dispositifs fonctionnant majoritairement à l'aide d'énergies renouvelables.</t>
+  </si>
+  <si>
+    <t>Rénovation énergétique lourde</t>
+  </si>
+  <si>
+    <t>Nombre de logements avec rénovation energétique lourde (ordres de service lancés). La rénovation énergétique est dîte "lourde" si le coût des travaux est supérieur à 50k€ par logement</t>
+  </si>
+  <si>
+    <t>Démolitions ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de démolitions ANRU (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Démolitions hors ANRU</t>
+  </si>
+  <si>
+    <t>Nombre de démolitions Hors ANRU (ordres de service lancés)</t>
+  </si>
+  <si>
+    <t>Nombre de démolitions total</t>
+  </si>
+  <si>
+    <t>Nombre de démolitions total (ordres de service lancés)</t>
   </si>
   <si>
     <t>Axe</t>
@@ -691,6 +1352,9 @@
 Autre: Ménages n'entrant pas dans les catégories sus-citées.</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Tranche de ressources par UC</t>
   </si>
   <si>
@@ -742,7 +1406,8 @@
     <t xml:space="preserve">Motifs évoqués par les demandeurs </t>
   </si>
   <si>
-    <t>Perte de logement : Situations de démolition, de logement repris ou mis en vente par le propriétaire ou en procédure d'expulsion.
+    <t>Tous les motifs sont pris en compte, pas seulement le premier.
+Perte de logement : Situations de démolition, de logement repris ou mis en vente par le propriétaire ou en procédure d'expulsion.
 Sans logement ou précaire/insalubre: Sans logement, hébergé/logement temporaire ou situation de logement non décent, insalubre, dangereux ou impropre à l'habitation.
 Evénements familiaux: Situation de divorce, séparation, décohabitation, futur mariage, concubinage ou PACS, regroupement familial ou volonté de se rapprocher de la famille.
 Rapprochement travail/comodités: Situations de mutation professionnelle, de rapprochement du lieu de travail, rapprochement des équipements et services du fait d'un(e) assistant(e) maternelle ou familiale.
@@ -907,10 +1572,10 @@
     <t>Type de bénéficiaire</t>
   </si>
   <si>
-    <t>Catégorie de l'organisme maître d'ouvrage bénéficiaire de l'agrément de production.</t>
-  </si>
-  <si>
-    <t>ESH (Entreprise Sociale pour l'Habitat / SA HLM) · OPH (Office Public de l'Habitat) · Coopérative HLM · SEM (Société d'Économie Mixte) · Organisme agréé · Autre</t>
+    <t>Type de bénéficiaire (personnes agées, jeunes, étudiants, ménages, …)</t>
+  </si>
+  <si>
+    <t>Ménages, GDV, jeunes, personnes agées, étudiants, handicapées, …</t>
   </si>
   <si>
     <t>ANRU / Hors ANRU</t>
@@ -935,770 +1600,119 @@
 Subventions : aides à la pierre de l'État, subventions des collectivités territoriales, aides Action Logement, autres aides publiques</t>
   </si>
   <si>
-    <t>Demandes et attributions</t>
-  </si>
-  <si>
-    <t>Ordre</t>
-  </si>
-  <si>
-    <t>Le rapport sur les demandes et les attributions de logements sociaux est réalisé à partir des données du Système National d’Enregistrement (SNE). Il met en parallèle le profil des demandeurs avec celui des attributaires de logements sociaux et montre l’adéquation entre les attributions et la demande au travers de différents indicateurs. 
-Sont considérés comme « demandeurs » les demandeurs en attente d’un logement social à fin décembre de l'année selectionnée et sont comptés comme « attributaires » les ménages ayant emménagé dans un logement social durant l’année sélectionnée. Les chiffres et indicateurs présentés sur le tableau de bord ne prennent pas en compte la demande des associations, mais uniquement celle des demandeurs physiques</t>
-  </si>
-  <si>
-    <t>SIAP, INSEE</t>
-  </si>
-  <si>
-    <t>Relogement</t>
-  </si>
-  <si>
-    <t>Nombre d'opérations</t>
-  </si>
-  <si>
-    <t>Nombre de ménages pris en charge</t>
-  </si>
-  <si>
-    <t>Nombre de départs spontanés ou autres</t>
-  </si>
-  <si>
-    <t>Moyenne de propositions par ménage relogé</t>
-  </si>
-  <si>
-    <t>Nombre de logements concernés</t>
-  </si>
-  <si>
-    <t>Nombre de logements vacants</t>
-  </si>
-  <si>
-    <t>Nombre de ménages relogés</t>
-  </si>
-  <si>
-    <t>Nombre de ménages à reloger</t>
-  </si>
-  <si>
-    <t>Pourcentage de relogement</t>
-  </si>
-  <si>
-    <t>Nombre de décohabitants</t>
-  </si>
-  <si>
-    <t>Nombre de dossiers</t>
-  </si>
-  <si>
-    <t>Nombre d'opérations de relogement distinctes comprises dans le périmètre d'analyse sélectionné.</t>
-  </si>
-  <si>
-    <t>Nombre total de ménages suivis au titre du relogement, dossiers principaux et supplémentaires (hébergés, décohabitants) confondus, tous statuts.</t>
-  </si>
-  <si>
-    <t>Ménages sortis du dispositif sans relogement par le bailleur : départ spontané (décès, départ volontaire), expulsion, prise en charge associative, etc.</t>
-  </si>
-  <si>
-    <t>Nombre moyen de propositions écrites de logement adressées aux ménages effectivement relogés.</t>
-  </si>
-  <si>
-    <t>Nombre total de logements de l'opération concernés par le relogement (occupés + vacants).</t>
-  </si>
-  <si>
-    <t>Parmi les logements concernés, ceux qui étaient vacants.</t>
-  </si>
-  <si>
-    <t>Ménages ayant fait l'objet d'un relogement effectif (statut de relogement = « Oui »).</t>
-  </si>
-  <si>
-    <t>Ménages pris en charge restant à reloger.</t>
-  </si>
-  <si>
-    <t>Part des ménages relogés sur l'ensemble des ménages pris en charge ; mesure l'état d'avancement global.</t>
-  </si>
-  <si>
-    <t>Ménages dont le statut d'occupation antérieur est une décohabitation (départ d'un membre du foyer vers un logement autonome).</t>
-  </si>
-  <si>
-    <t>Nombre de dossiers de relogement du périmètre (utilisé notamment dans le suivi par année).</t>
-  </si>
-  <si>
-    <t>Vue d'ensemble</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Pourcentage des 65 ans et plus</t>
-  </si>
-  <si>
-    <t>Nombre de ménages avec ancienneté de plus de 10 ans</t>
-  </si>
-  <si>
-    <t>Pourcentage de personnes isolées</t>
-  </si>
-  <si>
-    <t>Pourcentage du total</t>
-  </si>
-  <si>
-    <t>Profil des ménages — démographie</t>
-  </si>
-  <si>
-    <t>Part des ménages dont le représentant est âgé de 65 ans ou plus.</t>
-  </si>
-  <si>
-    <t>Ménages occupant leur logement d'origine depuis plus de 10 ans (tranches 10-15 ans et plus de 15 ans).</t>
-  </si>
-  <si>
-    <t>Part des ménages composés d'une personne seule.</t>
-  </si>
-  <si>
-    <t>Part (en %) d'une catégorie dans le total affiché à l'écran ; mesure de répartition générique des tableaux « Nombre + % total ».</t>
-  </si>
-  <si>
-    <t>Moyenne des ressources mensuelles</t>
-  </si>
-  <si>
-    <t>Moyenne du revenu fiscal de référence</t>
-  </si>
-  <si>
-    <t>Pourcentage de bénéficiaires des APL</t>
-  </si>
-  <si>
-    <t>Pourcentage de ménages en emploi</t>
-  </si>
-  <si>
-    <t>Pourcentage de ménages retraités</t>
-  </si>
-  <si>
-    <t>Profil des ménages — finances</t>
-  </si>
-  <si>
-    <t>Ressources mensuelles moyennes du ménage, prestations sociales comprises.</t>
-  </si>
-  <si>
-    <t>Revenu fiscal de référence moyen des ménages.</t>
-  </si>
-  <si>
-    <t>Part des ménages percevant une aide personnalisée au logement (APL réelle).</t>
-  </si>
-  <si>
-    <t>Part des ménages dont le représentant occupe un emploi, stable ou précaire.</t>
-  </si>
-  <si>
-    <t>Part des ménages dont le représentant est retraité.</t>
-  </si>
-  <si>
-    <t>Évolution de la surroccupation (points)</t>
-  </si>
-  <si>
-    <t>Moyenne de l'évolution du nombre de pièces</t>
-  </si>
-  <si>
-    <t>Moyenne de l'évolution de la surface (m²)</t>
-  </si>
-  <si>
-    <t>Moyenne de la surface habitable avant</t>
-  </si>
-  <si>
-    <t>Moyenne de la surface habitable après</t>
-  </si>
-  <si>
-    <t>Moyenne de l'évolution de la surface (%)</t>
-  </si>
-  <si>
-    <t>Variation, en points, de la part de ménages en situation de sur-occupation entre avant et après le relogement.</t>
-  </si>
-  <si>
-    <t>Variation moyenne du nombre de pièces du logement entre avant et après le relogement.</t>
-  </si>
-  <si>
-    <t>Variation moyenne de la surface habitable (m²) entre avant et après le relogement.</t>
-  </si>
-  <si>
-    <t>Surface habitable moyenne du logement d'origine.</t>
-  </si>
-  <si>
-    <t>Surface habitable moyenne du logement de relogement.</t>
-  </si>
-  <si>
-    <t>Variation moyenne de la surface habitable, exprimée en pourcentage de la surface du logement d'origine.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Évolution des conditions de logement</t>
-  </si>
-  <si>
-    <t>Moyenne du reste à charge après</t>
-  </si>
-  <si>
-    <t>Moyenne du reste à charge avant</t>
-  </si>
-  <si>
-    <t>Moyenne du taux d'effort avant</t>
-  </si>
-  <si>
-    <t>Moyenne du taux d'effort après</t>
-  </si>
-  <si>
-    <t>Pourcentage de ménages au taux d'effort critique (plus de 30 %)</t>
-  </si>
-  <si>
-    <t>Pourcentage de ménages avec hausse du taux d'effort</t>
-  </si>
-  <si>
-    <t>Moyenne du loyer avant</t>
-  </si>
-  <si>
-    <t>Moyenne du loyer après</t>
-  </si>
-  <si>
-    <t>Moyenne des charges avant</t>
-  </si>
-  <si>
-    <t>Moyenne des charges après</t>
-  </si>
-  <si>
-    <t>Moyenne de l'APL avant</t>
-  </si>
-  <si>
-    <t>Moyenne de l'APL après</t>
-  </si>
-  <si>
-    <t>Moyenne de la quittance avant</t>
-  </si>
-  <si>
-    <t>Moyenne de la quittance après</t>
-  </si>
-  <si>
-    <t>Nombre de ménages par tranche de taux d'effort</t>
-  </si>
-  <si>
-    <t>Nombre de ménages (matrice de transition du taux d'effort)</t>
-  </si>
-  <si>
-    <t>Nombre de ménages (matrice d'équilibre surface / reste à charge)</t>
-  </si>
-  <si>
-    <t>Pourcentage de ménages (matrices des déterminants du taux d'effort)</t>
-  </si>
-  <si>
-    <t>Position taux d'effort (diagonale)</t>
-  </si>
-  <si>
-    <t>Reste à charge mensuel moyen après relogement : dépense de logement réellement supportée (loyer + charges − APL).</t>
-  </si>
-  <si>
-    <t>Reste à charge mensuel moyen avant relogement : loyer + charges − APL du logement d'origine. Champ matérialisé dans le fait (CCD resteAChargeActuel).</t>
-  </si>
-  <si>
-    <t>Taux d'effort moyen avant relogement : part des ressources consacrée à la dépense de logement.</t>
-  </si>
-  <si>
-    <t>Taux d'effort moyen après relogement.</t>
-  </si>
-  <si>
-    <t>Part des ménages dont le taux d'effort après relogement est supérieur ou égal à 30 %.</t>
-  </si>
-  <si>
-    <t>Part des ménages dont le taux d'effort augmente de plus de 2,5 points après relogement (tranches « +2,5 à +15 pts » et « &gt; +15 pts »).</t>
-  </si>
-  <si>
-    <t>Loyer de base mensuel moyen avant relogement.</t>
-  </si>
-  <si>
-    <t>Loyer mensuel moyen inscrit au bail après relogement.</t>
-  </si>
-  <si>
-    <t>Charges mensuelles moyennes avant relogement (provisions individuelles + collectives).</t>
-  </si>
-  <si>
-    <t>Charges mensuelles moyennes après relogement (provisions individuelles + collectives).</t>
-  </si>
-  <si>
-    <t>APL mensuelle moyenne avant relogement (APL réelle).</t>
-  </si>
-  <si>
-    <t>APL mensuelle moyenne après relogement (APL simulée).</t>
-  </si>
-  <si>
-    <t>Quittance mensuelle moyenne avant relogement (loyer + charges).</t>
-  </si>
-  <si>
-    <t>Quittance mensuelle moyenne après relogement.</t>
-  </si>
-  <si>
-    <t>Répartition des ménages par tranche de taux d'effort, avant et après relogement.</t>
-  </si>
-  <si>
-    <t>Nombre de ménages pour chaque combinaison tranche de taux d'effort avant × après ; met en évidence améliorations et dégradations.</t>
-  </si>
-  <si>
-    <t>Nombre de ménages pour chaque combinaison évolution de la surface (%) × évolution du reste à charge (%).</t>
-  </si>
-  <si>
-    <t>Répartition (%) des ménages par modalité d'un facteur (typologie, financement, âge du bâti, nature de logement, QPV, localisation) croisée avec l'évolution du taux d'effort.</t>
-  </si>
-  <si>
-    <t>Qualifie, pour un couple de tranches de taux d'effort avant / après, le sens de l'évolution : dégradation, stabilité ou amélioration. Sert à colorer la matrice de transition.</t>
-  </si>
-  <si>
-    <t>Impact financier</t>
-  </si>
-  <si>
-    <t>Nombre de ménages relogés chez le même bailleur</t>
-  </si>
-  <si>
-    <t>Nombre de ménages relogés chez un autre bailleur</t>
-  </si>
-  <si>
-    <t>Nouveau logement</t>
-  </si>
-  <si>
-    <t>Ménages relogés par leur bailleur d'origine.</t>
-  </si>
-  <si>
-    <t>Ménages relogés par un bailleur différent de leur bailleur d'origine.</t>
-  </si>
-  <si>
-    <t>Sous-theme</t>
+    <t>Catégorie de l'organisme maître d'ouvrage bénéficiaire de l'agrément de production.</t>
+  </si>
+  <si>
+    <t>ESH (Entreprise Sociale pour l'Habitat / SA HLM) · OPH (Office Public de l'Habitat) · Coopérative HLM · SEM (Société d'Économie Mixte) · Organisme agréé · Autre</t>
   </si>
   <si>
     <t>Dossier supplémentaire</t>
   </si>
   <si>
+    <t>Dossier rattaché à un dossier principal, créé pour les personnes hébergées ou les décohabitants du ménage.</t>
+  </si>
+  <si>
     <t>Taux d'effort</t>
   </si>
   <si>
+    <t>Part des ressources du ménage consacrée à la dépense de logement (quittance nette d'APL rapportée aux ressources).</t>
+  </si>
+  <si>
     <t>Reste à charge</t>
   </si>
   <si>
+    <t>Dépense de logement réellement supportée par le ménage après déduction de l'APL.</t>
+  </si>
+  <si>
     <t>ANRU / NPNRU</t>
   </si>
   <si>
+    <t>Opération relevant du Nouveau Programme National de Renouvellement Urbain.</t>
+  </si>
+  <si>
     <t>Décohabitation</t>
   </si>
   <si>
+    <t>Départ d'un membre du foyer vers un logement autonome.</t>
+  </si>
+  <si>
     <t>QPV</t>
   </si>
   <si>
+    <t>Quartier prioritaire de la politique de la ville.</t>
+  </si>
+  <si>
     <t>Regroupement</t>
   </si>
   <si>
-    <t>Dossier rattaché à un dossier principal, créé pour les personnes hébergées ou les décohabitants du ménage.</t>
-  </si>
-  <si>
-    <t>Part des ressources du ménage consacrée à la dépense de logement (quittance nette d'APL rapportée aux ressources).</t>
-  </si>
-  <si>
-    <t>Dépense de logement réellement supportée par le ménage après déduction de l'APL.</t>
-  </si>
-  <si>
-    <t>Opération relevant du Nouveau Programme National de Renouvellement Urbain.</t>
-  </si>
-  <si>
-    <t>Départ d'un membre du foyer vers un logement autonome.</t>
-  </si>
-  <si>
-    <t>Quartier prioritaire de la politique de la ville.</t>
-  </si>
-  <si>
     <t>Ensemble d'opérations regroupées définissant un périmètre d'accès et d'analyse — base de la sécurité au niveau ligne (RLS).</t>
   </si>
   <si>
-    <t>Occupation</t>
-  </si>
-  <si>
-    <t>Portrait du parc social à partir des données du Répertoire du Parc Locatif des bailleurs Sociaux (RPLS) au 1er janvier
-L’objectif est de présenter, pour chaque territoire, une synthèse de l’évolution récente du parc, sa
-répartition selon des catégories habituellement utilisées (type de financement, origine, nombre de
-pièces, localisation en QPV...) ainsi qu’un comparatif des indicateurs clés (rotation, vacance,
-surface et loyer…) par catégorie.
-Seuls les logements locatifs ordinaires sont recensés, les logements foyers ne sont
-donc pas compris dans les résultats. Par ailleurs, les informations présentées portent sur le parc locatif social, au sens strict, et n’intègrent donc pas les logements non conventionnés des SEM de France métropolitaine</t>
-  </si>
-  <si>
-    <t>Le rapport sur l’occupation des logements sociaux est élaboré à partir des données issues de l’enquête OPS (Occupation du Parc Social). Réalisée tous les deux ans, cette enquête est menée auprès des organismes d’habitations à loyer modéré (HLM), des sociétés d’économie mixte (SEM) agréées pour le logement social, des administrations publiques, des organismes agréés pour le logement des personnes défavorisées, ainsi que des autres personnes morales propriétaires de logements locatifs sociaux.
-Ce rapport a pour objectif de dresser une synthèse de l’occupation du parc locatif social et de contribuer à une meilleure connaissance des caractéristiques socio-économiques des ménages locataires de logements sociaux.</t>
-  </si>
-  <si>
-    <t>Biennale</t>
-  </si>
-  <si>
-    <t>OPS, INSEE</t>
-  </si>
-  <si>
-    <t>Taux de réponse à l'enquête OPS</t>
-  </si>
-  <si>
-    <t>Nombre de ménages répondants</t>
-  </si>
-  <si>
-    <t>Nombre de ménages non répondants</t>
-  </si>
-  <si>
-    <t>Nombre de logements occupés</t>
-  </si>
-  <si>
-    <t>Part des occupants &gt; 65 ans</t>
-  </si>
-  <si>
-    <t>Part de familles nombreuses</t>
-  </si>
-  <si>
-    <t>Taille moyenne des ménages</t>
-  </si>
-  <si>
-    <t>Part de familles monoparentales</t>
-  </si>
-  <si>
-    <t>Part de personnes seules</t>
-  </si>
-  <si>
-    <t>Part d'occupants majeurs au chômage</t>
-  </si>
-  <si>
-    <t>Part de ménages dont les revenus sont &lt; PLAI</t>
-  </si>
-  <si>
-    <t>Nombre de familles monoparentales</t>
-  </si>
-  <si>
-    <t>Nombre de familles monoparentales avec 1 ou 2 enfants</t>
-  </si>
-  <si>
-    <t>Nombre de familles monoparentales avec 3 enfants ou plus</t>
-  </si>
-  <si>
-    <t>Nombre de couples sans enfant</t>
-  </si>
-  <si>
-    <t>Nombre de couples avec enfant(s)</t>
-  </si>
-  <si>
-    <t>Nombre de couples avec 1 ou 2 enfants</t>
-  </si>
-  <si>
-    <t>Nombre de couples avec 3 enfants ou plus</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants &lt; 18 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants 18-24 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants 25-49 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants 50-64 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants 65-74 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants &gt;75 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants total</t>
-  </si>
-  <si>
-    <t>Nombre de titulaires du bail &lt; 29 ans</t>
-  </si>
-  <si>
-    <t>Nombre de titulaires du bail 30-49 ans</t>
-  </si>
-  <si>
-    <t>Nombre de titulaires du bail 50-64 ans</t>
-  </si>
-  <si>
-    <t>Nombre de titulaires du bail &gt; 65 ans</t>
-  </si>
-  <si>
-    <t>Nombre de ménages dont les revenus sont &lt; 40% PLUS</t>
-  </si>
-  <si>
-    <t>Nombre de ménages dont les revenus sont 40-60% PLUS</t>
-  </si>
-  <si>
-    <t>Nombre de ménages dont les revenus sont 60-100% PLUS</t>
-  </si>
-  <si>
-    <t>Nombre de ménages dont les revenus sont 100-130% PLUS</t>
-  </si>
-  <si>
-    <t>Nombre de ménages dont les revenus sont 130-160% PLUS</t>
-  </si>
-  <si>
-    <t>Nombre de ménages dont les revenus sont &gt;160% PLUS</t>
-  </si>
-  <si>
-    <t>Nombre de répondants sur les ressources</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants majeurs en CDI</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants majeurs en CDD</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants majeurs au chômage</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants majeurs sans emploi</t>
-  </si>
-  <si>
-    <t>Nombre de logements occupés, donnés en gestion ou en location</t>
-  </si>
-  <si>
-    <t>Part des ménages dont les plafonds de ressources sont strictement inférieur à 60% du plafond PLUS parmi les ménages ayant répondu sur les ressources</t>
-  </si>
-  <si>
-    <t>Nombre de ménages composés d'une personne isolée avec au moins un enfant</t>
-  </si>
-  <si>
-    <t>Nombre de ménages composés d'une personne isolée avec 1 ou 2 enfant(s)</t>
-  </si>
-  <si>
-    <t>Nombre de ménages composés d'une personne isolée avec 3 enfant(s) ou plus</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants âgés de moins de 18 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants âgés de 18 à 24 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants âgés de 25 à 49 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants âgés de 50 à 64 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants âgés de 65 à 74 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants âgés de 75 ans ou plus</t>
-  </si>
-  <si>
-    <t>Nombre de titulaires du bail âgés de moins de 29 ans</t>
-  </si>
-  <si>
-    <t>Nombre de titulaires du bail âgés de 30 à 49 ans</t>
-  </si>
-  <si>
-    <t>Nombre de titulaires du bail âgés de 50 à 64 ans</t>
-  </si>
-  <si>
-    <t>Nombre de titulaires du bail âgés de 65 ans ou plus</t>
-  </si>
-  <si>
-    <t>Nombre de ménages ayant répondu sur les ressources</t>
-  </si>
-  <si>
-    <t>Taux de réponse à l'enquête OPS
-Calcul: Nombre de ménages répondants / Nombre de logements occupés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de ménages ayant répondu à l'enquête  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de ménages n'ayant pas répondu à l'enquête  </t>
-  </si>
-  <si>
-    <t>Nombre d'occupants répondants</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants parmi les ménages ayant répondu à l'enquête</t>
-  </si>
-  <si>
-    <t>Part d'occupants de 65 ans et plus parmi les occupants ayant répondu à l'enquête
-Calcul: Nombre d'occupants de 65 ans et plus / Nombre d'occupants répondants</t>
-  </si>
-  <si>
-    <t>Part de familles nombreuses (3 enfants ou plus) parmi les ménages ayant répondu sur la composition familiale
-Calcul: (Nombre de familles monoparentales avec 3 enfants ou plus + Nombre de couples avec 3 enfants ou plus) / Nombre de ménages répondants sur la composition familiale</t>
-  </si>
-  <si>
-    <t>Taille moyenne des ménages
-Calcul: Nombre d'occupants répondants / Nombre de ménages répondants</t>
-  </si>
-  <si>
-    <t>Part de familles monoparentales parmi les ménages ayant répondu sur la composition familiale
-Calcul: Nombre de familles monoparentales / Nombre de ménages répondants sur la compositon familiale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part de personnes seules parmi les ménages ayant répondu sur la composition familiale
-Calcul: Nombre de personnes seules /   Nombre de ménages répondants sur la compositon familiale
-</t>
-  </si>
-  <si>
-    <t>Part d'occupants majeurs au chômage parmi les occupants majeurs ayant répondu sur la situation professionnelle</t>
-  </si>
-  <si>
-    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) sans enfant</t>
-  </si>
-  <si>
-    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec enfant(s)</t>
-  </si>
-  <si>
-    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec 1 ou 2 enfant(s)</t>
-  </si>
-  <si>
-    <t>Nombre de ménages constitués de deux personnes majeures, vivant en couple (mariés, en concubinage, bénéficiant d’un PACS, vivant maritalement) avec 3 enfant(s) ou plus</t>
-  </si>
-  <si>
-    <t>Nombre de nouveaux locataires du parc social qui ont emménagé depuis moins de 2 ans</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants majeurs au chômage (personne en recherche d’emploi)</t>
-  </si>
-  <si>
-    <t>Nombre d'occupants majeurs sans emploi: foyer, retraités, pré-retraités, en invalidité, au foyer, étudiants, etc.</t>
-  </si>
-  <si>
-    <t>Emménagés récents</t>
-  </si>
-  <si>
     <t>Ensemble des ménages</t>
   </si>
   <si>
+    <t>Nombre de ménages ayant répondu à l'enquête</t>
+  </si>
+  <si>
     <t>Les données représentent l’ensemble des ménages du parc social ayant répondu à l’enquête</t>
   </si>
   <si>
-    <t xml:space="preserve">Nombre de ménages composés d'une personne isolée majeure sans enfant </t>
+    <t>Nombre de ménages ayant emmenagés récemment</t>
   </si>
   <si>
     <t>QPV/Hors QPV</t>
   </si>
   <si>
+    <t>Filtre obligatoire: TOUS, QPV, HQPV</t>
+  </si>
+  <si>
+    <t>Echelle géographique</t>
+  </si>
+  <si>
+    <t>Echelle géographique affiché. Met à jour le champ Région/Département/Commune en fonction de la sélection</t>
+  </si>
+  <si>
+    <t>Filtre obligatoire: REGION, DEPARTEMENT ou COMMUNE</t>
+  </si>
+  <si>
+    <t>Région/Département/Commune</t>
+  </si>
+  <si>
+    <t>Sélection du ou des territoires à afficher</t>
+  </si>
+  <si>
     <t>Année</t>
   </si>
   <si>
-    <t>Echelle géographique</t>
-  </si>
-  <si>
-    <t>Filtre obligatoire: REGION, DEPARTEMENT ou COMMUNE</t>
-  </si>
-  <si>
-    <t>Région/Département/Commune</t>
-  </si>
-  <si>
-    <t>Sélection du ou des territoires à afficher</t>
-  </si>
-  <si>
-    <t>Filtre obligatoire: TOUS, QPV, HQPV</t>
-  </si>
-  <si>
-    <t>Echelle géographique affiché. Met à jour le champ Région/Département/Commune en fonction de la sélection</t>
-  </si>
-  <si>
-    <t>Nombre de ménages ayant répondu à l'enquête</t>
-  </si>
-  <si>
-    <t>Nombre de ménages ayant emmenagés récemment</t>
-  </si>
-  <si>
     <t>Année de l'enquête.</t>
   </si>
   <si>
     <t xml:space="preserve"> Les enquêtes OPS ont lieu tous les 2 ans. </t>
   </si>
   <si>
-    <t>Réhabilitations et démolitions</t>
-  </si>
-  <si>
-    <t>Le rapport sur les réhabilitations et les démolitions est élaboré à partir des données issues de l'Observatoire de la Production Locative (OPL), et concerne les ordres de service lancés. Il a pour objectif de présenter l'évolution du nombre de logements ayant fait l'objet de travaux d'amélioration énergétique, en mettant en valeur ceux ayant connu un changement d'étiquette énergétique, ainsi que les passoires thermiques. Il permet également de suivre l'évolution des démolitions, qu'elles soient ANRU ou hors ANRU.</t>
-  </si>
-  <si>
-    <t>OPL, INSEE</t>
-  </si>
-  <si>
-    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique (lancés)</t>
-  </si>
-  <si>
-    <t>Nombre de démolitions total</t>
-  </si>
-  <si>
-    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Nombre de démolitions ANRU (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Nombre de démolitions Hors ANRU (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Nombre de démolitions total (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Changement de vecteur energetique</t>
-  </si>
-  <si>
-    <t>Rénovation énergétique lourde</t>
-  </si>
-  <si>
-    <t>Démolitions ANRU</t>
-  </si>
-  <si>
-    <t>Démolitions hors ANRU</t>
-  </si>
-  <si>
-    <t>Nombre de logements avec rénovation energétique lourde (ordres de service lancés). La rénovation énergétique est dîte "lourde" si le coût des travaux est supérieur à 50k€ par logement</t>
-  </si>
-  <si>
-    <t>Nombre de logements avec changement de vecteur energetique (ordres de service lancés).Il s'agit du nombre de logements ayant fait l'objet d'une modification du mode de chauffage et de production d'eau chaude sanitaire par l'installation de dispositifs fonctionnant majoritairement à l'aide d'énergies renouvelables.</t>
-  </si>
-  <si>
     <t>Régions actuelles</t>
   </si>
   <si>
+    <t>Découpage des régions tel que défini depuis 1er janvier 2026</t>
+  </si>
+  <si>
+    <t>Depuis le 1er janvier 2016, on observe un total de 18 régions, dont 13 en France Métropolitaine</t>
+  </si>
+  <si>
     <t>Régions anciennes</t>
   </si>
   <si>
-    <t>Découpage des régions tel que défini depuis 1er janvier 2026</t>
-  </si>
-  <si>
     <t>Découpage des régions avant le 1er janvier 2016</t>
   </si>
   <si>
-    <t>Depuis le 1er janvier 2016, on observe un total de 18 régions, dont 13 en France Métropolitaine</t>
-  </si>
-  <si>
     <t>Avant le 1er janvier 2016, la France comptait 27 régions, dont 22 en France Métropolitaine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de logements dont changement d'etiquette </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques F et G </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques E </t>
-  </si>
-  <si>
-    <t>Nombre de logements dont traitement des passoires thermiques F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de logements dont traitement des passoires thermiques G </t>
-  </si>
-  <si>
-    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques F et G (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont changement d'etiquette (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques E (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques F (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Nombre de logements bénéficiants de travaux d'amélioration energetique dont traitement des passoires thermiques G (ordres de service lancés)</t>
-  </si>
-  <si>
-    <t>Ordre affichage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1776,7 +1790,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1796,7 +1810,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2133,13 +2146,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="31.86328125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="109" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2153,152 +2166,152 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>253</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" ht="128.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="128.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>374</v>
+        <v>8</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="85.5" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="85.5">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="E4" s="1">
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="71.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="99.75">
       <c r="A6" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>375</v>
+        <v>23</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>376</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>377</v>
+        <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="57">
       <c r="A7" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>469</v>
+        <v>27</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>470</v>
+        <v>28</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2312,2472 +2325,2485 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F174"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F175"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
-    <col min="2" max="2" width="65.59765625" customWidth="1"/>
-    <col min="3" max="3" width="73.59765625" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="65.5703125" customWidth="1"/>
+    <col min="3" max="3" width="73.5703125" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="42.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="42.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="42.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="57" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="71.25" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="57" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" ht="71.25" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" ht="28.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" ht="57" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" ht="57" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" ht="42.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" ht="85.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" ht="57" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="57" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="57" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="42.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="28.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="71.25" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" ht="57" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" ht="42.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" ht="28.5" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" ht="42.75">
       <c r="A36" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" ht="28.5" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" ht="57">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" ht="42.75">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" ht="42.75">
       <c r="A40" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" ht="42.75">
       <c r="A41" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" ht="42.75">
       <c r="A42" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" ht="42.75">
       <c r="A43" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" ht="42.75">
       <c r="A44" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" ht="28.5">
       <c r="A46" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" ht="28.5">
       <c r="A47" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
     </row>
-    <row r="53" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" ht="28.5">
       <c r="A53" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5">
       <c r="A54" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5">
       <c r="A55" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
     </row>
-    <row r="56" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" ht="42.75">
       <c r="A56" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
     </row>
-    <row r="57" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" ht="28.5">
       <c r="A57" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
     </row>
-    <row r="58" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" ht="28.5">
       <c r="A58" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
     </row>
-    <row r="59" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" ht="42.75">
       <c r="A59" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
     </row>
-    <row r="60" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" ht="42.75">
       <c r="A60" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
     </row>
-    <row r="61" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" ht="57">
       <c r="A61" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
     </row>
-    <row r="62" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" ht="28.5">
       <c r="A62" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
     </row>
-    <row r="63" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" ht="42.75">
       <c r="A63" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
     </row>
-    <row r="64" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" ht="28.5">
       <c r="A64" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
     </row>
-    <row r="65" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" ht="28.5">
       <c r="A65" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
     </row>
-    <row r="66" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" ht="28.5">
       <c r="A66" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
     </row>
-    <row r="67" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" ht="28.5">
       <c r="A67" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
     </row>
-    <row r="68" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" ht="28.5">
       <c r="A68" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
     </row>
-    <row r="69" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" ht="42.75">
       <c r="A69" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
     </row>
-    <row r="70" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" ht="42.75">
       <c r="A70" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
     </row>
-    <row r="71" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" ht="42.75">
       <c r="A71" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
     </row>
-    <row r="72" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" ht="28.5">
       <c r="A72" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>257</v>
+        <v>179</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5">
       <c r="A75" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>269</v>
+        <v>183</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5">
       <c r="A76" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>270</v>
+        <v>185</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5">
       <c r="A77" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>260</v>
+        <v>186</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>271</v>
+        <v>187</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5">
       <c r="A78" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>272</v>
+        <v>189</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5">
       <c r="A79" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>273</v>
+        <v>191</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5">
       <c r="A80" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>263</v>
+        <v>192</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>274</v>
+        <v>193</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5">
       <c r="A81" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>264</v>
+        <v>194</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>275</v>
+        <v>195</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5">
       <c r="A82" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>276</v>
+        <v>197</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5">
       <c r="A83" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>266</v>
+        <v>198</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>277</v>
+        <v>199</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5">
       <c r="A84" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>267</v>
+        <v>200</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5">
       <c r="A85" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>286</v>
+        <v>203</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5">
       <c r="A86" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>282</v>
+        <v>205</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>287</v>
+        <v>206</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5">
       <c r="A87" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>288</v>
+        <v>208</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5">
       <c r="A88" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>284</v>
+        <v>209</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E88" s="1">
+        <v>210</v>
+      </c>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E89" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A89" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="E89" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5">
       <c r="A90" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>291</v>
+        <v>213</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>297</v>
+        <v>214</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>295</v>
+        <v>215</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5">
       <c r="A91" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>292</v>
+        <v>216</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>298</v>
+        <v>217</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>295</v>
+        <v>215</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5">
       <c r="A92" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>293</v>
+        <v>218</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>299</v>
+        <v>219</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>295</v>
+        <v>215</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5">
       <c r="A93" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>294</v>
+        <v>220</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>295</v>
+        <v>215</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5">
       <c r="A94" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>307</v>
+        <v>223</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="E94" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>308</v>
+        <v>225</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="E95" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5">
       <c r="A96" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="E96" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5">
       <c r="A97" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>304</v>
+        <v>229</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="E97" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5">
       <c r="A98" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>305</v>
+        <v>231</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>311</v>
+        <v>232</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="E98" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5">
       <c r="A99" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>306</v>
+        <v>233</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="E99" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5">
       <c r="A100" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>314</v>
+        <v>235</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>333</v>
+        <v>236</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>352</v>
+        <v>226</v>
       </c>
       <c r="E100" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>315</v>
+        <v>237</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>334</v>
+        <v>238</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E101" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5">
       <c r="A102" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>316</v>
+        <v>240</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>335</v>
+        <v>241</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E102" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5">
       <c r="A103" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>317</v>
+        <v>242</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>336</v>
+        <v>243</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E103" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5">
       <c r="A104" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>318</v>
+        <v>244</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>337</v>
+        <v>245</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E104" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5">
       <c r="A105" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>319</v>
+        <v>246</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>338</v>
+        <v>247</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E105" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5">
       <c r="A106" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>320</v>
+        <v>248</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>339</v>
+        <v>249</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E106" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5">
       <c r="A107" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>321</v>
+        <v>250</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>340</v>
+        <v>251</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E107" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5">
       <c r="A108" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>322</v>
+        <v>252</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>341</v>
+        <v>253</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E108" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5">
       <c r="A109" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>323</v>
+        <v>254</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>342</v>
+        <v>255</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E109" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5">
       <c r="A110" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C110" s="1" t="s">
-        <v>343</v>
+        <v>257</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5">
       <c r="A111" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>325</v>
+        <v>258</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>344</v>
+        <v>259</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E111" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5">
       <c r="A112" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>326</v>
+        <v>260</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>345</v>
+        <v>261</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E112" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5">
       <c r="A113" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>327</v>
+        <v>262</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>346</v>
+        <v>263</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E113" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5">
       <c r="A114" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>328</v>
+        <v>264</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>347</v>
+        <v>265</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E114" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5">
       <c r="A115" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>329</v>
+        <v>266</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>348</v>
+        <v>267</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E115" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5">
       <c r="A116" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>330</v>
+        <v>268</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>349</v>
+        <v>269</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E116" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:5">
       <c r="A117" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>331</v>
+        <v>270</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>350</v>
+        <v>271</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E117" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:5">
       <c r="A118" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>332</v>
+        <v>272</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>351</v>
+        <v>273</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>352</v>
+        <v>239</v>
       </c>
       <c r="E118" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:5">
       <c r="A119" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>353</v>
+        <v>274</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>355</v>
+        <v>239</v>
       </c>
       <c r="E119" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>354</v>
+        <v>276</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>355</v>
+        <v>278</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:5">
       <c r="A121" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E121" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="28.5">
       <c r="A122" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>437</v>
+        <v>281</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>438</v>
+        <v>282</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:5">
       <c r="A123" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>379</v>
+        <v>283</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>435</v>
+        <v>284</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:5">
       <c r="A124" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>436</v>
+        <v>285</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:5">
       <c r="A125" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>418</v>
+        <v>22</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
     </row>
-    <row r="126" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:5">
       <c r="A126" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>439</v>
+        <v>289</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
     </row>
-    <row r="127" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:5" ht="28.5">
       <c r="A127" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>383</v>
+        <v>291</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>440</v>
+        <v>292</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
     </row>
-    <row r="128" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:5" ht="57">
       <c r="A128" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>441</v>
+        <v>22</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>294</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
     </row>
-    <row r="129" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:5" ht="28.5">
       <c r="A129" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>442</v>
+        <v>22</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>296</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
     </row>
-    <row r="130" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:5" ht="57">
       <c r="A130" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>386</v>
+        <v>297</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>443</v>
+        <v>298</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
     </row>
-    <row r="131" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:5" ht="57">
       <c r="A131" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>444</v>
+        <v>300</v>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
     </row>
-    <row r="132" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:5" ht="28.5">
       <c r="A132" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>388</v>
+        <v>301</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>419</v>
+        <v>302</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:5" ht="28.5">
       <c r="A133" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>455</v>
+        <v>303</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:5">
       <c r="A134" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>389</v>
+        <v>71</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>420</v>
+        <v>305</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:5">
       <c r="A135" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>390</v>
+        <v>306</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>421</v>
+        <v>307</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:5">
       <c r="A136" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>391</v>
+        <v>308</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>422</v>
+        <v>309</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:5">
       <c r="A137" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>392</v>
+        <v>310</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>445</v>
+        <v>311</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:5">
       <c r="A138" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>393</v>
+        <v>312</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>446</v>
+        <v>313</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:5">
       <c r="A139" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>394</v>
+        <v>314</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>447</v>
+        <v>315</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:5">
       <c r="A140" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>395</v>
+        <v>316</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>448</v>
+        <v>317</v>
       </c>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:5">
       <c r="A141" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>396</v>
+        <v>318</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>423</v>
+        <v>319</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:5">
       <c r="A142" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>397</v>
+        <v>320</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>424</v>
+        <v>321</v>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:5">
       <c r="A143" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>398</v>
+        <v>322</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>425</v>
+        <v>323</v>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:5">
       <c r="A144" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>399</v>
+        <v>324</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:5">
       <c r="A145" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>400</v>
+        <v>326</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>427</v>
+        <v>327</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:5">
       <c r="A146" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>401</v>
+        <v>328</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>428</v>
+        <v>329</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:5">
       <c r="A147" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>402</v>
+        <v>331</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:5">
       <c r="A148" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>403</v>
+        <v>332</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>429</v>
+        <v>332</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:5">
       <c r="A149" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>404</v>
+        <v>333</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>430</v>
+        <v>334</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:5">
       <c r="A150" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:5">
       <c r="A151" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>406</v>
+        <v>337</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>432</v>
+        <v>338</v>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:5">
       <c r="A152" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>407</v>
+        <v>339</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>407</v>
+        <v>340</v>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:5">
       <c r="A153" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>408</v>
+        <v>341</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>408</v>
+        <v>341</v>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:5">
       <c r="A154" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>409</v>
+        <v>342</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>409</v>
+        <v>342</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:5">
       <c r="A155" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>410</v>
+        <v>343</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>410</v>
+        <v>343</v>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:5">
       <c r="A156" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>411</v>
+        <v>344</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>411</v>
+        <v>344</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:5">
       <c r="A157" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>412</v>
+        <v>345</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>412</v>
+        <v>345</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:5">
       <c r="A158" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>413</v>
+        <v>346</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>433</v>
+        <v>346</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:5">
       <c r="A159" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>414</v>
+        <v>347</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:5">
       <c r="A160" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>415</v>
+        <v>349</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5">
       <c r="A161" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>416</v>
+        <v>350</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
     </row>
-    <row r="162" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5">
       <c r="A162" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>417</v>
+        <v>351</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>451</v>
+        <v>352</v>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5" ht="28.5">
       <c r="A163" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>452</v>
+        <v>353</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>449</v>
+        <v>354</v>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
     </row>
-    <row r="164" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5">
       <c r="A164" s="1" t="s">
-        <v>468</v>
+        <v>22</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>471</v>
+        <v>355</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>473</v>
+        <v>356</v>
       </c>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
     </row>
-    <row r="165" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5" ht="28.5">
       <c r="A165" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>489</v>
+        <v>357</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>495</v>
+        <v>358</v>
       </c>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
     </row>
-    <row r="166" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5" ht="28.5">
       <c r="A166" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>490</v>
+        <v>359</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>494</v>
+        <v>360</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
     </row>
-    <row r="167" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5" ht="28.5">
       <c r="A167" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>491</v>
+        <v>361</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>496</v>
+        <v>362</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
     </row>
-    <row r="168" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5" ht="28.5">
       <c r="A168" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>492</v>
+        <v>363</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>497</v>
+        <v>364</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
     </row>
-    <row r="169" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5" ht="28.5">
       <c r="A169" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>493</v>
+        <v>365</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>498</v>
+        <v>366</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
     </row>
-    <row r="170" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5" ht="28.5">
       <c r="A170" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>477</v>
+        <v>367</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>482</v>
+        <v>368</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
     </row>
-    <row r="171" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5" ht="57">
       <c r="A171" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>478</v>
+        <v>369</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>481</v>
+        <v>370</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5" ht="42.75">
       <c r="A172" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>479</v>
+        <v>371</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>474</v>
+        <v>372</v>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5">
       <c r="A173" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>480</v>
+        <v>373</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>475</v>
+        <v>374</v>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:5">
       <c r="A174" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>472</v>
+        <v>375</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>476</v>
+        <v>376</v>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4787,709 +4813,709 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.73046875" customWidth="1"/>
-    <col min="2" max="2" width="33.59765625" customWidth="1"/>
-    <col min="3" max="3" width="104.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.265625" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" customWidth="1"/>
+    <col min="3" max="3" width="104.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>164</v>
+        <v>379</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="85.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>166</v>
+        <v>381</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>167</v>
+        <v>382</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>169</v>
+        <v>384</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>385</v>
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="42.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>171</v>
+        <v>386</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>172</v>
+        <v>387</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="114" customHeight="1" x14ac:dyDescent="0.45">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="114" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>174</v>
+        <v>389</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>175</v>
+        <v>390</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="128.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="128.25" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>177</v>
+        <v>392</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>178</v>
+        <v>393</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>180</v>
+        <v>395</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>181</v>
+        <v>396</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="99.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>183</v>
+        <v>398</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="99.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>186</v>
+        <v>401</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>187</v>
+        <v>402</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="171" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>189</v>
+        <v>404</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>190</v>
+        <v>405</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="187.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="187.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>192</v>
+        <v>407</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>193</v>
+        <v>408</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>194</v>
+        <v>409</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="85.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>195</v>
+        <v>411</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>196</v>
+        <v>412</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="270.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="270.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>198</v>
+        <v>414</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>199</v>
+        <v>415</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>177</v>
+        <v>392</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>201</v>
+        <v>417</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="171" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>202</v>
+        <v>418</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>203</v>
+        <v>419</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="285" customHeight="1" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="285" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>205</v>
+        <v>421</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>206</v>
+        <v>422</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="85.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>208</v>
+        <v>424</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>209</v>
+        <v>425</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="242.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="242.25" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>211</v>
+        <v>427</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>212</v>
+        <v>428</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="71.25" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>214</v>
+        <v>430</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>215</v>
+        <v>431</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="99.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>217</v>
+        <v>433</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>218</v>
+        <v>434</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="85.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>220</v>
+        <v>436</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>221</v>
+        <v>437</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="71.25" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>223</v>
+        <v>439</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>224</v>
+        <v>440</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="57" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>226</v>
+        <v>442</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>227</v>
+        <v>443</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="171" customHeight="1" x14ac:dyDescent="0.45">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="171" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>229</v>
+        <v>445</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>230</v>
+        <v>446</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="85.5">
       <c r="A25" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>233</v>
+        <v>449</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="42.75">
       <c r="A26" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>235</v>
+        <v>451</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>236</v>
+        <v>452</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="85.5">
       <c r="A27" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>238</v>
+        <v>454</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>239</v>
+        <v>455</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="57">
       <c r="A28" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>174</v>
+        <v>389</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>241</v>
+        <v>457</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="28.5">
       <c r="A29" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>243</v>
+        <v>459</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>244</v>
+        <v>460</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="57">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>246</v>
+        <v>462</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>247</v>
+        <v>463</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="85.5">
       <c r="A31" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>249</v>
+        <v>465</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>250</v>
+        <v>466</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="85.5">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>233</v>
+        <v>449</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="42.75">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>235</v>
+        <v>451</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>236</v>
+        <v>452</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="85.5">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>238</v>
+        <v>454</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>239</v>
+        <v>455</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="57">
       <c r="A35" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>174</v>
+        <v>389</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>241</v>
+        <v>457</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="42.75">
       <c r="A36" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>243</v>
+        <v>459</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>244</v>
+        <v>468</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>359</v>
+        <v>470</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>366</v>
+        <v>471</v>
       </c>
       <c r="D37" s="1"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>360</v>
+        <v>472</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>367</v>
+        <v>473</v>
       </c>
       <c r="D38" s="1"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>361</v>
+        <v>474</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>368</v>
+        <v>475</v>
       </c>
       <c r="D39" s="1"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>362</v>
+        <v>476</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>369</v>
+        <v>477</v>
       </c>
       <c r="D40" s="1"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>363</v>
+        <v>478</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>370</v>
+        <v>479</v>
       </c>
       <c r="D41" s="1"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>364</v>
+        <v>480</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>371</v>
+        <v>481</v>
       </c>
       <c r="D42" s="1"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>365</v>
+        <v>482</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>372</v>
+        <v>483</v>
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" ht="28.5">
       <c r="A44" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>452</v>
+        <v>355</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>371</v>
+        <v>481</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="D48" s="1"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>457</v>
+        <v>495</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="28.5">
       <c r="A50" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="28.5">
       <c r="A51" s="1" t="s">
-        <v>468</v>
+        <v>26</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -5507,6 +5533,21 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052237A89E8CA214B92381756AEA23611" ma:contentTypeVersion="20" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="510f2d890aca16c7e52118f19c292bce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44042f46-c638-40f0-b803-0a3c16db3a5d" xmlns:ns3="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5bb1233f2449b16a4f87373320f89a9" ns2:_="" ns3:_="">
     <xsd:import namespace="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
@@ -5806,55 +5847,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8E4D90C-A9A5-4A73-BF8C-EEF74536E875}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8E4D90C-A9A5-4A73-BF8C-EEF74536E875}"/>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71C99907-4E04-42C5-A04D-144B63FCBE57}"/>
+  <xr:revisionPtr revIDLastSave="383" documentId="13_ncr:1_{411B2BE2-86D3-43AC-A02C-4AB7B88665B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB512127-B3AC-4981-A452-375F27BB2C88}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="581">
   <si>
     <t>Theme</t>
   </si>
@@ -626,9 +626,6 @@
     <t>Nombre de ménages pris en charge</t>
   </si>
   <si>
-    <t>Nombre total de ménages suivis au titre du relogement, dossiers principaux et supplémentaires (décohabitants)confondus. Les ménages relogés (Statut d'occupation antérieur = "H") sont exclus de l'ensemble des analyses du rapport</t>
-  </si>
-  <si>
     <t>Nombre de départs spontanés ou autres</t>
   </si>
   <si>
@@ -656,21 +653,12 @@
     <t>Nombre de ménages relogés</t>
   </si>
   <si>
-    <t>Ménages ayant fait l'objet d'un relogement effectif (statut de relogement = « Oui »).</t>
-  </si>
-  <si>
     <t>Nombre de ménages à reloger</t>
   </si>
   <si>
-    <t>Ménages pris en charge restant à reloger (type de relogement = à logement tiroir ou temporaire).</t>
-  </si>
-  <si>
     <t>Pourcentage de relogement</t>
   </si>
   <si>
-    <t>Part des ménages relogés sur l'ensemble des ménages pris en charge ; mesure l'état d'avancement global.</t>
-  </si>
-  <si>
     <t>Nombre de décohabitants</t>
   </si>
   <si>
@@ -707,9 +695,6 @@
     <t>NR</t>
   </si>
   <si>
-    <t>Nombre de ménages dont les informations non renseignées pour un indicateur</t>
-  </si>
-  <si>
     <t>Pourcentage du total</t>
   </si>
   <si>
@@ -749,15 +734,6 @@
     <t>Part des ménages dont le représentant est retraité.</t>
   </si>
   <si>
-    <t>Évolution de la surroccupation (Nombre de ménages)</t>
-  </si>
-  <si>
-    <t>Différence entre le nombre de ménages en situation de sur-occupation avant le relogement et le nombre de ménages en situation de sur-occupation après le relogement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Évolution des conditions de logement</t>
-  </si>
-  <si>
     <t>Moyenne de l'évolution du nombre de pièces</t>
   </si>
   <si>
@@ -822,9 +798,6 @@
   </si>
   <si>
     <t>Pourcentage de ménages avec hausse du taux d'effort</t>
-  </si>
-  <si>
-    <t>Part des ménages dont le taux d'effort  est en augmentation par rapport à la situation précédente.</t>
   </si>
   <si>
     <t>Moyenne du loyer avant</t>
@@ -1707,12 +1680,361 @@
   <si>
     <t>Avant le 1er janvier 2016, la France comptait 27 régions, dont 22 en France Métropolitaine</t>
   </si>
+  <si>
+    <t>Le rapport de suivi du relogement est élaboré à partir des données saisies dans l'application eRime par les bailleurs sociaux et leurs partenaires. Il restitue, pour une opération ou un regroupement d'opérations de renouvellement urbain, l'état d'avancement du relogement des ménages ainsi que les effets du relogement sur leurs conditions de logement et leur situation financière.
+Le rapport couvre cinq volets : l'état d'avancement global (ménages pris en charge, relogés, restant à reloger, départs spontanés), le profil des ménages concernés (démographie, ressources, situation professionnelle), les caractéristiques du nouveau logement (bailleur, type de financement, origine du contingent, localisation en QPV ou hors QPV), l'évolution des conditions de logement (surface, nombre de pièces, suroccupation) et l'impact financier du relogement (loyer, charges, APL, quittance, reste à charge et taux d'effort avant et après relogement).
+La maille la plus fine est le dossier (+  dossier supplémentaire) de relogement. L'ensemble des statistiques est restitué selon le scénario sélectionné, qui définit la population de ménages analysée. Les données sont actualisées quotidiennement. L'accès est restreint aux opérations et regroupements d'opérations sur lesquels l'utilisateur est habilité. Cette version ne comporte ni cartographie, ni comparaison historique entre deux dates d'observation.</t>
+  </si>
+  <si>
+    <t>Quotidienne</t>
+  </si>
+  <si>
+    <t>eRime</t>
+  </si>
+  <si>
+    <t>Opérations de renouvellement urbain suivies dans eRime, France métropolitaine et régions d'Outre-Mer</t>
+  </si>
+  <si>
+    <t>Ménages pris en charge restant à reloger ou ayant fait l’objet d’un relogement non définitif (logement tiroir ou relogement temporaire) et devant encore être relogés définitivement. Ne comprend pas les ménages sortis du dispositif sans relogement (voir « Nombre de départs spontanés ou autres »).</t>
+  </si>
+  <si>
+    <t>Ménages hébergés (hors périmètre)</t>
+  </si>
+  <si>
+    <t>Les ménages dont le statut d’occupation antérieur est « hébergé » (H) sont exclus de l’ensemble des analyses du rapport. Ils n’entrent ni dans les effectifs, ni dans les moyennes, ni dans les dénominateurs des pourcentages, y compris dans le nombre de ménages pris en charge. Ces ménages restent consultables dans l’application eRime.</t>
+  </si>
+  <si>
+    <t>Échelle géographique</t>
+  </si>
+  <si>
+    <t>Niveau de restitution géographique de l'analyse. Pilote le filtre territorial situé immédiatement à sa droite, qui devient Région, Département, EPCI ou Commune selon la valeur choisie. Filtre obligatoire, à sélection unique.</t>
+  </si>
+  <si>
+    <t>Filtres</t>
+  </si>
+  <si>
+    <t>Région / Département / EPCI / Commune</t>
+  </si>
+  <si>
+    <t>Sélection du ou des territoires analysés, au niveau défini par l'échelle géographique. Le territoire retenu est celui de rattachement de l'opération de renouvellement urbain (localisation du patrimoine concerné par le relogement), et non celui du logement de relogement.</t>
+  </si>
+  <si>
+    <t>Nature de l'opération</t>
+  </si>
+  <si>
+    <t>Typologie de l'opération de renouvellement urbain à l'origine du relogement (par exemple : démolition de logements locatifs sociaux, réhabilitation, restructuration, vente). Sélection multiple.</t>
+  </si>
+  <si>
+    <t>Bailleur</t>
+  </si>
+  <si>
+    <t>Organisme de logement social porteur de l'opération de renouvellement urbain. À distinguer du bailleur du logement de relogement, qui peut être différent : voir les indicateurs « Nombre de ménages relogés chez le même bailleur » et « chez un autre bailleur ». Sélection multiple.</t>
+  </si>
+  <si>
+    <t>Identifiant de l'opération</t>
+  </si>
+  <si>
+    <t>Code unique attribué à l'opération dans eRime. Permet d'isoler une opération précise ou un ensemble d'opérations ; le nom en clair des opérations retenues est affiché dans la liste des opérations de l'analyse, en page Vue d'ensemble. Sélection multiple.</t>
+  </si>
+  <si>
+    <t>ANRU (O/N)</t>
+  </si>
+  <si>
+    <t>Rattachement de l'opération à un programme national de renouvellement urbain : ANRU (PNRU), NPNRU, ou opération hors programme. Permet d'isoler le périmètre conventionné ANRU, notamment pour les restitutions institutionnelles et l'export anonyme ANRU.</t>
+  </si>
+  <si>
+    <t>Scénario</t>
+  </si>
+  <si>
+    <t>Population de ménages sur laquelle portent l'ensemble des statistiques du rapport. Le scénario s'applique en amont de tous les indicateurs : changer de scénario change la population de référence de toutes les pages, y compris les totaux et les pourcentages. Valeurs : Ensemble des ménages ; Ménages relogés ; Ménages relogés hors QPV ; Ménages relogés en QPV ; Ménages relogés ayant subi une augmentation du taux d'effort. Filtre obligatoire, à sélection unique.</t>
+  </si>
+  <si>
+    <t>Date de début</t>
+  </si>
+  <si>
+    <t>Borne de sélection sur la date de début de l'opération. Seules les opérations dont la date de début est comprise dans l'intervalle choisi sont retenues dans le périmètre d'analyse.</t>
+  </si>
+  <si>
+    <t>Date de fin prévisionnelle</t>
+  </si>
+  <si>
+    <t>Borne de sélection sur la date de fin prévisionnelle de l'opération. Seules les opérations dont la date de fin prévisionnelle est comprise dans l'intervalle choisi sont retenues dans le périmètre d'analyse.</t>
+  </si>
+  <si>
+    <t>Ménages (ou dossiers) dont l'information n'est pas renseignée pour l'indicateur affiché. Les NR sont comptabilisés et affichés à part dans les répartitions.</t>
+  </si>
+  <si>
+    <t>Transversal</t>
+  </si>
+  <si>
+    <t>Évolution des conditions de logement</t>
+  </si>
+  <si>
+    <t>Part des ménages dont le taux d'effort est supérieur au taux d'effort avant relogement.</t>
+  </si>
+  <si>
+    <t>Scénario (population d'étude)</t>
+  </si>
+  <si>
+    <t>Ensemble des ménages
+Ménages relogés
+Ménages relogés hors QPV
+Ménages relogés en QPV
+Ménages relogés ayant subi une augmentation du taux d'effort</t>
+  </si>
+  <si>
+    <t>Statut de relogement</t>
+  </si>
+  <si>
+    <t>Tranche d'âge du représentant du ménage</t>
+  </si>
+  <si>
+    <t>Moins de 30 ans
+30-39 ans
+40-49 ans
+50-59 ans
+60-74 ans
+75 ans et plus
+NR</t>
+  </si>
+  <si>
+    <t>Nombre d'enfants par ménage</t>
+  </si>
+  <si>
+    <t>Répartition des ménages selon le nombre d'enfants, mineurs et majeurs, rattachés au foyer.</t>
+  </si>
+  <si>
+    <t>Ancienneté dans le logement d'origine</t>
+  </si>
+  <si>
+    <t>Typologie du logement</t>
+  </si>
+  <si>
+    <t>Type de financement du logement de relogement</t>
+  </si>
+  <si>
+    <t>Origine du contingent</t>
+  </si>
+  <si>
+    <t>Réservataire au titre duquel le logement de relogement a été attribué.</t>
+  </si>
+  <si>
+    <t>Mobilité inter-bailleurs</t>
+  </si>
+  <si>
+    <t>Distingue les ménages relogés par leur bailleur d'origine de ceux relogés par un autre organisme.</t>
+  </si>
+  <si>
+    <t>QPV / Hors QPV du relogement</t>
+  </si>
+  <si>
+    <t>Tranche de taux d'effort</t>
+  </si>
+  <si>
+    <t>Évolution du taux d'effort</t>
+  </si>
+  <si>
+    <t>Évolution de la surface</t>
+  </si>
+  <si>
+    <t>Suroccupation</t>
+  </si>
+  <si>
+    <t>Évolution de la suroccupation (Nombre de ménages)</t>
+  </si>
+  <si>
+    <t>Différence entre le nombre de ménages en situation de suroccupation avant le relogement et le nombre de ménages en situation de suroccupation après le relogement.</t>
+  </si>
+  <si>
+    <t>Population de ménages sur laquelle portent les statistiques du rapport. Le scénario s'applique en amont de tous les indicateurs : il détermine les effectifs, les moyennes et les dénominateurs de tous les pourcentages de toutes les pages.</t>
+  </si>
+  <si>
+    <t>État du ménage dans le dispositif de relogement. Combiné au type de relogement pour distinguer les ménages relogés à titre définitif de ceux restant à reloger.</t>
+  </si>
+  <si>
+    <t>Ménage relogé : relogement à titre définitif
+Ménage à reloger : relogement non définitif (logement tiroir ou logement temporaire), en attente d'un relogement définitif
+Départ spontané ou autre : sortie du dispositif sans relogement par le bailleur (décès, départ volontaire, expulsion, prise en charge associative)</t>
+  </si>
+  <si>
+    <t>Répartition des ménages selon l'âge du représentant du ménage.</t>
+  </si>
+  <si>
+    <t>Sans enfants
+1 à 2 enfants
+3 enfants et +
+NR</t>
+  </si>
+  <si>
+    <t>Durée d'occupation du logement quitté. L'indicateur « Nombre de ménages avec ancienneté de plus de 10 ans » regroupe les deux dernières tranches.</t>
+  </si>
+  <si>
+    <t>Moins d'un an
+1 - 5 ans
+5 - 10 ans
+10 - 15 ans
+Plus de 15 ans
+NR</t>
+  </si>
+  <si>
+    <t>Nombre de pièces principales du logement. Axe à double rôle : il qualifie le logement d'origine et le logement de relogement, croisés dans la matrice typologie avant / après.</t>
+  </si>
+  <si>
+    <t>T1 ou T1bis
+T2
+T3
+T4
+T5
+T6 ou +
+NR</t>
+  </si>
+  <si>
+    <t>Financement du logement social ou intermédiaire dans lequel le ménage est relogé. Dans les matrices des déterminants du taux d'effort, l'axe est regroupé en trois modalités : PLA, PLUS, PLAI.</t>
+  </si>
+  <si>
+    <t>PLS
+PLA
+PLUS CD 12 %
+PLUS CD 17 %
+PLUS CD 22 %
+PLUS
+PLAI
+PLI
+HLMO
+Autres social
+Autres intermédiaires
+LLS
+LLTS
+NR</t>
+  </si>
+  <si>
+    <t>Contingent prioritaire Préfecture
+Fonctionnaires préfecture et assimilés
+1 % action logement
+Ville
+EPCI
+Bailleur
+Autres Résa
+NR</t>
+  </si>
+  <si>
+    <t>Même bailleur
+Autre bailleur
+NR</t>
+  </si>
+  <si>
+    <t>Localisation du logement de relogement au regard de la géographie prioritaire de la politique de la ville, appréciée par rapport au quartier d'origine. Dans les matrices des déterminants du taux d'effort, l'axe est regroupé en deux modalités : même QPV et Hors QPV.</t>
+  </si>
+  <si>
+    <t>même QPV : relogement dans le même quartier prioritaire
+autre QPV : relogement dans un autre quartier prioritaire
+Hors QPV : relogement hors quartier prioritaire
+NR</t>
+  </si>
+  <si>
+    <t>Répartition des ménages par tranche de taux d'effort, documentée avant et après relogement. Support du tableau « Détail du taux d'effort » et de la matrice de transition.</t>
+  </si>
+  <si>
+    <t>Moins de 10 %
+De 10 % à 15 %
+De 15 % à 20 %
+De 20 % à 25 %
+De 25 % à 30 %
+Plus de 30 %
+NR</t>
+  </si>
+  <si>
+    <t>Variation du taux d'effort entre la situation avant et après relogement, exprimée en points de pourcentage. Deux découpages coexistent dans le rapport.</t>
+  </si>
+  <si>
+    <t>Découpage en 5 bandes (histogramme « Évolution du taux d'effort ») :
+&lt; -15 pts
+]-2,5 ; -15 pts]
+[-2,5 ; +2,5 pts[
+[+2,5 ; +15 pts[
+&gt; +15 pts
+Découpage en 3 bandes (matrices des déterminants) :
+&lt; -2,5 pts
+[-2,5 ; +2,5] pts
+&gt; +2,5 pts</t>
+  </si>
+  <si>
+    <t>Variation de la surface habitable entre le logement d'origine et le logement de relogement, exprimée en pourcentage. Croisée avec la variation du reste à charge dans la matrice d'équilibre.</t>
+  </si>
+  <si>
+    <t>&lt; -5%
+-5-0%
+0%
+0-5%
+5-10%
+10-20%
+20-30%
+30-40%
+&gt;40%
+NR</t>
+  </si>
+  <si>
+    <t>Adéquation entre la taille du ménage et la typologie du logement, documentée avant et après relogement. Restituée dans le visuel « Densité d'occupation ».</t>
+  </si>
+  <si>
+    <t>Sous-occupation
+Équilibre
+Sur-occupation
+NR</t>
+  </si>
+  <si>
+    <t>Statut d'occupation antérieur</t>
+  </si>
+  <si>
+    <t>Situation d'occupation du ménage dans le logement quitté, avant relogement. Porte la règle de périmètre du rapport : les ménages hébergés sont exclus de l'ensemble des analyses.</t>
+  </si>
+  <si>
+    <t>Titulaire d'un bail
+Décohabitation
+Hébergé — exclu du périmètre du rapport
+Propriétaire
+NR</t>
+  </si>
+  <si>
+    <t>Type de relogement</t>
+  </si>
+  <si>
+    <t>Nature du relogement proposé au ménage. Détermine, avec le statut de relogement, si le ménage est comptabilisé comme relogé ou comme restant à reloger.</t>
+  </si>
+  <si>
+    <t>Logement définitif
+Logement tiroir
+Logement temporaire en attente d'un relogement dans du neuf
+Logement temporaire en attente d'un relogement dans l'existant
+NR</t>
+  </si>
+  <si>
+    <t>Localisation du relogement</t>
+  </si>
+  <si>
+    <t>Distance entre la commune d'origine et la commune de relogement.</t>
+  </si>
+  <si>
+    <t>Relogement dans commune
+Relogement hors commune dans agglomération
+Relogement hors agglomération
+NR</t>
+  </si>
+  <si>
+    <t>Nombre total de ménages suivis au titre du relogement, dossiers principaux et supplémentaires (décohabitants) confondus. Les ménages relogés (Statut d'occupation antérieur = "H") sont exclus de l'ensemble des analyses du rapport</t>
+  </si>
+  <si>
+    <t>Ménages ayant fait l'objet d'un relogement définitif (statut de relogement = « Oui » et type de relogement = "D").</t>
+  </si>
+  <si>
+    <t>Part des ménages relogés définitivement parmi les ménages pris en charge restant dans le dispositif. Calcul : Nombre de ménages relogés / (Nombre de ménages relogés + Nombre de ménages à reloger) ; mesure l'état d'avancement global.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1790,7 +2112,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1809,6 +2131,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2145,14 +2473,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.81640625" customWidth="1"/>
     <col min="2" max="2" width="109" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2176,7 +2504,7 @@
       </c>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" ht="128.25" customHeight="1">
+    <row r="2" spans="1:8" ht="128.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2199,7 +2527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="85.5" customHeight="1">
+    <row r="3" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2222,7 +2550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="85.5">
+    <row r="4" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -2245,7 +2573,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="71.25">
+    <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,7 +2596,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="99.75">
+    <row r="6" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -2291,7 +2619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="57">
+    <row r="7" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -2312,6 +2640,29 @@
       </c>
       <c r="G7" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -2325,17 +2676,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F175"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
+  <dimension ref="A1:F185"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="65.5703125" customWidth="1"/>
-    <col min="3" max="3" width="73.5703125" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
+    <col min="2" max="2" width="65.54296875" customWidth="1"/>
+    <col min="3" max="3" width="79.453125" customWidth="1"/>
+    <col min="4" max="4" width="32.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2352,7 +2703,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="42.75" customHeight="1">
+    <row r="2" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2365,7 +2716,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="42.75" customHeight="1">
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -2378,7 +2729,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="42.75" customHeight="1">
+    <row r="4" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2391,7 +2742,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" ht="57" customHeight="1">
+    <row r="5" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2404,7 +2755,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="71.25" customHeight="1">
+    <row r="6" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -2417,7 +2768,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" ht="57" customHeight="1">
+    <row r="7" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2430,7 +2781,7 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="71.25" customHeight="1">
+    <row r="8" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -2443,7 +2794,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="28.5" customHeight="1">
+    <row r="9" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2456,7 +2807,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="57" customHeight="1">
+    <row r="10" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2469,7 +2820,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="57" customHeight="1">
+    <row r="11" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -2482,7 +2833,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="42.75" customHeight="1">
+    <row r="12" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -2495,7 +2846,7 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" ht="85.5" customHeight="1">
+    <row r="13" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -2508,7 +2859,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" ht="57" customHeight="1">
+    <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -2521,7 +2872,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="57" customHeight="1">
+    <row r="15" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -2534,7 +2885,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="57" customHeight="1">
+    <row r="16" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -2547,7 +2898,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -2560,7 +2911,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
@@ -2573,7 +2924,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="42.75" customHeight="1">
+    <row r="19" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2586,7 +2937,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="28.5" customHeight="1">
+    <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>13</v>
       </c>
@@ -2599,7 +2950,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
@@ -2612,7 +2963,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="71.25" customHeight="1">
+    <row r="22" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
@@ -2625,7 +2976,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
@@ -2638,7 +2989,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -2651,7 +3002,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="57" customHeight="1">
+    <row r="25" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
@@ -2664,7 +3015,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:6" ht="42.75" customHeight="1">
+    <row r="26" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -2680,7 +3031,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>13</v>
       </c>
@@ -2693,7 +3044,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>13</v>
       </c>
@@ -2706,7 +3057,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
@@ -2719,7 +3070,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>13</v>
       </c>
@@ -2732,7 +3083,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>13</v>
       </c>
@@ -2745,7 +3096,7 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -2758,7 +3109,7 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
@@ -2771,7 +3122,7 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" ht="28.5" customHeight="1">
+    <row r="34" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>13</v>
       </c>
@@ -2784,7 +3135,7 @@
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>13</v>
       </c>
@@ -2797,7 +3148,7 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" ht="42.75">
+    <row r="36" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>13</v>
       </c>
@@ -2810,7 +3161,7 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" ht="28.5" customHeight="1">
+    <row r="37" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
@@ -2823,7 +3174,7 @@
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" ht="57">
+    <row r="38" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>16</v>
       </c>
@@ -2836,7 +3187,7 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" ht="42.75">
+    <row r="39" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>16</v>
       </c>
@@ -2849,7 +3200,7 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" ht="42.75">
+    <row r="40" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
@@ -2862,7 +3213,7 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" ht="42.75">
+    <row r="41" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>16</v>
       </c>
@@ -2875,7 +3226,7 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" ht="42.75">
+    <row r="42" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>16</v>
       </c>
@@ -2888,7 +3239,7 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="1:5" ht="42.75">
+    <row r="43" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
@@ -2901,7 +3252,7 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" spans="1:5" ht="42.75">
+    <row r="44" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>16</v>
       </c>
@@ -2914,7 +3265,7 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
@@ -2927,7 +3278,7 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="1:5" ht="28.5">
+    <row r="46" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>16</v>
       </c>
@@ -2940,7 +3291,7 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="1:5" ht="28.5">
+    <row r="47" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>16</v>
       </c>
@@ -2953,7 +3304,7 @@
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>16</v>
       </c>
@@ -2966,7 +3317,7 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>16</v>
       </c>
@@ -2979,7 +3330,7 @@
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>16</v>
       </c>
@@ -2992,7 +3343,7 @@
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>16</v>
       </c>
@@ -3005,7 +3356,7 @@
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>16</v>
       </c>
@@ -3018,7 +3369,7 @@
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
     </row>
-    <row r="53" spans="1:5" ht="28.5">
+    <row r="53" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>16</v>
       </c>
@@ -3031,7 +3382,7 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>16</v>
       </c>
@@ -3044,7 +3395,7 @@
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>16</v>
       </c>
@@ -3057,7 +3408,7 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
     </row>
-    <row r="56" spans="1:5" ht="42.75">
+    <row r="56" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>16</v>
       </c>
@@ -3070,7 +3421,7 @@
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
     </row>
-    <row r="57" spans="1:5" ht="28.5">
+    <row r="57" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>20</v>
       </c>
@@ -3083,7 +3434,7 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
     </row>
-    <row r="58" spans="1:5" ht="28.5">
+    <row r="58" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>20</v>
       </c>
@@ -3096,7 +3447,7 @@
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
     </row>
-    <row r="59" spans="1:5" ht="42.75">
+    <row r="59" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>20</v>
       </c>
@@ -3109,7 +3460,7 @@
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
     </row>
-    <row r="60" spans="1:5" ht="42.75">
+    <row r="60" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,7 +3473,7 @@
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
     </row>
-    <row r="61" spans="1:5" ht="57">
+    <row r="61" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>20</v>
       </c>
@@ -3135,7 +3486,7 @@
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
     </row>
-    <row r="62" spans="1:5" ht="28.5">
+    <row r="62" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>20</v>
       </c>
@@ -3148,7 +3499,7 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
     </row>
-    <row r="63" spans="1:5" ht="42.75">
+    <row r="63" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>20</v>
       </c>
@@ -3161,7 +3512,7 @@
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
     </row>
-    <row r="64" spans="1:5" ht="28.5">
+    <row r="64" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3174,7 +3525,7 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
     </row>
-    <row r="65" spans="1:5" ht="28.5">
+    <row r="65" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>20</v>
       </c>
@@ -3187,7 +3538,7 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
     </row>
-    <row r="66" spans="1:5" ht="28.5">
+    <row r="66" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>20</v>
       </c>
@@ -3200,7 +3551,7 @@
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
     </row>
-    <row r="67" spans="1:5" ht="28.5">
+    <row r="67" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>20</v>
       </c>
@@ -3213,7 +3564,7 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
     </row>
-    <row r="68" spans="1:5" ht="28.5">
+    <row r="68" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>20</v>
       </c>
@@ -3226,7 +3577,7 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
     </row>
-    <row r="69" spans="1:5" ht="42.75">
+    <row r="69" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>20</v>
       </c>
@@ -3239,7 +3590,7 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
     </row>
-    <row r="70" spans="1:5" ht="42.75">
+    <row r="70" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>20</v>
       </c>
@@ -3252,7 +3603,7 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
     </row>
-    <row r="71" spans="1:5" ht="42.75">
+    <row r="71" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>20</v>
       </c>
@@ -3265,7 +3616,7 @@
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
     </row>
-    <row r="72" spans="1:5" ht="28.5">
+    <row r="72" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,7 +3629,7 @@
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>20</v>
       </c>
@@ -3291,168 +3642,168 @@
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E82" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>181</v>
@@ -3461,15 +3812,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>201</v>
+        <v>501</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>181</v>
@@ -3478,1332 +3829,1506 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E95" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D96" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E96" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E85" s="1">
+      <c r="D97" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B86" s="1" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E86" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B87" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D99" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E87" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B88" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B89" s="1" t="s">
+      <c r="E100" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E89" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B90" s="1" t="s">
+      <c r="D101" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E101" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D102" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E102" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E90" s="1">
+      <c r="C103" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E103" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C91" s="1" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E91" s="1">
+      <c r="C104" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E104" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C92" s="1" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E105" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E92" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B93" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D106" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E106" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E93" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B94" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D107" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E107" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E94" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B95" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D108" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E108" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E95" s="1">
+      <c r="D109" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E109" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B96" s="1" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E96" s="1">
+      <c r="D110" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E110" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B97" s="1" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E97" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B98" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E98" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E99" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E100" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E101" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E102" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E103" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E104" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E105" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E106" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E107" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E108" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E109" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E110" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="E111" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E112" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E113" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E114" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E115" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>269</v>
+        <v>524</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E116" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E117" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E118" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E119" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>178</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="E120" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E121" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E122" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E123" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E124" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E125" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E126" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E127" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E128" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E129" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E130" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E121" s="1">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E131" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="28.5">
-      <c r="A122" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-    </row>
-    <row r="127" spans="1:5" ht="28.5">
-      <c r="A127" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-    </row>
-    <row r="128" spans="1:5" ht="57">
-      <c r="A128" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D128" s="1"/>
-      <c r="E128" s="1"/>
-    </row>
-    <row r="129" spans="1:5" ht="28.5">
-      <c r="A129" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
-    </row>
-    <row r="130" spans="1:5" ht="57">
-      <c r="A130" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
-    </row>
-    <row r="131" spans="1:5" ht="57">
-      <c r="A131" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-    </row>
-    <row r="132" spans="1:5" ht="28.5">
+    <row r="132" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>301</v>
+      <c r="B132" s="6" t="s">
+        <v>272</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
     </row>
-    <row r="133" spans="1:5" ht="28.5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>303</v>
+      <c r="B133" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>305</v>
+      <c r="B134" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>307</v>
+      <c r="B135" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>279</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>311</v>
+        <v>282</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>313</v>
+        <v>284</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>315</v>
+      <c r="B139" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>287</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>317</v>
+        <v>288</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>319</v>
+        <v>290</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>321</v>
+        <v>292</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>323</v>
+        <v>294</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>324</v>
+        <v>71</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>350</v>
+        <v>328</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
     </row>
-    <row r="163" spans="1:5" ht="28.5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>354</v>
+        <v>332</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>356</v>
+        <v>333</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
     </row>
-    <row r="165" spans="1:5" ht="28.5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>358</v>
+        <v>334</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
     </row>
-    <row r="166" spans="1:5" ht="28.5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>360</v>
+        <v>335</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
     </row>
-    <row r="167" spans="1:5" ht="28.5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>362</v>
+        <v>336</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
     </row>
-    <row r="168" spans="1:5" ht="28.5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>364</v>
+        <v>337</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
     </row>
-    <row r="169" spans="1:5" ht="28.5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>366</v>
+        <v>338</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
     </row>
-    <row r="170" spans="1:5" ht="28.5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>368</v>
+        <v>340</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
     </row>
-    <row r="171" spans="1:5" ht="57">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
     </row>
-    <row r="172" spans="1:5" ht="42.75">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
+    </row>
+    <row r="176" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A176" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+    </row>
+    <row r="177" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A177" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D177" s="1"/>
+      <c r="E177" s="1"/>
+    </row>
+    <row r="178" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A178" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+    </row>
+    <row r="179" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A179" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D179" s="1"/>
+      <c r="E179" s="1"/>
+    </row>
+    <row r="180" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A180" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D180" s="1"/>
+      <c r="E180" s="1"/>
+    </row>
+    <row r="181" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A181" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D181" s="1"/>
+      <c r="E181" s="1"/>
+    </row>
+    <row r="182" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A182" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A183" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A184" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A185" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4812,710 +5337,1032 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
+  <dimension ref="A1:E75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
-    <col min="3" max="3" width="104.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" customWidth="1"/>
+    <col min="3" max="3" width="104.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="85.5" customHeight="1">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.5" customHeight="1">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="42.75" customHeight="1">
+    <row r="4" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="114" customHeight="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="114" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="128.25" customHeight="1">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="128.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="57" customHeight="1">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="99.75" customHeight="1">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="99.75" customHeight="1">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="171" customHeight="1">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="187.5" customHeight="1">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="187.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="85.5" customHeight="1">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="270.75" customHeight="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="270.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="57" customHeight="1">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="171" customHeight="1">
+    <row r="15" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="285" customHeight="1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="285" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="85.5" customHeight="1">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="242.25" customHeight="1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="242.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="71.25" customHeight="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="99.75" customHeight="1">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="85.5" customHeight="1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="71.25" customHeight="1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="57" customHeight="1">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="171" customHeight="1">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="171" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="85.5">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="42.75">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="85.5">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="57">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="28.5">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="57">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="85.5">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="85.5">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="42.75">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="85.5">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="57">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="42.75">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D37" s="1"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="D38" s="1"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="D39" s="1"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D40" s="1"/>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="D41" s="1"/>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="D42" s="1"/>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" ht="28.5">
+    <row r="44" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="D48" s="1"/>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="28.5">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="28.5">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="203" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="116" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -5524,15 +6371,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
@@ -5547,7 +6385,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052237A89E8CA214B92381756AEA23611" ma:contentTypeVersion="20" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="510f2d890aca16c7e52118f19c292bce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44042f46-c638-40f0-b803-0a3c16db3a5d" xmlns:ns3="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5bb1233f2449b16a4f87373320f89a9" ns2:_="" ns3:_="">
     <xsd:import namespace="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
@@ -5847,14 +6685,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7409EEEE-5CCC-44DE-BA4D-C67E7030C62B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8E4D90C-A9A5-4A73-BF8C-EEF74536E875}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8E4D90C-A9A5-4A73-BF8C-EEF74536E875}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D2635B-B916-4E34-9AB4-DDDBD286E60B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>